--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="168">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 27.07.2026 16:47</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 21.09.2026 11:32</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -921,7 +921,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>81.48</v>
+        <v>84.1975</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -930,7 +930,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>11.5607</v>
+        <v>12.6103</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -976,22 +976,22 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C6">
-        <v>83.24</v>
+        <v>70.75</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
       </c>
       <c r="E6">
-        <v>9341.74</v>
+        <v>8758.23</v>
       </c>
       <c r="F6">
-        <v>6352.6</v>
+        <v>5767.7</v>
       </c>
       <c r="G6">
-        <v>6225.44</v>
+        <v>5548.53</v>
       </c>
       <c r="H6">
         <f>MIN(E6:G6)</f>
@@ -1014,22 +1014,22 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C7">
-        <v>78.66</v>
+        <v>66.54</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
       </c>
       <c r="E7">
-        <v>9431.8</v>
+        <v>7778.41</v>
       </c>
       <c r="F7">
-        <v>5918.96</v>
+        <v>5220.66</v>
       </c>
       <c r="G7">
-        <v>5826.48</v>
+        <v>5220.66</v>
       </c>
       <c r="H7">
         <f>MIN(E7:G7)</f>
@@ -1052,22 +1052,22 @@
         <v>23</v>
       </c>
       <c r="B8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>70.99</v>
+        <v>73.29</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
       </c>
       <c r="E8">
-        <v>7320.58</v>
+        <v>8705.02</v>
       </c>
       <c r="F8">
-        <v>6228.91</v>
+        <v>5824.82</v>
       </c>
       <c r="G8">
-        <v>5156.07</v>
+        <v>5749.16</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -1090,22 +1090,22 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>168</v>
+        <v>261</v>
       </c>
       <c r="C9">
-        <v>60.35</v>
+        <v>53.16</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
       </c>
       <c r="E9">
-        <v>6558.15</v>
+        <v>6203.26</v>
       </c>
       <c r="F9">
-        <v>4635.84</v>
+        <v>4287.5</v>
       </c>
       <c r="G9">
-        <v>4531.79</v>
+        <v>4161.4</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -1128,22 +1128,22 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>146</v>
+        <v>194</v>
       </c>
       <c r="C10">
-        <v>58.54</v>
+        <v>47.89</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
       </c>
       <c r="E10">
-        <v>6360.58</v>
+        <v>5505.78</v>
       </c>
       <c r="F10">
-        <v>4462.43</v>
+        <v>3751.56</v>
       </c>
       <c r="G10">
-        <v>4300.58</v>
+        <v>3801.88</v>
       </c>
       <c r="H10">
         <f>MIN(E10:G10)</f>
@@ -1166,22 +1166,22 @@
         <v>29</v>
       </c>
       <c r="B11">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C11">
-        <v>56.64</v>
+        <v>43.78</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
       </c>
       <c r="E11">
-        <v>6336.07</v>
+        <v>4861.52</v>
       </c>
       <c r="F11">
-        <v>4188.56</v>
+        <v>3503.77</v>
       </c>
       <c r="G11">
-        <v>4138.73</v>
+        <v>3450.18</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -1204,22 +1204,22 @@
         <v>30</v>
       </c>
       <c r="B12">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C12">
-        <v>55.91</v>
+        <v>42.95</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
       </c>
       <c r="E12">
-        <v>5926.01</v>
+        <v>5013.6</v>
       </c>
       <c r="F12">
-        <v>4167.63</v>
+        <v>3417.39</v>
       </c>
       <c r="G12">
-        <v>4150.29</v>
+        <v>3467.83</v>
       </c>
       <c r="H12">
         <f>MIN(E12:G12)</f>
@@ -1242,22 +1242,22 @@
         <v>31</v>
       </c>
       <c r="B13">
-        <v>247</v>
+        <v>333</v>
       </c>
       <c r="C13">
-        <v>54.68</v>
+        <v>50</v>
       </c>
       <c r="D13">
         <f>C13*$B$3</f>
       </c>
       <c r="E13">
-        <v>5927.52</v>
+        <v>5767.83</v>
       </c>
       <c r="F13">
-        <v>4161.85</v>
+        <v>3959.63</v>
       </c>
       <c r="G13">
-        <v>4173.41</v>
+        <v>3921.8</v>
       </c>
       <c r="H13">
         <f>MIN(E13:G13)</f>
@@ -1280,22 +1280,22 @@
         <v>32</v>
       </c>
       <c r="B14">
-        <v>383</v>
+        <v>223</v>
       </c>
       <c r="C14">
-        <v>52.57</v>
+        <v>47</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
       </c>
       <c r="E14">
-        <v>5869.83</v>
+        <v>5114.23</v>
       </c>
       <c r="F14">
-        <v>3982.66</v>
+        <v>3820.92</v>
       </c>
       <c r="G14">
-        <v>3924.86</v>
+        <v>3773</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1318,22 +1318,22 @@
         <v>33</v>
       </c>
       <c r="B15">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C15">
-        <v>51.48</v>
+        <v>49.42</v>
       </c>
       <c r="D15">
         <f>C15*$B$3</f>
       </c>
       <c r="E15">
-        <v>5752.14</v>
+        <v>5819.4</v>
       </c>
       <c r="F15">
-        <v>3757.23</v>
+        <v>3902.76</v>
       </c>
       <c r="G15">
-        <v>3965.32</v>
+        <v>4054.21</v>
       </c>
       <c r="H15">
         <f>MIN(E15:G15)</f>
@@ -1356,22 +1356,22 @@
         <v>34</v>
       </c>
       <c r="B16">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C16">
-        <v>48.51</v>
+        <v>43.36</v>
       </c>
       <c r="D16">
         <f>C16*$B$3</f>
       </c>
       <c r="E16">
-        <v>5729.25</v>
+        <v>4956.1</v>
       </c>
       <c r="F16">
-        <v>3802.08</v>
+        <v>3606.29</v>
       </c>
       <c r="G16">
-        <v>3617.11</v>
+        <v>3467.83</v>
       </c>
       <c r="H16">
         <f>MIN(E16:G16)</f>
@@ -1394,22 +1394,22 @@
         <v>35</v>
       </c>
       <c r="B17">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="C17">
-        <v>46.94</v>
+        <v>38.39</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
       </c>
       <c r="E17">
-        <v>5433.76</v>
+        <v>4569.72</v>
       </c>
       <c r="F17">
-        <v>3684.51</v>
+        <v>3020.17</v>
       </c>
       <c r="G17">
-        <v>3514.45</v>
+        <v>3026.47</v>
       </c>
       <c r="H17">
         <f>MIN(E17:G17)</f>
@@ -1432,22 +1432,22 @@
         <v>36</v>
       </c>
       <c r="B18">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C18">
-        <v>44.86</v>
+        <v>45.76</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
       </c>
       <c r="E18">
-        <v>5229.83</v>
+        <v>4921.55</v>
       </c>
       <c r="F18">
-        <v>3494.57</v>
+        <v>3773</v>
       </c>
       <c r="G18">
-        <v>3265.9</v>
+        <v>3737.69</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1470,22 +1470,22 @@
         <v>37</v>
       </c>
       <c r="B19">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="C19">
-        <v>44.04</v>
+        <v>41.91</v>
       </c>
       <c r="D19">
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>5361.04</v>
+        <v>5727.22</v>
       </c>
       <c r="F19">
-        <v>3455.26</v>
+        <v>3272.25</v>
       </c>
       <c r="G19">
-        <v>3288.9</v>
+        <v>3353.08</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1511,19 +1511,19 @@
         <v>75</v>
       </c>
       <c r="C20">
-        <v>36.53</v>
+        <v>29.75</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
       </c>
       <c r="E20">
-        <v>4285.67</v>
+        <v>3720.04</v>
       </c>
       <c r="F20">
-        <v>2709.94</v>
+        <v>2336.18</v>
       </c>
       <c r="G20">
-        <v>2653.18</v>
+        <v>2320.17</v>
       </c>
       <c r="H20">
         <f>MIN(E20:G20)</f>
@@ -1546,22 +1546,22 @@
         <v>39</v>
       </c>
       <c r="B21">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="C21">
-        <v>36.43</v>
+        <v>28.12</v>
       </c>
       <c r="D21">
         <f>C21*$B$3</f>
       </c>
       <c r="E21">
-        <v>4139.42</v>
+        <v>3297.34</v>
       </c>
       <c r="F21">
-        <v>3179.19</v>
+        <v>2456.36</v>
       </c>
       <c r="G21">
-        <v>2947.98</v>
+        <v>2248.42</v>
       </c>
       <c r="H21">
         <f>MIN(E21:G21)</f>
@@ -1584,22 +1584,22 @@
         <v>40</v>
       </c>
       <c r="B22">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="C22">
-        <v>36.33</v>
+        <v>33.29</v>
       </c>
       <c r="D22">
         <f>C22*$B$3</f>
       </c>
       <c r="E22">
-        <v>4029.6</v>
+        <v>3840.97</v>
       </c>
       <c r="F22">
-        <v>3150.29</v>
+        <v>2711.21</v>
       </c>
       <c r="G22">
-        <v>2685.55</v>
+        <v>2815.63</v>
       </c>
       <c r="H22">
         <f>MIN(E22:G22)</f>
@@ -1622,22 +1622,22 @@
         <v>41</v>
       </c>
       <c r="B23">
-        <v>302</v>
+        <v>427</v>
       </c>
       <c r="C23">
-        <v>32</v>
+        <v>23.95</v>
       </c>
       <c r="D23">
         <f>C23*$B$3</f>
       </c>
       <c r="E23">
-        <v>3565.9</v>
+        <v>2956.61</v>
       </c>
       <c r="F23">
-        <v>2439.31</v>
+        <v>1910.46</v>
       </c>
       <c r="G23">
-        <v>2368.79</v>
+        <v>1840.98</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1660,22 +1660,22 @@
         <v>43</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C24">
-        <v>31.95</v>
+        <v>5.07</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
       </c>
       <c r="E24">
-        <v>661.27</v>
+        <v>771.88</v>
       </c>
       <c r="F24">
-        <v>460.35</v>
+        <v>414.88</v>
       </c>
       <c r="G24">
-        <v>462.43</v>
+        <v>535.94</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1698,22 +1698,22 @@
         <v>46</v>
       </c>
       <c r="B25">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="C25">
-        <v>30.18</v>
+        <v>25.6</v>
       </c>
       <c r="D25">
         <f>C25*$B$3</f>
       </c>
       <c r="E25">
-        <v>3234.8</v>
+        <v>2849.17</v>
       </c>
       <c r="F25">
-        <v>2346.13</v>
+        <v>2116.89</v>
       </c>
       <c r="G25">
-        <v>2279.77</v>
+        <v>2112.23</v>
       </c>
       <c r="H25">
         <f>MIN(E25:G25)</f>
@@ -1736,22 +1736,22 @@
         <v>47</v>
       </c>
       <c r="B26">
-        <v>284</v>
+        <v>518</v>
       </c>
       <c r="C26">
-        <v>27.47</v>
+        <v>17.5</v>
       </c>
       <c r="D26">
         <f>C26*$B$3</f>
       </c>
       <c r="E26">
-        <v>3074.34</v>
+        <v>1960.65</v>
       </c>
       <c r="F26">
-        <v>2057.8</v>
+        <v>1387.13</v>
       </c>
       <c r="G26">
-        <v>2062.43</v>
+        <v>1372</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1774,22 +1774,22 @@
         <v>48</v>
       </c>
       <c r="B27">
-        <v>241</v>
+        <v>313</v>
       </c>
       <c r="C27">
-        <v>23.89</v>
+        <v>17.41</v>
       </c>
       <c r="D27">
         <f>C27*$B$3</f>
       </c>
       <c r="E27">
-        <v>2844.39</v>
+        <v>1944.51</v>
       </c>
       <c r="F27">
-        <v>1803.47</v>
+        <v>1380.45</v>
       </c>
       <c r="G27">
-        <v>1801.85</v>
+        <v>1412.35</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1812,22 +1812,22 @@
         <v>49</v>
       </c>
       <c r="B28">
-        <v>431</v>
+        <v>284</v>
       </c>
       <c r="C28">
-        <v>23.24</v>
+        <v>18.87</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
       </c>
       <c r="E28">
-        <v>3090.18</v>
+        <v>2306.42</v>
       </c>
       <c r="F28">
-        <v>1802.31</v>
+        <v>1594.95</v>
       </c>
       <c r="G28">
-        <v>1728.21</v>
+        <v>1525.85</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1850,22 +1850,22 @@
         <v>52</v>
       </c>
       <c r="B29">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="C29">
-        <v>22.38</v>
+        <v>20.67</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
       </c>
       <c r="E29">
-        <v>2484.97</v>
+        <v>2169.48</v>
       </c>
       <c r="F29">
-        <v>1843.58</v>
+        <v>1513.24</v>
       </c>
       <c r="G29">
-        <v>1878.5</v>
+        <v>1475.41</v>
       </c>
       <c r="H29">
         <f>MIN(E29:G29)</f>
@@ -1888,22 +1888,22 @@
         <v>53</v>
       </c>
       <c r="B30">
-        <v>165</v>
+        <v>231</v>
       </c>
       <c r="C30">
-        <v>21.27</v>
+        <v>16.54</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
       </c>
       <c r="E30">
-        <v>2613.76</v>
+        <v>1876.92</v>
       </c>
       <c r="F30">
-        <v>1618.5</v>
+        <v>1336.69</v>
       </c>
       <c r="G30">
-        <v>1549.02</v>
+        <v>1349.3</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1926,22 +1926,22 @@
         <v>54</v>
       </c>
       <c r="B31">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C31">
-        <v>19.76</v>
+        <v>17.6</v>
       </c>
       <c r="D31">
         <f>C31*$B$3</f>
       </c>
       <c r="E31">
-        <v>2133.3</v>
+        <v>1989.4</v>
       </c>
       <c r="F31">
-        <v>1429.02</v>
+        <v>1366.96</v>
       </c>
       <c r="G31">
-        <v>1450.87</v>
+        <v>1374.52</v>
       </c>
       <c r="H31">
         <f>MIN(E31:G31)</f>
@@ -1964,22 +1964,22 @@
         <v>55</v>
       </c>
       <c r="B32">
-        <v>1214</v>
+        <v>620</v>
       </c>
       <c r="C32">
-        <v>19.38</v>
+        <v>15.59</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>2266.01</v>
+        <v>1886.25</v>
       </c>
       <c r="F32">
-        <v>1443.93</v>
+        <v>1286.12</v>
       </c>
       <c r="G32">
-        <v>1439.31</v>
+        <v>1255.99</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -2002,22 +2002,22 @@
         <v>56</v>
       </c>
       <c r="B33">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="C33">
-        <v>18.77</v>
+        <v>13.75</v>
       </c>
       <c r="D33">
         <f>C33*$B$3</f>
       </c>
       <c r="E33">
-        <v>1965.78</v>
+        <v>1645.27</v>
       </c>
       <c r="F33">
-        <v>1329.25</v>
+        <v>1071.88</v>
       </c>
       <c r="G33">
-        <v>1309.6</v>
+        <v>1103.4</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -2040,22 +2040,22 @@
         <v>57</v>
       </c>
       <c r="B34">
-        <v>111</v>
+        <v>251</v>
       </c>
       <c r="C34">
-        <v>18.68</v>
+        <v>15.68</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
       </c>
       <c r="E34">
-        <v>2323.7</v>
+        <v>1804.16</v>
       </c>
       <c r="F34">
-        <v>1410.41</v>
+        <v>1197.98</v>
       </c>
       <c r="G34">
-        <v>1352.6</v>
+        <v>1242.11</v>
       </c>
       <c r="H34">
         <f>MIN(E34:G34)</f>
@@ -2078,22 +2078,22 @@
         <v>58</v>
       </c>
       <c r="B35">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C35">
-        <v>18.39</v>
+        <v>14.9</v>
       </c>
       <c r="D35">
         <f>C35*$B$3</f>
       </c>
       <c r="E35">
-        <v>2315.03</v>
+        <v>1730.64</v>
       </c>
       <c r="F35">
-        <v>1410.41</v>
+        <v>1197.85</v>
       </c>
       <c r="G35">
-        <v>1368.79</v>
+        <v>1182.85</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -2116,22 +2116,22 @@
         <v>60</v>
       </c>
       <c r="B36">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C36">
-        <v>17.35</v>
+        <v>7.23</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
       </c>
       <c r="E36">
-        <v>1859.19</v>
+        <v>839.47</v>
       </c>
       <c r="F36">
-        <v>1277.34</v>
+        <v>624.08</v>
       </c>
       <c r="G36">
-        <v>1277.46</v>
+        <v>716.27</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -2154,22 +2154,22 @@
         <v>61</v>
       </c>
       <c r="B37">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C37">
-        <v>15.84</v>
+        <v>10.51</v>
       </c>
       <c r="D37">
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>1738.27</v>
+        <v>1066.96</v>
       </c>
       <c r="F37">
-        <v>1255.84</v>
+        <v>944.13</v>
       </c>
       <c r="G37">
-        <v>1225.67</v>
+        <v>859.52</v>
       </c>
       <c r="H37">
         <f>MIN(E37:G37)</f>
@@ -2192,22 +2192,22 @@
         <v>62</v>
       </c>
       <c r="B38">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C38">
-        <v>13.82</v>
+        <v>11.91</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>1460.12</v>
+        <v>1404.28</v>
       </c>
       <c r="F38">
-        <v>1141.97</v>
+        <v>886</v>
       </c>
       <c r="G38">
-        <v>1098.15</v>
+        <v>983.6</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -2230,22 +2230,22 @@
         <v>63</v>
       </c>
       <c r="B39">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C39">
-        <v>12.96</v>
+        <v>10.42</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
       </c>
       <c r="E39">
-        <v>1548.67</v>
+        <v>1132.91</v>
       </c>
       <c r="F39">
-        <v>994.22</v>
+        <v>876.29</v>
       </c>
       <c r="G39">
-        <v>1002.54</v>
+        <v>879.95</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -2268,22 +2268,22 @@
         <v>64</v>
       </c>
       <c r="B40">
-        <v>1748</v>
+        <v>899</v>
       </c>
       <c r="C40">
-        <v>12.89</v>
+        <v>9.94</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>1501.16</v>
+        <v>1150.69</v>
       </c>
       <c r="F40">
-        <v>987.17</v>
+        <v>793.19</v>
       </c>
       <c r="G40">
-        <v>981.27</v>
+        <v>787.26</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -2306,22 +2306,22 @@
         <v>66</v>
       </c>
       <c r="B41">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C41">
-        <v>12.39</v>
+        <v>12.76</v>
       </c>
       <c r="D41">
         <f>C41*$B$3</f>
       </c>
       <c r="E41">
-        <v>1493.3</v>
+        <v>1701.89</v>
       </c>
       <c r="F41">
-        <v>922.66</v>
+        <v>1007.56</v>
       </c>
       <c r="G41">
-        <v>949.02</v>
+        <v>1046.65</v>
       </c>
       <c r="H41">
         <f>MIN(E41:G41)</f>
@@ -2344,22 +2344,22 @@
         <v>68</v>
       </c>
       <c r="B42">
-        <v>1480</v>
+        <v>838</v>
       </c>
       <c r="C42">
-        <v>12.2</v>
+        <v>10.01</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
       </c>
       <c r="E42">
-        <v>1517.8</v>
+        <v>1187.01</v>
       </c>
       <c r="F42">
-        <v>946.71</v>
+        <v>832.28</v>
       </c>
       <c r="G42">
-        <v>913.3</v>
+        <v>807.06</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2382,22 +2382,22 @@
         <v>69</v>
       </c>
       <c r="B43">
-        <v>544</v>
+        <v>652</v>
       </c>
       <c r="C43">
-        <v>11.9</v>
+        <v>8.83</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>1290.29</v>
+        <v>930.01</v>
       </c>
       <c r="F43">
-        <v>896.42</v>
+        <v>744.01</v>
       </c>
       <c r="G43">
-        <v>906.36</v>
+        <v>717.53</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2420,22 +2420,22 @@
         <v>70</v>
       </c>
       <c r="B44">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="C44">
-        <v>11.82</v>
+        <v>11.87</v>
       </c>
       <c r="D44">
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1303.7</v>
+        <v>1421.18</v>
       </c>
       <c r="F44">
-        <v>842.54</v>
+        <v>957.75</v>
       </c>
       <c r="G44">
-        <v>831.21</v>
+        <v>873.89</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2458,22 +2458,22 @@
         <v>72</v>
       </c>
       <c r="B45">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="C45">
-        <v>11.76</v>
+        <v>7.17</v>
       </c>
       <c r="D45">
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>1512.26</v>
+        <v>940.98</v>
       </c>
       <c r="F45">
-        <v>881.27</v>
+        <v>612.73</v>
       </c>
       <c r="G45">
-        <v>877.34</v>
+        <v>576.16</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2496,22 +2496,22 @@
         <v>74</v>
       </c>
       <c r="B46">
-        <v>1670</v>
+        <v>1099</v>
       </c>
       <c r="C46">
-        <v>11.04</v>
+        <v>9.1</v>
       </c>
       <c r="D46">
         <f>C46*$B$3</f>
       </c>
       <c r="E46">
-        <v>1279.19</v>
+        <v>1076.29</v>
       </c>
       <c r="F46">
-        <v>824.28</v>
+        <v>737.7</v>
       </c>
       <c r="G46">
-        <v>804.51</v>
+        <v>718.79</v>
       </c>
       <c r="H46">
         <f>MIN(E46:G46)</f>
@@ -2534,22 +2534,22 @@
         <v>75</v>
       </c>
       <c r="B47">
-        <v>166</v>
+        <v>101</v>
       </c>
       <c r="C47">
-        <v>11.04</v>
+        <v>10.54</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>1266.59</v>
+        <v>1161.66</v>
       </c>
       <c r="F47">
-        <v>806.94</v>
+        <v>907.94</v>
       </c>
       <c r="G47">
-        <v>830.98</v>
+        <v>926.23</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2572,22 +2572,22 @@
         <v>76</v>
       </c>
       <c r="B48">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C48">
-        <v>10.42</v>
+        <v>8.55</v>
       </c>
       <c r="D48">
         <f>C48*$B$3</f>
       </c>
       <c r="E48">
-        <v>1313.99</v>
+        <v>1002.64</v>
       </c>
       <c r="F48">
-        <v>796.53</v>
+        <v>715</v>
       </c>
       <c r="G48">
-        <v>771.1</v>
+        <v>677.17</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2610,22 +2610,22 @@
         <v>77</v>
       </c>
       <c r="B49">
-        <v>1469</v>
+        <v>772</v>
       </c>
       <c r="C49">
-        <v>10.1</v>
+        <v>7.7</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>1142.43</v>
+        <v>947.66</v>
       </c>
       <c r="F49">
-        <v>745.67</v>
+        <v>636.82</v>
       </c>
       <c r="G49">
-        <v>735.26</v>
+        <v>621.18</v>
       </c>
       <c r="H49">
         <f>MIN(E49:G49)</f>
@@ -2648,22 +2648,22 @@
         <v>79</v>
       </c>
       <c r="B50">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C50">
-        <v>10.01</v>
+        <v>7.71</v>
       </c>
       <c r="D50">
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>1196.19</v>
+        <v>832.78</v>
       </c>
       <c r="F50">
-        <v>711.45</v>
+        <v>630.39</v>
       </c>
       <c r="G50">
-        <v>710.17</v>
+        <v>630.52</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2686,22 +2686,22 @@
         <v>80</v>
       </c>
       <c r="B51">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="C51">
-        <v>9.83</v>
+        <v>9.4</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>1144.86</v>
+        <v>1075.41</v>
       </c>
       <c r="F51">
-        <v>781.5</v>
+        <v>817.02</v>
       </c>
       <c r="G51">
-        <v>728.21</v>
+        <v>806.3</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2724,22 +2724,22 @@
         <v>81</v>
       </c>
       <c r="B52">
-        <v>452</v>
+        <v>276</v>
       </c>
       <c r="C52">
-        <v>9.82</v>
+        <v>7.8</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>1077.69</v>
+        <v>888.52</v>
       </c>
       <c r="F52">
-        <v>706.36</v>
+        <v>630.52</v>
       </c>
       <c r="G52">
-        <v>682.08</v>
+        <v>622.32</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2762,22 +2762,22 @@
         <v>82</v>
       </c>
       <c r="B53">
-        <v>1048</v>
+        <v>904</v>
       </c>
       <c r="C53">
-        <v>9.78</v>
+        <v>7.79</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>1183.58</v>
+        <v>968.85</v>
       </c>
       <c r="F53">
-        <v>728.32</v>
+        <v>668.35</v>
       </c>
       <c r="G53">
-        <v>700.35</v>
+        <v>630.52</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2800,22 +2800,22 @@
         <v>84</v>
       </c>
       <c r="B54">
-        <v>260</v>
+        <v>434</v>
       </c>
       <c r="C54">
-        <v>9.37</v>
+        <v>5.63</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
       </c>
       <c r="E54">
-        <v>1011.33</v>
+        <v>608.7</v>
       </c>
       <c r="F54">
-        <v>674.57</v>
+        <v>432.41</v>
       </c>
       <c r="G54">
-        <v>693.64</v>
+        <v>438.84</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2838,22 +2838,22 @@
         <v>85</v>
       </c>
       <c r="B55">
-        <v>332</v>
+        <v>637</v>
       </c>
       <c r="C55">
-        <v>9.15</v>
+        <v>7.5</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>1092.72</v>
+        <v>905.42</v>
       </c>
       <c r="F55">
-        <v>682.08</v>
+        <v>567.46</v>
       </c>
       <c r="G55">
-        <v>707.28</v>
+        <v>567.46</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2876,22 +2876,22 @@
         <v>86</v>
       </c>
       <c r="B56">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C56">
-        <v>8.96</v>
+        <v>7.33</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>949.71</v>
+        <v>836.06</v>
       </c>
       <c r="F56">
-        <v>658.96</v>
+        <v>704.79</v>
       </c>
       <c r="G56">
-        <v>669.36</v>
+        <v>686.38</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2914,22 +2914,22 @@
         <v>87</v>
       </c>
       <c r="B57">
-        <v>674</v>
+        <v>364</v>
       </c>
       <c r="C57">
-        <v>8.65</v>
+        <v>7.12</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>1011.33</v>
+        <v>817.53</v>
       </c>
       <c r="F57">
-        <v>621.97</v>
+        <v>592.68</v>
       </c>
       <c r="G57">
-        <v>635.84</v>
+        <v>581.21</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2952,22 +2952,22 @@
         <v>88</v>
       </c>
       <c r="B58">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C58">
-        <v>8.24</v>
+        <v>6.32</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>920.46</v>
+        <v>879.19</v>
       </c>
       <c r="F58">
-        <v>594.8</v>
+        <v>601.51</v>
       </c>
       <c r="G58">
-        <v>584.86</v>
+        <v>542.24</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2990,22 +2990,22 @@
         <v>89</v>
       </c>
       <c r="B59">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="C59">
-        <v>8.2</v>
+        <v>6.99</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
       </c>
       <c r="E59">
-        <v>903.12</v>
+        <v>777.8</v>
       </c>
       <c r="F59">
-        <v>580.93</v>
+        <v>504.41</v>
       </c>
       <c r="G59">
-        <v>577.92</v>
+        <v>586.38</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -3028,22 +3028,22 @@
         <v>90</v>
       </c>
       <c r="B60">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="C60">
-        <v>8.19</v>
+        <v>6.49</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>897.57</v>
+        <v>754.1</v>
       </c>
       <c r="F60">
-        <v>595.38</v>
+        <v>504.41</v>
       </c>
       <c r="G60">
-        <v>593.87</v>
+        <v>498.74</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -3066,22 +3066,22 @@
         <v>91</v>
       </c>
       <c r="B61">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="C61">
-        <v>8.15</v>
+        <v>7.1</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>868.32</v>
+        <v>752.46</v>
       </c>
       <c r="F61">
-        <v>576.65</v>
+        <v>592.68</v>
       </c>
       <c r="G61">
-        <v>619.65</v>
+        <v>576.67</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -3104,22 +3104,22 @@
         <v>92</v>
       </c>
       <c r="B62">
-        <v>828</v>
+        <v>780</v>
       </c>
       <c r="C62">
-        <v>8.1</v>
+        <v>6.49</v>
       </c>
       <c r="D62">
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>942.54</v>
+        <v>839.47</v>
       </c>
       <c r="F62">
-        <v>596.99</v>
+        <v>530.89</v>
       </c>
       <c r="G62">
-        <v>573.99</v>
+        <v>501.89</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -3142,22 +3142,22 @@
         <v>93</v>
       </c>
       <c r="B63">
-        <v>788</v>
+        <v>503</v>
       </c>
       <c r="C63">
-        <v>8.1</v>
+        <v>6.07</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>897.57</v>
+        <v>780.33</v>
       </c>
       <c r="F63">
-        <v>600</v>
+        <v>500.63</v>
       </c>
       <c r="G63">
-        <v>580.23</v>
+        <v>490.54</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -3180,22 +3180,22 @@
         <v>94</v>
       </c>
       <c r="B64">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C64">
-        <v>7.97</v>
+        <v>4.92</v>
       </c>
       <c r="D64">
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>892.83</v>
+        <v>547.79</v>
       </c>
       <c r="F64">
-        <v>581.27</v>
+        <v>376.04</v>
       </c>
       <c r="G64">
-        <v>609.48</v>
+        <v>385.5</v>
       </c>
       <c r="H64">
         <f>MIN(E64:G64)</f>
@@ -3218,22 +3218,22 @@
         <v>95</v>
       </c>
       <c r="B65">
-        <v>143</v>
+        <v>253</v>
       </c>
       <c r="C65">
-        <v>7.94</v>
+        <v>6.68</v>
       </c>
       <c r="D65">
         <f>C65*$B$3</f>
       </c>
       <c r="E65">
-        <v>884.86</v>
+        <v>771.88</v>
       </c>
       <c r="F65">
-        <v>561.27</v>
+        <v>517.02</v>
       </c>
       <c r="G65">
-        <v>587.05</v>
+        <v>522.07</v>
       </c>
       <c r="H65">
         <f>MIN(E65:G65)</f>
@@ -3256,22 +3256,22 @@
         <v>96</v>
       </c>
       <c r="B66">
-        <v>1379</v>
+        <v>745</v>
       </c>
       <c r="C66">
-        <v>7.79</v>
+        <v>5.86</v>
       </c>
       <c r="D66">
         <f>C66*$B$3</f>
       </c>
       <c r="E66">
-        <v>869.13</v>
+        <v>725.34</v>
       </c>
       <c r="F66">
-        <v>566.47</v>
+        <v>453.97</v>
       </c>
       <c r="G66">
-        <v>574.22</v>
+        <v>471.63</v>
       </c>
       <c r="H66">
         <f>MIN(E66:G66)</f>
@@ -3294,22 +3294,22 @@
         <v>97</v>
       </c>
       <c r="B67">
-        <v>1011</v>
+        <v>560</v>
       </c>
       <c r="C67">
-        <v>7.63</v>
+        <v>6.22</v>
       </c>
       <c r="D67">
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>904.62</v>
+        <v>678.06</v>
       </c>
       <c r="F67">
-        <v>553.18</v>
+        <v>504.41</v>
       </c>
       <c r="G67">
-        <v>541.04</v>
+        <v>485.37</v>
       </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
@@ -3332,22 +3332,22 @@
         <v>98</v>
       </c>
       <c r="B68">
-        <v>821</v>
+        <v>513</v>
       </c>
       <c r="C68">
-        <v>7.57</v>
+        <v>6.15</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
       <c r="E68">
-        <v>914.91</v>
+        <v>750.69</v>
       </c>
       <c r="F68">
-        <v>578.04</v>
+        <v>513.24</v>
       </c>
       <c r="G68">
-        <v>550.29</v>
+        <v>484.24</v>
       </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
@@ -3370,22 +3370,22 @@
         <v>99</v>
       </c>
       <c r="B69">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="C69">
-        <v>7.54</v>
+        <v>6.68</v>
       </c>
       <c r="D69">
         <f>C69*$B$3</f>
       </c>
       <c r="E69">
-        <v>854.91</v>
+        <v>760.02</v>
       </c>
       <c r="F69">
-        <v>582.2</v>
+        <v>479.19</v>
       </c>
       <c r="G69">
-        <v>547.98</v>
+        <v>490.29</v>
       </c>
       <c r="H69">
         <f>MIN(E69:G69)</f>
@@ -3408,22 +3408,22 @@
         <v>100</v>
       </c>
       <c r="B70">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C70">
-        <v>7.11</v>
+        <v>5.89</v>
       </c>
       <c r="D70">
         <f>C70*$B$3</f>
       </c>
       <c r="E70">
-        <v>790.06</v>
+        <v>732.15</v>
       </c>
       <c r="F70">
-        <v>535.84</v>
+        <v>469.36</v>
       </c>
       <c r="G70">
-        <v>519.08</v>
+        <v>434.93</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -3446,22 +3446,22 @@
         <v>101</v>
       </c>
       <c r="B71">
-        <v>1513</v>
+        <v>862</v>
       </c>
       <c r="C71">
-        <v>6.83</v>
+        <v>5.88</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
       </c>
       <c r="E71">
-        <v>724.51</v>
+        <v>768.47</v>
       </c>
       <c r="F71">
-        <v>524.86</v>
+        <v>509.08</v>
       </c>
       <c r="G71">
-        <v>518.84</v>
+        <v>505.42</v>
       </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
@@ -3484,22 +3484,22 @@
         <v>102</v>
       </c>
       <c r="B72">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C72">
-        <v>6.73</v>
+        <v>6.37</v>
       </c>
       <c r="D72">
         <f>C72*$B$3</f>
       </c>
       <c r="E72">
-        <v>844.62</v>
+        <v>774.4</v>
       </c>
       <c r="F72">
-        <v>462.31</v>
+        <v>499.37</v>
       </c>
       <c r="G72">
-        <v>469.83</v>
+        <v>468.98</v>
       </c>
       <c r="H72">
         <f>MIN(E72:G72)</f>
@@ -3522,22 +3522,22 @@
         <v>103</v>
       </c>
       <c r="B73">
-        <v>1138</v>
+        <v>876</v>
       </c>
       <c r="C73">
-        <v>6.48</v>
+        <v>5.24</v>
       </c>
       <c r="D73">
         <f>C73*$B$3</f>
       </c>
       <c r="E73">
-        <v>740.35</v>
+        <v>652.71</v>
       </c>
       <c r="F73">
-        <v>473.99</v>
+        <v>403.53</v>
       </c>
       <c r="G73">
-        <v>460.12</v>
+        <v>413.24</v>
       </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
@@ -3560,22 +3560,22 @@
         <v>104</v>
       </c>
       <c r="B74">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="C74">
-        <v>6.45</v>
+        <v>5.98</v>
       </c>
       <c r="D74">
         <f>C74*$B$3</f>
       </c>
       <c r="E74">
-        <v>748.21</v>
+        <v>624.71</v>
       </c>
       <c r="F74">
-        <v>525.32</v>
+        <v>455.23</v>
       </c>
       <c r="G74">
-        <v>508.67</v>
+        <v>440.1</v>
       </c>
       <c r="H74">
         <f>MIN(E74:G74)</f>
@@ -3598,22 +3598,22 @@
         <v>105</v>
       </c>
       <c r="B75">
-        <v>1017</v>
+        <v>382</v>
       </c>
       <c r="C75">
-        <v>6.44</v>
+        <v>5.23</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
       </c>
       <c r="E75">
-        <v>774.34</v>
+        <v>586.76</v>
       </c>
       <c r="F75">
-        <v>473.99</v>
+        <v>424.71</v>
       </c>
       <c r="G75">
-        <v>464.62</v>
+        <v>411.85</v>
       </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
@@ -3636,22 +3636,22 @@
         <v>106</v>
       </c>
       <c r="B76">
-        <v>588</v>
+        <v>778</v>
       </c>
       <c r="C76">
-        <v>6.33</v>
+        <v>4.46</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
       </c>
       <c r="E76">
-        <v>681.85</v>
+        <v>522.44</v>
       </c>
       <c r="F76">
-        <v>466.82</v>
+        <v>352.96</v>
       </c>
       <c r="G76">
-        <v>471.45</v>
+        <v>359.9</v>
       </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
@@ -3674,22 +3674,22 @@
         <v>107</v>
       </c>
       <c r="B77">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C77">
-        <v>5.96</v>
+        <v>3.99</v>
       </c>
       <c r="D77">
         <f>C77*$B$3</f>
       </c>
       <c r="E77">
-        <v>674.68</v>
+        <v>470.87</v>
       </c>
       <c r="F77">
-        <v>443.93</v>
+        <v>291.68</v>
       </c>
       <c r="G77">
-        <v>445.09</v>
+        <v>301.26</v>
       </c>
       <c r="H77">
         <f>MIN(E77:G77)</f>
@@ -3712,22 +3712,22 @@
         <v>108</v>
       </c>
       <c r="B78">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="C78">
-        <v>5.7</v>
+        <v>4.62</v>
       </c>
       <c r="D78">
         <f>C78*$B$3</f>
       </c>
       <c r="E78">
-        <v>641.5</v>
+        <v>528.37</v>
       </c>
       <c r="F78">
-        <v>431.1</v>
+        <v>416.9</v>
       </c>
       <c r="G78">
-        <v>425.43</v>
+        <v>339.09</v>
       </c>
       <c r="H78">
         <f>MIN(E78:G78)</f>
@@ -3750,22 +3750,22 @@
         <v>109</v>
       </c>
       <c r="B79">
-        <v>101</v>
+        <v>254</v>
       </c>
       <c r="C79">
-        <v>5.69</v>
+        <v>2.96</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
       </c>
       <c r="E79">
-        <v>628.09</v>
+        <v>396.47</v>
       </c>
       <c r="F79">
-        <v>409.83</v>
+        <v>235.69</v>
       </c>
       <c r="G79">
-        <v>432.95</v>
+        <v>232.03</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3788,22 +3788,22 @@
         <v>110</v>
       </c>
       <c r="B80">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="C80">
-        <v>5.68</v>
+        <v>5.04</v>
       </c>
       <c r="D80">
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>630.52</v>
+        <v>526.73</v>
       </c>
       <c r="F80">
-        <v>442.77</v>
+        <v>423.58</v>
       </c>
       <c r="G80">
-        <v>404.62</v>
+        <v>388.02</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3826,22 +3826,22 @@
         <v>111</v>
       </c>
       <c r="B81">
-        <v>203</v>
+        <v>58</v>
       </c>
       <c r="C81">
-        <v>5.6</v>
+        <v>4.72</v>
       </c>
       <c r="D81">
         <f>C81*$B$3</f>
       </c>
       <c r="E81">
-        <v>619.42</v>
+        <v>540.23</v>
       </c>
       <c r="F81">
-        <v>413.76</v>
+        <v>389.66</v>
       </c>
       <c r="G81">
-        <v>402.89</v>
+        <v>388.4</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3864,22 +3864,22 @@
         <v>112</v>
       </c>
       <c r="B82">
-        <v>760</v>
+        <v>502</v>
       </c>
       <c r="C82">
-        <v>5.56</v>
+        <v>5.23</v>
       </c>
       <c r="D82">
         <f>C82*$B$3</f>
       </c>
       <c r="E82">
-        <v>575.95</v>
+        <v>631.52</v>
       </c>
       <c r="F82">
-        <v>413.87</v>
+        <v>446.78</v>
       </c>
       <c r="G82">
-        <v>419.54</v>
+        <v>445.14</v>
       </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
@@ -3902,22 +3902,22 @@
         <v>113</v>
       </c>
       <c r="B83">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="C83">
-        <v>5.54</v>
+        <v>2.7</v>
       </c>
       <c r="D83">
         <f>C83*$B$3</f>
       </c>
       <c r="E83">
-        <v>597.34</v>
+        <v>411.73</v>
       </c>
       <c r="F83">
-        <v>449.48</v>
+        <v>263.81</v>
       </c>
       <c r="G83">
-        <v>402.77</v>
+        <v>211.85</v>
       </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
@@ -3940,22 +3940,22 @@
         <v>115</v>
       </c>
       <c r="B84">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="C84">
-        <v>5.36</v>
+        <v>3.55</v>
       </c>
       <c r="D84">
         <f>C84*$B$3</f>
       </c>
       <c r="E84">
-        <v>620.23</v>
+        <v>486.88</v>
       </c>
       <c r="F84">
-        <v>400.81</v>
+        <v>340.48</v>
       </c>
       <c r="G84">
-        <v>397.69</v>
+        <v>272.13</v>
       </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
@@ -3978,22 +3978,22 @@
         <v>116</v>
       </c>
       <c r="B85">
-        <v>216</v>
+        <v>312</v>
       </c>
       <c r="C85">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="D85">
         <f>C85*$B$3</f>
       </c>
       <c r="E85">
-        <v>626.47</v>
+        <v>400.76</v>
       </c>
       <c r="F85">
-        <v>425.2</v>
+        <v>327.74</v>
       </c>
       <c r="G85">
-        <v>386.13</v>
+        <v>325.35</v>
       </c>
       <c r="H85">
         <f>MIN(E85:G85)</f>
@@ -4016,22 +4016,22 @@
         <v>117</v>
       </c>
       <c r="B86">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="C86">
-        <v>5.19</v>
+        <v>4.93</v>
       </c>
       <c r="D86">
         <f>C86*$B$3</f>
       </c>
       <c r="E86">
-        <v>628.9</v>
+        <v>560.53</v>
       </c>
       <c r="F86">
-        <v>404.62</v>
+        <v>366.58</v>
       </c>
       <c r="G86">
-        <v>412.49</v>
+        <v>361.92</v>
       </c>
       <c r="H86">
         <f>MIN(E86:G86)</f>
@@ -4054,22 +4054,22 @@
         <v>118</v>
       </c>
       <c r="B87">
-        <v>451</v>
+        <v>568</v>
       </c>
       <c r="C87">
-        <v>5.05</v>
+        <v>4.14</v>
       </c>
       <c r="D87">
         <f>C87*$B$3</f>
       </c>
       <c r="E87">
-        <v>606.01</v>
+        <v>502.14</v>
       </c>
       <c r="F87">
-        <v>369.71</v>
+        <v>298.74</v>
       </c>
       <c r="G87">
-        <v>367.63</v>
+        <v>308.95</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -4092,22 +4092,22 @@
         <v>119</v>
       </c>
       <c r="B88">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="C88">
-        <v>5.05</v>
+        <v>4.39</v>
       </c>
       <c r="D88">
         <f>C88*$B$3</f>
       </c>
       <c r="E88">
-        <v>638.38</v>
+        <v>442.12</v>
       </c>
       <c r="F88">
-        <v>381.5</v>
+        <v>347.92</v>
       </c>
       <c r="G88">
-        <v>364.16</v>
+        <v>301.01</v>
       </c>
       <c r="H88">
         <f>MIN(E88:G88)</f>
@@ -4130,22 +4130,22 @@
         <v>120</v>
       </c>
       <c r="B89">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="C89">
-        <v>5.03</v>
+        <v>3.56</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
       </c>
       <c r="E89">
-        <v>575.95</v>
+        <v>462.42</v>
       </c>
       <c r="F89">
-        <v>440.58</v>
+        <v>386.38</v>
       </c>
       <c r="G89">
-        <v>373.3</v>
+        <v>279.95</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -4168,22 +4168,22 @@
         <v>121</v>
       </c>
       <c r="B90">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C90">
-        <v>4.98</v>
+        <v>3</v>
       </c>
       <c r="D90">
         <f>C90*$B$3</f>
       </c>
       <c r="E90">
-        <v>556.19</v>
+        <v>350.82</v>
       </c>
       <c r="F90">
-        <v>378.73</v>
+        <v>233.16</v>
       </c>
       <c r="G90">
-        <v>360.69</v>
+        <v>233.16</v>
       </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
@@ -4206,22 +4206,22 @@
         <v>122</v>
       </c>
       <c r="B91">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C91">
-        <v>4.9</v>
+        <v>5.87</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
       </c>
       <c r="E91">
-        <v>572.83</v>
+        <v>537.7</v>
       </c>
       <c r="F91">
-        <v>381.5</v>
+        <v>368.09</v>
       </c>
       <c r="G91">
-        <v>355.84</v>
+        <v>353.09</v>
       </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
@@ -4244,22 +4244,22 @@
         <v>123</v>
       </c>
       <c r="B92">
-        <v>100</v>
+        <v>243</v>
       </c>
       <c r="C92">
-        <v>4.86</v>
+        <v>4.2</v>
       </c>
       <c r="D92">
         <f>C92*$B$3</f>
       </c>
       <c r="E92">
-        <v>592.6</v>
+        <v>499.62</v>
       </c>
       <c r="F92">
-        <v>363.93</v>
+        <v>333.29</v>
       </c>
       <c r="G92">
-        <v>326.01</v>
+        <v>327.87</v>
       </c>
       <c r="H92">
         <f>MIN(E92:G92)</f>
@@ -4282,22 +4282,22 @@
         <v>124</v>
       </c>
       <c r="B93">
-        <v>614</v>
+        <v>153</v>
       </c>
       <c r="C93">
-        <v>4.64</v>
+        <v>3.87</v>
       </c>
       <c r="D93">
         <f>C93*$B$3</f>
       </c>
       <c r="E93">
-        <v>535.61</v>
+        <v>483.61</v>
       </c>
       <c r="F93">
-        <v>369.71</v>
+        <v>351.83</v>
       </c>
       <c r="G93">
-        <v>346.71</v>
+        <v>339.22</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -4320,22 +4320,22 @@
         <v>125</v>
       </c>
       <c r="B94">
-        <v>595</v>
+        <v>671</v>
       </c>
       <c r="C94">
-        <v>4.59</v>
+        <v>2.92</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>495.38</v>
+        <v>344.89</v>
       </c>
       <c r="F94">
-        <v>339.88</v>
+        <v>226.99</v>
       </c>
       <c r="G94">
-        <v>335.26</v>
+        <v>220.68</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -4358,22 +4358,22 @@
         <v>126</v>
       </c>
       <c r="B95">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C95">
-        <v>4.57</v>
+        <v>3.69</v>
       </c>
       <c r="D95">
         <f>C95*$B$3</f>
       </c>
       <c r="E95">
-        <v>659.65</v>
+        <v>502.14</v>
       </c>
       <c r="F95">
-        <v>344.51</v>
+        <v>317.78</v>
       </c>
       <c r="G95">
-        <v>345.55</v>
+        <v>304.79</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -4396,22 +4396,22 @@
         <v>127</v>
       </c>
       <c r="B96">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="C96">
-        <v>4.57</v>
+        <v>3.92</v>
       </c>
       <c r="D96">
         <f>C96*$B$3</f>
       </c>
       <c r="E96">
-        <v>487.51</v>
+        <v>486.13</v>
       </c>
       <c r="F96">
-        <v>327.98</v>
+        <v>325.98</v>
       </c>
       <c r="G96">
-        <v>330.29</v>
+        <v>350.44</v>
       </c>
       <c r="H96">
         <f>MIN(E96:G96)</f>
@@ -4434,22 +4434,22 @@
         <v>128</v>
       </c>
       <c r="B97">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="C97">
-        <v>4.5</v>
+        <v>3.76</v>
       </c>
       <c r="D97">
         <f>C97*$B$3</f>
       </c>
       <c r="E97">
-        <v>537.23</v>
+        <v>488.65</v>
       </c>
       <c r="F97">
-        <v>392.83</v>
+        <v>290.04</v>
       </c>
       <c r="G97">
-        <v>339.88</v>
+        <v>289.91</v>
       </c>
       <c r="H97">
         <f>MIN(E97:G97)</f>
@@ -4472,22 +4472,22 @@
         <v>129</v>
       </c>
       <c r="B98">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="C98">
-        <v>4.4</v>
+        <v>3.78</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
       </c>
       <c r="E98">
-        <v>479.54</v>
+        <v>399.87</v>
       </c>
       <c r="F98">
-        <v>330.4</v>
+        <v>258.89</v>
       </c>
       <c r="G98">
-        <v>324.28</v>
+        <v>250.82</v>
       </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
@@ -4510,22 +4510,22 @@
         <v>130</v>
       </c>
       <c r="B99">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C99">
-        <v>4.38</v>
+        <v>3.74</v>
       </c>
       <c r="D99">
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>511.21</v>
+        <v>545.27</v>
       </c>
       <c r="F99">
-        <v>354.57</v>
+        <v>301.39</v>
       </c>
       <c r="G99">
-        <v>316.19</v>
+        <v>271</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -4548,22 +4548,22 @@
         <v>131</v>
       </c>
       <c r="B100">
-        <v>2885</v>
+        <v>1025</v>
       </c>
       <c r="C100">
-        <v>4.35</v>
+        <v>3.76</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>464.51</v>
+        <v>421.81</v>
       </c>
       <c r="F100">
-        <v>328.32</v>
+        <v>326.23</v>
       </c>
       <c r="G100">
-        <v>330.64</v>
+        <v>327.87</v>
       </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
@@ -4586,22 +4586,22 @@
         <v>132</v>
       </c>
       <c r="B101">
-        <v>127</v>
+        <v>58</v>
       </c>
       <c r="C101">
-        <v>4.28</v>
+        <v>3.29</v>
       </c>
       <c r="D101">
         <f>C101*$B$3</f>
       </c>
       <c r="E101">
-        <v>558.61</v>
+        <v>459.9</v>
       </c>
       <c r="F101">
-        <v>380</v>
+        <v>276.54</v>
       </c>
       <c r="G101">
-        <v>329.48</v>
+        <v>271.12</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -4624,22 +4624,22 @@
         <v>133</v>
       </c>
       <c r="B102">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C102">
-        <v>4.1</v>
+        <v>10.61</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>438.5</v>
+        <v>420.18</v>
       </c>
       <c r="F102">
-        <v>375.61</v>
+        <v>304.79</v>
       </c>
       <c r="G102">
-        <v>332.95</v>
+        <v>244.51</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -4662,22 +4662,22 @@
         <v>134</v>
       </c>
       <c r="B103">
-        <v>92</v>
+        <v>215</v>
       </c>
       <c r="C103">
-        <v>4.05</v>
+        <v>3.09</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
       </c>
       <c r="E103">
-        <v>448.79</v>
+        <v>354.98</v>
       </c>
       <c r="F103">
-        <v>297.8</v>
+        <v>239.6</v>
       </c>
       <c r="G103">
-        <v>300.58</v>
+        <v>237.7</v>
       </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
@@ -4700,22 +4700,22 @@
         <v>135</v>
       </c>
       <c r="B104">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C104">
-        <v>4.05</v>
+        <v>3.24</v>
       </c>
       <c r="D104">
         <f>C104*$B$3</f>
       </c>
       <c r="E104">
-        <v>449.48</v>
+        <v>380.45</v>
       </c>
       <c r="F104">
-        <v>322.31</v>
+        <v>250.94</v>
       </c>
       <c r="G104">
-        <v>280.23</v>
+        <v>239.22</v>
       </c>
       <c r="H104">
         <f>MIN(E104:G104)</f>
@@ -4738,22 +4738,22 @@
         <v>136</v>
       </c>
       <c r="B105">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C105">
-        <v>3.91</v>
+        <v>3.25</v>
       </c>
       <c r="D105">
         <f>C105*$B$3</f>
       </c>
       <c r="E105">
-        <v>513.53</v>
+        <v>422.7</v>
       </c>
       <c r="F105">
-        <v>312.14</v>
+        <v>258.51</v>
       </c>
       <c r="G105">
-        <v>324.86</v>
+        <v>250.82</v>
       </c>
       <c r="H105">
         <f>MIN(E105:G105)</f>
@@ -4776,22 +4776,22 @@
         <v>137</v>
       </c>
       <c r="B106">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C106">
-        <v>3.91</v>
+        <v>3.21</v>
       </c>
       <c r="D106">
         <f>C106*$B$3</f>
       </c>
       <c r="E106">
-        <v>429.83</v>
+        <v>400.76</v>
       </c>
       <c r="F106">
-        <v>317.57</v>
+        <v>252.21</v>
       </c>
       <c r="G106">
-        <v>300.58</v>
+        <v>236.44</v>
       </c>
       <c r="H106">
         <f>MIN(E106:G106)</f>
@@ -4814,22 +4814,22 @@
         <v>138</v>
       </c>
       <c r="B107">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="C107">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="D107">
         <f>C107*$B$3</f>
       </c>
       <c r="E107">
-        <v>433.76</v>
+        <v>330.52</v>
       </c>
       <c r="F107">
-        <v>304.74</v>
+        <v>252.21</v>
       </c>
       <c r="G107">
-        <v>306.36</v>
+        <v>243.25</v>
       </c>
       <c r="H107">
         <f>MIN(E107:G107)</f>
@@ -4852,22 +4852,22 @@
         <v>139</v>
       </c>
       <c r="B108">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C108">
-        <v>3.7</v>
+        <v>2.77</v>
       </c>
       <c r="D108">
         <f>C108*$B$3</f>
       </c>
       <c r="E108">
-        <v>515.14</v>
+        <v>277.3</v>
       </c>
       <c r="F108">
-        <v>289.02</v>
+        <v>234.43</v>
       </c>
       <c r="G108">
-        <v>265.78</v>
+        <v>223.2</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4890,22 +4890,22 @@
         <v>140</v>
       </c>
       <c r="B109">
-        <v>388</v>
+        <v>337</v>
       </c>
       <c r="C109">
-        <v>3.68</v>
+        <v>2.92</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
       </c>
       <c r="E109">
-        <v>392.6</v>
+        <v>338.08</v>
       </c>
       <c r="F109">
-        <v>287.63</v>
+        <v>240.86</v>
       </c>
       <c r="G109">
-        <v>287.63</v>
+        <v>219.42</v>
       </c>
       <c r="H109">
         <f>MIN(E109:G109)</f>
@@ -4928,22 +4928,22 @@
         <v>141</v>
       </c>
       <c r="B110">
-        <v>421</v>
+        <v>399</v>
       </c>
       <c r="C110">
-        <v>3.64</v>
+        <v>2.7</v>
       </c>
       <c r="D110">
         <f>C110*$B$3</f>
       </c>
       <c r="E110">
-        <v>383.93</v>
+        <v>331.4</v>
       </c>
       <c r="F110">
-        <v>263.35</v>
+        <v>236.06</v>
       </c>
       <c r="G110">
-        <v>264.74</v>
+        <v>219.29</v>
       </c>
       <c r="H110">
         <f>MIN(E110:G110)</f>
@@ -4966,22 +4966,22 @@
         <v>142</v>
       </c>
       <c r="B111">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="C111">
-        <v>3.39</v>
+        <v>2.91</v>
       </c>
       <c r="D111">
         <f>C111*$B$3</f>
       </c>
       <c r="E111">
-        <v>382.31</v>
+        <v>337.33</v>
       </c>
       <c r="F111">
-        <v>252.95</v>
+        <v>221.06</v>
       </c>
       <c r="G111">
-        <v>253.41</v>
+        <v>221.82</v>
       </c>
       <c r="H111">
         <f>MIN(E111:G111)</f>
@@ -5004,22 +5004,22 @@
         <v>143</v>
       </c>
       <c r="B112">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C112">
-        <v>3.34</v>
+        <v>2.44</v>
       </c>
       <c r="D112">
         <f>C112*$B$3</f>
       </c>
       <c r="E112">
-        <v>395.03</v>
+        <v>278.06</v>
       </c>
       <c r="F112">
-        <v>252.95</v>
+        <v>182.72</v>
       </c>
       <c r="G112">
-        <v>250.29</v>
+        <v>194.32</v>
       </c>
       <c r="H112">
         <f>MIN(E112:G112)</f>
@@ -5042,22 +5042,22 @@
         <v>144</v>
       </c>
       <c r="B113">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="C113">
-        <v>3.21</v>
+        <v>2.71</v>
       </c>
       <c r="D113">
         <f>C113*$B$3</f>
       </c>
       <c r="E113">
-        <v>336.53</v>
+        <v>324.59</v>
       </c>
       <c r="F113">
-        <v>244.74</v>
+        <v>235.81</v>
       </c>
       <c r="G113">
-        <v>242.77</v>
+        <v>229.13</v>
       </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
@@ -5080,22 +5080,22 @@
         <v>145</v>
       </c>
       <c r="B114">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="C114">
-        <v>3.19</v>
+        <v>2.7</v>
       </c>
       <c r="D114">
         <f>C114*$B$3</f>
       </c>
       <c r="E114">
-        <v>383.12</v>
+        <v>300.88</v>
       </c>
       <c r="F114">
-        <v>245.09</v>
+        <v>211.35</v>
       </c>
       <c r="G114">
-        <v>235.61</v>
+        <v>218.79</v>
       </c>
       <c r="H114">
         <f>MIN(E114:G114)</f>
@@ -5118,22 +5118,22 @@
         <v>146</v>
       </c>
       <c r="B115">
-        <v>268</v>
+        <v>397</v>
       </c>
       <c r="C115">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="D115">
         <f>C115*$B$3</f>
       </c>
       <c r="E115">
-        <v>382.31</v>
+        <v>357.63</v>
       </c>
       <c r="F115">
-        <v>241.62</v>
+        <v>170.24</v>
       </c>
       <c r="G115">
-        <v>238.84</v>
+        <v>181.59</v>
       </c>
       <c r="H115">
         <f>MIN(E115:G115)</f>
@@ -5156,22 +5156,22 @@
         <v>147</v>
       </c>
       <c r="B116">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C116">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="D116">
         <f>C116*$B$3</f>
       </c>
       <c r="E116">
-        <v>455.03</v>
+        <v>236.7</v>
       </c>
       <c r="F116">
-        <v>269.48</v>
+        <v>182.85</v>
       </c>
       <c r="G116">
-        <v>265.78</v>
+        <v>192.94</v>
       </c>
       <c r="H116">
         <f>MIN(E116:G116)</f>
@@ -5194,22 +5194,22 @@
         <v>148</v>
       </c>
       <c r="B117">
-        <v>328</v>
+        <v>396</v>
       </c>
       <c r="C117">
-        <v>3.03</v>
+        <v>2.26</v>
       </c>
       <c r="D117">
         <f>C117*$B$3</f>
       </c>
       <c r="E117">
-        <v>363.35</v>
+        <v>253.59</v>
       </c>
       <c r="F117">
-        <v>224.28</v>
+        <v>179.44</v>
       </c>
       <c r="G117">
-        <v>223.24</v>
+        <v>167.72</v>
       </c>
       <c r="H117">
         <f>MIN(E117:G117)</f>
@@ -5232,22 +5232,22 @@
         <v>149</v>
       </c>
       <c r="B118">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C118">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="D118">
         <f>C118*$B$3</f>
       </c>
       <c r="E118">
-        <v>376.07</v>
+        <v>312.74</v>
       </c>
       <c r="F118">
-        <v>231.21</v>
+        <v>224.72</v>
       </c>
       <c r="G118">
-        <v>217.57</v>
+        <v>226.61</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -5270,22 +5270,22 @@
         <v>150</v>
       </c>
       <c r="B119">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="C119">
-        <v>2.87</v>
+        <v>2.37</v>
       </c>
       <c r="D119">
         <f>C119*$B$3</f>
       </c>
       <c r="E119">
-        <v>310.52</v>
+        <v>272.13</v>
       </c>
       <c r="F119">
-        <v>215.03</v>
+        <v>205.55</v>
       </c>
       <c r="G119">
-        <v>208.09</v>
+        <v>202.14</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -5308,22 +5308,22 @@
         <v>151</v>
       </c>
       <c r="B120">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="C120">
-        <v>2.83</v>
+        <v>2.21</v>
       </c>
       <c r="D120">
         <f>C120*$B$3</f>
       </c>
       <c r="E120">
-        <v>363.35</v>
+        <v>305.17</v>
       </c>
       <c r="F120">
-        <v>231.1</v>
+        <v>171.63</v>
       </c>
       <c r="G120">
-        <v>218.5</v>
+        <v>165.19</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -5346,22 +5346,22 @@
         <v>152</v>
       </c>
       <c r="B121">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C121">
-        <v>2.82</v>
+        <v>3.03</v>
       </c>
       <c r="D121">
         <f>C121*$B$3</f>
       </c>
       <c r="E121">
-        <v>301.04</v>
+        <v>321.18</v>
       </c>
       <c r="F121">
-        <v>191.79</v>
+        <v>201.76</v>
       </c>
       <c r="G121">
-        <v>195.26</v>
+        <v>201.76</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -5384,22 +5384,22 @@
         <v>153</v>
       </c>
       <c r="B122">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="C122">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="D122">
         <f>C122*$B$3</f>
       </c>
       <c r="E122">
-        <v>290.75</v>
+        <v>242.62</v>
       </c>
       <c r="F122">
-        <v>205.66</v>
+        <v>153.47</v>
       </c>
       <c r="G122">
-        <v>197.8</v>
+        <v>172.76</v>
       </c>
       <c r="H122">
         <f>MIN(E122:G122)</f>
@@ -5422,22 +5422,22 @@
         <v>154</v>
       </c>
       <c r="B123">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C123">
-        <v>2.29</v>
+        <v>1.47</v>
       </c>
       <c r="D123">
         <f>C123*$B$3</f>
       </c>
       <c r="E123">
-        <v>248.09</v>
+        <v>142.87</v>
       </c>
       <c r="F123">
-        <v>179.08</v>
+        <v>131.02</v>
       </c>
       <c r="G123">
-        <v>174.34</v>
+        <v>111.85</v>
       </c>
       <c r="H123">
         <f>MIN(E123:G123)</f>
@@ -5460,22 +5460,22 @@
         <v>155</v>
       </c>
       <c r="B124">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C124">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="D124">
         <f>C124*$B$3</f>
       </c>
       <c r="E124">
-        <v>259.08</v>
+        <v>245.14</v>
       </c>
       <c r="F124">
-        <v>167.51</v>
+        <v>166.46</v>
       </c>
       <c r="G124">
-        <v>159.42</v>
+        <v>162.67</v>
       </c>
       <c r="H124">
         <f>MIN(E124:G124)</f>
@@ -5498,22 +5498,22 @@
         <v>156</v>
       </c>
       <c r="B125">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="C125">
-        <v>2.21</v>
+        <v>1.49</v>
       </c>
       <c r="D125">
         <f>C125*$B$3</f>
       </c>
       <c r="E125">
-        <v>266.24</v>
+        <v>196.97</v>
       </c>
       <c r="F125">
-        <v>172.72</v>
+        <v>143.38</v>
       </c>
       <c r="G125">
-        <v>175.03</v>
+        <v>128.25</v>
       </c>
       <c r="H125">
         <f>MIN(E125:G125)</f>
@@ -5536,22 +5536,22 @@
         <v>157</v>
       </c>
       <c r="B126">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="C126">
-        <v>1.81</v>
+        <v>1.14</v>
       </c>
       <c r="D126">
         <f>C126*$B$3</f>
       </c>
       <c r="E126">
-        <v>196.65</v>
+        <v>140.23</v>
       </c>
       <c r="F126">
-        <v>138.5</v>
+        <v>106.05</v>
       </c>
       <c r="G126">
-        <v>138.61</v>
+        <v>100.88</v>
       </c>
       <c r="H126">
         <f>MIN(E126:G126)</f>
@@ -5574,22 +5574,22 @@
         <v>158</v>
       </c>
       <c r="B127">
-        <v>43</v>
+        <v>182</v>
       </c>
       <c r="C127">
-        <v>1.76</v>
+        <v>1.27</v>
       </c>
       <c r="D127">
         <f>C127*$B$3</f>
       </c>
       <c r="E127">
-        <v>196.65</v>
+        <v>145.4</v>
       </c>
       <c r="F127">
-        <v>125.32</v>
+        <v>111.73</v>
       </c>
       <c r="G127">
-        <v>125.2</v>
+        <v>106.68</v>
       </c>
       <c r="H127">
         <f>MIN(E127:G127)</f>
@@ -5612,22 +5612,22 @@
         <v>159</v>
       </c>
       <c r="B128">
-        <v>255</v>
+        <v>212</v>
       </c>
       <c r="C128">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="D128">
         <f>C128*$B$3</f>
       </c>
       <c r="E128">
-        <v>183.24</v>
+        <v>146.15</v>
       </c>
       <c r="F128">
-        <v>130.64</v>
+        <v>89.91</v>
       </c>
       <c r="G128">
-        <v>124.62</v>
+        <v>89.41</v>
       </c>
       <c r="H128">
         <f>MIN(E128:G128)</f>
@@ -5650,22 +5650,22 @@
         <v>160</v>
       </c>
       <c r="B129">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C129">
-        <v>1.54</v>
+        <v>1</v>
       </c>
       <c r="D129">
         <f>C129*$B$3</f>
       </c>
       <c r="E129">
-        <v>176.88</v>
+        <v>109.84</v>
       </c>
       <c r="F129">
-        <v>119.31</v>
+        <v>81.46</v>
       </c>
       <c r="G129">
-        <v>132.95</v>
+        <v>88.15</v>
       </c>
       <c r="H129">
         <f>MIN(E129:G129)</f>
@@ -5688,22 +5688,22 @@
         <v>161</v>
       </c>
       <c r="B130">
-        <v>316</v>
+        <v>27</v>
       </c>
       <c r="C130">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="D130">
         <f>C130*$B$3</f>
       </c>
       <c r="E130">
-        <v>157.23</v>
+        <v>98.86</v>
       </c>
       <c r="F130">
-        <v>109.48</v>
+        <v>75.03</v>
       </c>
       <c r="G130">
-        <v>115.49</v>
+        <v>74.02</v>
       </c>
       <c r="H130">
         <f>MIN(E130:G130)</f>
@@ -5726,22 +5726,22 @@
         <v>162</v>
       </c>
       <c r="B131">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C131">
-        <v>1.35</v>
+        <v>0.73</v>
       </c>
       <c r="D131">
         <f>C131*$B$3</f>
       </c>
       <c r="E131">
-        <v>172.14</v>
+        <v>92.94</v>
       </c>
       <c r="F131">
-        <v>101.85</v>
+        <v>64.31</v>
       </c>
       <c r="G131">
-        <v>102.31</v>
+        <v>61.41</v>
       </c>
       <c r="H131">
         <f>MIN(E131:G131)</f>
@@ -5764,22 +5764,22 @@
         <v>163</v>
       </c>
       <c r="B132">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="C132">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="D132">
         <f>C132*$B$3</f>
       </c>
       <c r="E132">
-        <v>149.25</v>
+        <v>114.12</v>
       </c>
       <c r="F132">
-        <v>99.31</v>
+        <v>75.54</v>
       </c>
       <c r="G132">
-        <v>101.39</v>
+        <v>81.71</v>
       </c>
       <c r="H132">
         <f>MIN(E132:G132)</f>
@@ -5802,22 +5802,22 @@
         <v>164</v>
       </c>
       <c r="B133">
-        <v>603</v>
+        <v>682</v>
       </c>
       <c r="C133">
-        <v>0.93</v>
+        <v>0.55</v>
       </c>
       <c r="D133">
         <f>C133*$B$3</f>
       </c>
       <c r="E133">
-        <v>110.52</v>
+        <v>65.07</v>
       </c>
       <c r="F133">
-        <v>71.91</v>
+        <v>44.01</v>
       </c>
       <c r="G133">
-        <v>71.1</v>
+        <v>46.53</v>
       </c>
       <c r="H133">
         <f>MIN(E133:G133)</f>
@@ -5840,22 +5840,22 @@
         <v>165</v>
       </c>
       <c r="B134">
-        <v>344</v>
+        <v>219</v>
       </c>
       <c r="C134">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="D134">
         <f>C134*$B$3</f>
       </c>
       <c r="E134">
-        <v>93.18</v>
+        <v>83.61</v>
       </c>
       <c r="F134">
-        <v>60.81</v>
+        <v>52.08</v>
       </c>
       <c r="G134">
-        <v>64.16</v>
+        <v>50.06</v>
       </c>
       <c r="H134">
         <f>MIN(E134:G134)</f>
@@ -5878,22 +5878,22 @@
         <v>166</v>
       </c>
       <c r="B135">
-        <v>345</v>
+        <v>289</v>
       </c>
       <c r="C135">
-        <v>0.64</v>
+        <v>0.41</v>
       </c>
       <c r="D135">
         <f>C135*$B$3</f>
       </c>
       <c r="E135">
-        <v>81.27</v>
+        <v>53.22</v>
       </c>
       <c r="F135">
-        <v>43.01</v>
+        <v>34.05</v>
       </c>
       <c r="G135">
-        <v>46.13</v>
+        <v>40.73</v>
       </c>
       <c r="H135">
         <f>MIN(E135:G135)</f>
@@ -5916,22 +5916,22 @@
         <v>167</v>
       </c>
       <c r="B136">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="C136">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="D136">
         <f>C136*$B$3</f>
       </c>
       <c r="E136">
-        <v>60.81</v>
+        <v>51.45</v>
       </c>
       <c r="F136">
-        <v>34.68</v>
+        <v>30.52</v>
       </c>
       <c r="G136">
-        <v>34.34</v>
+        <v>30.52</v>
       </c>
       <c r="H136">
         <f>MIN(E136:G136)</f>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="168">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 21.09.2026 11:32</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 21.09.2026 13:34</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -1014,10 +1014,10 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C7">
-        <v>66.54</v>
+        <v>66.15</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
@@ -1026,10 +1026,10 @@
         <v>7778.41</v>
       </c>
       <c r="F7">
-        <v>5220.66</v>
+        <v>5208.05</v>
       </c>
       <c r="G7">
-        <v>5220.66</v>
+        <v>5214.36</v>
       </c>
       <c r="H7">
         <f>MIN(E7:G7)</f>
@@ -1055,7 +1055,7 @@
         <v>30</v>
       </c>
       <c r="C8">
-        <v>73.29</v>
+        <v>74.66</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
@@ -1064,7 +1064,7 @@
         <v>8705.02</v>
       </c>
       <c r="F8">
-        <v>5824.82</v>
+        <v>6987.37</v>
       </c>
       <c r="G8">
         <v>5749.16</v>
@@ -1090,22 +1090,22 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C9">
-        <v>53.16</v>
+        <v>53.08</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
       </c>
       <c r="E9">
-        <v>6203.26</v>
+        <v>6154.2</v>
       </c>
       <c r="F9">
         <v>4287.5</v>
       </c>
       <c r="G9">
-        <v>4161.4</v>
+        <v>4192.92</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -1128,10 +1128,10 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C10">
-        <v>47.89</v>
+        <v>48.32</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
@@ -1140,7 +1140,7 @@
         <v>5505.78</v>
       </c>
       <c r="F10">
-        <v>3751.56</v>
+        <v>3745.26</v>
       </c>
       <c r="G10">
         <v>3801.88</v>
@@ -1166,10 +1166,10 @@
         <v>29</v>
       </c>
       <c r="B11">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C11">
-        <v>43.78</v>
+        <v>43.57</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
@@ -1181,7 +1181,7 @@
         <v>3503.77</v>
       </c>
       <c r="G11">
-        <v>3450.18</v>
+        <v>3417.39</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -1207,19 +1207,19 @@
         <v>329</v>
       </c>
       <c r="C12">
-        <v>42.95</v>
+        <v>43.24</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
       </c>
       <c r="E12">
-        <v>5013.6</v>
+        <v>5008.56</v>
       </c>
       <c r="F12">
-        <v>3417.39</v>
+        <v>3411.09</v>
       </c>
       <c r="G12">
-        <v>3467.83</v>
+        <v>3455.22</v>
       </c>
       <c r="H12">
         <f>MIN(E12:G12)</f>
@@ -1242,10 +1242,10 @@
         <v>31</v>
       </c>
       <c r="B13">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C13">
-        <v>50</v>
+        <v>49.93</v>
       </c>
       <c r="D13">
         <f>C13*$B$3</f>
@@ -1254,10 +1254,10 @@
         <v>5767.83</v>
       </c>
       <c r="F13">
-        <v>3959.63</v>
+        <v>3991.16</v>
       </c>
       <c r="G13">
-        <v>3921.8</v>
+        <v>3915.5</v>
       </c>
       <c r="H13">
         <f>MIN(E13:G13)</f>
@@ -1280,10 +1280,10 @@
         <v>32</v>
       </c>
       <c r="B14">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C14">
-        <v>47</v>
+        <v>47.08</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
@@ -1292,10 +1292,10 @@
         <v>5114.23</v>
       </c>
       <c r="F14">
-        <v>3820.92</v>
+        <v>3789.4</v>
       </c>
       <c r="G14">
-        <v>3773</v>
+        <v>3763.8</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1318,7 +1318,7 @@
         <v>33</v>
       </c>
       <c r="B15">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C15">
         <v>49.42</v>
@@ -1330,7 +1330,7 @@
         <v>5819.4</v>
       </c>
       <c r="F15">
-        <v>3902.76</v>
+        <v>3871.36</v>
       </c>
       <c r="G15">
         <v>4054.21</v>
@@ -1356,16 +1356,16 @@
         <v>34</v>
       </c>
       <c r="B16">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C16">
-        <v>43.36</v>
+        <v>43.04</v>
       </c>
       <c r="D16">
         <f>C16*$B$3</f>
       </c>
       <c r="E16">
-        <v>4956.1</v>
+        <v>5187.88</v>
       </c>
       <c r="F16">
         <v>3606.29</v>
@@ -1394,10 +1394,10 @@
         <v>35</v>
       </c>
       <c r="B17">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C17">
-        <v>38.39</v>
+        <v>37.78</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
@@ -1435,7 +1435,7 @@
         <v>67</v>
       </c>
       <c r="C18">
-        <v>45.76</v>
+        <v>45.47</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
@@ -1444,10 +1444,10 @@
         <v>4921.55</v>
       </c>
       <c r="F18">
-        <v>3773</v>
+        <v>3770.48</v>
       </c>
       <c r="G18">
-        <v>3737.69</v>
+        <v>3735.17</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1470,10 +1470,10 @@
         <v>37</v>
       </c>
       <c r="B19">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19">
-        <v>41.91</v>
+        <v>42.84</v>
       </c>
       <c r="D19">
         <f>C19*$B$3</f>
@@ -1482,10 +1482,10 @@
         <v>5727.22</v>
       </c>
       <c r="F19">
-        <v>3272.25</v>
+        <v>3526.6</v>
       </c>
       <c r="G19">
-        <v>3353.08</v>
+        <v>3360.27</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1517,13 +1517,13 @@
         <f>C20*$B$3</f>
       </c>
       <c r="E20">
-        <v>3720.04</v>
+        <v>3753.83</v>
       </c>
       <c r="F20">
         <v>2336.18</v>
       </c>
       <c r="G20">
-        <v>2320.17</v>
+        <v>2332.91</v>
       </c>
       <c r="H20">
         <f>MIN(E20:G20)</f>
@@ -1549,7 +1549,7 @@
         <v>118</v>
       </c>
       <c r="C21">
-        <v>28.12</v>
+        <v>27.84</v>
       </c>
       <c r="D21">
         <f>C21*$B$3</f>
@@ -1558,7 +1558,7 @@
         <v>3297.34</v>
       </c>
       <c r="F21">
-        <v>2456.36</v>
+        <v>2455.23</v>
       </c>
       <c r="G21">
         <v>2248.42</v>
@@ -1596,7 +1596,7 @@
         <v>3840.97</v>
       </c>
       <c r="F22">
-        <v>2711.21</v>
+        <v>2698.6</v>
       </c>
       <c r="G22">
         <v>2815.63</v>
@@ -1622,7 +1622,7 @@
         <v>41</v>
       </c>
       <c r="B23">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="C23">
         <v>23.95</v>
@@ -1698,7 +1698,7 @@
         <v>46</v>
       </c>
       <c r="B25">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C25">
         <v>25.6</v>
@@ -1736,7 +1736,7 @@
         <v>47</v>
       </c>
       <c r="B26">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C26">
         <v>17.5</v>
@@ -1748,7 +1748,7 @@
         <v>1960.65</v>
       </c>
       <c r="F26">
-        <v>1387.13</v>
+        <v>1380.83</v>
       </c>
       <c r="G26">
         <v>1372</v>
@@ -1774,7 +1774,7 @@
         <v>48</v>
       </c>
       <c r="B27">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C27">
         <v>17.41</v>
@@ -1786,7 +1786,7 @@
         <v>1944.51</v>
       </c>
       <c r="F27">
-        <v>1380.45</v>
+        <v>1360.65</v>
       </c>
       <c r="G27">
         <v>1412.35</v>
@@ -1812,22 +1812,22 @@
         <v>49</v>
       </c>
       <c r="B28">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C28">
-        <v>18.87</v>
+        <v>18.88</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
       </c>
       <c r="E28">
-        <v>2306.42</v>
+        <v>2155.1</v>
       </c>
       <c r="F28">
-        <v>1594.95</v>
+        <v>1563.68</v>
       </c>
       <c r="G28">
-        <v>1525.85</v>
+        <v>1519.54</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1850,10 +1850,10 @@
         <v>52</v>
       </c>
       <c r="B29">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C29">
-        <v>20.67</v>
+        <v>19.75</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
@@ -1862,10 +1862,10 @@
         <v>2169.48</v>
       </c>
       <c r="F29">
-        <v>1513.24</v>
+        <v>1500.63</v>
       </c>
       <c r="G29">
-        <v>1475.41</v>
+        <v>1469.1</v>
       </c>
       <c r="H29">
         <f>MIN(E29:G29)</f>
@@ -1897,13 +1897,13 @@
         <f>C30*$B$3</f>
       </c>
       <c r="E30">
-        <v>1876.92</v>
+        <v>1925.09</v>
       </c>
       <c r="F30">
         <v>1336.69</v>
       </c>
       <c r="G30">
-        <v>1349.3</v>
+        <v>1343</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1926,10 +1926,10 @@
         <v>54</v>
       </c>
       <c r="B31">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C31">
-        <v>17.6</v>
+        <v>17.52</v>
       </c>
       <c r="D31">
         <f>C31*$B$3</f>
@@ -1964,19 +1964,19 @@
         <v>55</v>
       </c>
       <c r="B32">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="C32">
-        <v>15.59</v>
+        <v>15.3</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>1886.25</v>
+        <v>1874.39</v>
       </c>
       <c r="F32">
-        <v>1286.12</v>
+        <v>1288.77</v>
       </c>
       <c r="G32">
         <v>1255.99</v>
@@ -2002,7 +2002,7 @@
         <v>56</v>
       </c>
       <c r="B33">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C33">
         <v>13.75</v>
@@ -2014,10 +2014,10 @@
         <v>1645.27</v>
       </c>
       <c r="F33">
-        <v>1071.88</v>
+        <v>1109.71</v>
       </c>
       <c r="G33">
-        <v>1103.4</v>
+        <v>1102.14</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -2040,10 +2040,10 @@
         <v>57</v>
       </c>
       <c r="B34">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C34">
-        <v>15.68</v>
+        <v>15.82</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
@@ -2052,10 +2052,10 @@
         <v>1804.16</v>
       </c>
       <c r="F34">
-        <v>1197.98</v>
+        <v>1197.85</v>
       </c>
       <c r="G34">
-        <v>1242.11</v>
+        <v>1223.2</v>
       </c>
       <c r="H34">
         <f>MIN(E34:G34)</f>
@@ -2078,10 +2078,10 @@
         <v>58</v>
       </c>
       <c r="B35">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C35">
-        <v>14.9</v>
+        <v>15.05</v>
       </c>
       <c r="D35">
         <f>C35*$B$3</f>
@@ -2093,7 +2093,7 @@
         <v>1197.85</v>
       </c>
       <c r="G35">
-        <v>1182.85</v>
+        <v>1181.84</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -2119,19 +2119,19 @@
         <v>53</v>
       </c>
       <c r="C36">
-        <v>7.23</v>
+        <v>7.29</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
       </c>
       <c r="E36">
-        <v>839.47</v>
+        <v>809.96</v>
       </c>
       <c r="F36">
-        <v>624.08</v>
+        <v>620.43</v>
       </c>
       <c r="G36">
-        <v>716.27</v>
+        <v>643.13</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -2166,7 +2166,7 @@
         <v>1066.96</v>
       </c>
       <c r="F37">
-        <v>944.13</v>
+        <v>944.26</v>
       </c>
       <c r="G37">
         <v>859.52</v>
@@ -2192,10 +2192,10 @@
         <v>62</v>
       </c>
       <c r="B38">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C38">
-        <v>11.91</v>
+        <v>11.79</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
@@ -2204,7 +2204,7 @@
         <v>1404.28</v>
       </c>
       <c r="F38">
-        <v>886</v>
+        <v>856.24</v>
       </c>
       <c r="G38">
         <v>983.6</v>
@@ -2230,10 +2230,10 @@
         <v>63</v>
       </c>
       <c r="B39">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C39">
-        <v>10.42</v>
+        <v>10.4</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
@@ -2268,10 +2268,10 @@
         <v>64</v>
       </c>
       <c r="B40">
-        <v>899</v>
+        <v>916</v>
       </c>
       <c r="C40">
-        <v>9.94</v>
+        <v>9.96</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
@@ -2280,10 +2280,10 @@
         <v>1150.69</v>
       </c>
       <c r="F40">
-        <v>793.19</v>
+        <v>795.84</v>
       </c>
       <c r="G40">
-        <v>787.26</v>
+        <v>781.84</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -2344,22 +2344,22 @@
         <v>68</v>
       </c>
       <c r="B42">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C42">
-        <v>10.01</v>
+        <v>10.16</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
       </c>
       <c r="E42">
-        <v>1187.01</v>
+        <v>1188.65</v>
       </c>
       <c r="F42">
-        <v>832.28</v>
+        <v>824.71</v>
       </c>
       <c r="G42">
-        <v>807.06</v>
+        <v>812.1</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2382,10 +2382,10 @@
         <v>69</v>
       </c>
       <c r="B43">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C43">
-        <v>8.83</v>
+        <v>8.82</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
@@ -2394,10 +2394,10 @@
         <v>930.01</v>
       </c>
       <c r="F43">
-        <v>744.01</v>
+        <v>718.79</v>
       </c>
       <c r="G43">
-        <v>717.53</v>
+        <v>716.9</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2461,7 +2461,7 @@
         <v>145</v>
       </c>
       <c r="C45">
-        <v>7.17</v>
+        <v>7.25</v>
       </c>
       <c r="D45">
         <f>C45*$B$3</f>
@@ -2470,10 +2470,10 @@
         <v>940.98</v>
       </c>
       <c r="F45">
-        <v>612.73</v>
+        <v>605.04</v>
       </c>
       <c r="G45">
-        <v>576.16</v>
+        <v>574.9</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2496,22 +2496,22 @@
         <v>74</v>
       </c>
       <c r="B46">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="C46">
-        <v>9.1</v>
+        <v>9.52</v>
       </c>
       <c r="D46">
         <f>C46*$B$3</f>
       </c>
       <c r="E46">
-        <v>1076.29</v>
+        <v>1066.96</v>
       </c>
       <c r="F46">
-        <v>737.7</v>
+        <v>736.44</v>
       </c>
       <c r="G46">
-        <v>718.79</v>
+        <v>725.09</v>
       </c>
       <c r="H46">
         <f>MIN(E46:G46)</f>
@@ -2534,10 +2534,10 @@
         <v>75</v>
       </c>
       <c r="B47">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C47">
-        <v>10.54</v>
+        <v>10.55</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
@@ -2546,10 +2546,10 @@
         <v>1161.66</v>
       </c>
       <c r="F47">
-        <v>907.94</v>
+        <v>907.82</v>
       </c>
       <c r="G47">
-        <v>926.23</v>
+        <v>925.34</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2572,7 +2572,7 @@
         <v>76</v>
       </c>
       <c r="B48">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C48">
         <v>8.55</v>
@@ -2610,22 +2610,22 @@
         <v>77</v>
       </c>
       <c r="B49">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C49">
-        <v>7.7</v>
+        <v>7.83</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>947.66</v>
+        <v>945.14</v>
       </c>
       <c r="F49">
-        <v>636.82</v>
+        <v>640.48</v>
       </c>
       <c r="G49">
-        <v>621.18</v>
+        <v>623.71</v>
       </c>
       <c r="H49">
         <f>MIN(E49:G49)</f>
@@ -2648,10 +2648,10 @@
         <v>79</v>
       </c>
       <c r="B50">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50">
-        <v>7.71</v>
+        <v>8</v>
       </c>
       <c r="D50">
         <f>C50*$B$3</f>
@@ -2686,10 +2686,10 @@
         <v>80</v>
       </c>
       <c r="B51">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C51">
-        <v>9.4</v>
+        <v>9.84</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
@@ -2701,7 +2701,7 @@
         <v>817.02</v>
       </c>
       <c r="G51">
-        <v>806.3</v>
+        <v>805.55</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2724,10 +2724,10 @@
         <v>81</v>
       </c>
       <c r="B52">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C52">
-        <v>7.8</v>
+        <v>7.79</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
@@ -2736,7 +2736,7 @@
         <v>888.52</v>
       </c>
       <c r="F52">
-        <v>630.52</v>
+        <v>627.99</v>
       </c>
       <c r="G52">
         <v>622.32</v>
@@ -2762,22 +2762,22 @@
         <v>82</v>
       </c>
       <c r="B53">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="C53">
-        <v>7.79</v>
+        <v>8.17</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>968.85</v>
+        <v>930.77</v>
       </c>
       <c r="F53">
-        <v>668.35</v>
+        <v>640.6</v>
       </c>
       <c r="G53">
-        <v>630.52</v>
+        <v>629.25</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2800,10 +2800,10 @@
         <v>84</v>
       </c>
       <c r="B54">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C54">
-        <v>5.63</v>
+        <v>5.34</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
@@ -2812,10 +2812,10 @@
         <v>608.7</v>
       </c>
       <c r="F54">
-        <v>432.41</v>
+        <v>431.15</v>
       </c>
       <c r="G54">
-        <v>438.84</v>
+        <v>435.06</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2838,22 +2838,22 @@
         <v>85</v>
       </c>
       <c r="B55">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C55">
-        <v>7.5</v>
+        <v>7.38</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>905.42</v>
+        <v>920.68</v>
       </c>
       <c r="F55">
-        <v>567.46</v>
+        <v>587.14</v>
       </c>
       <c r="G55">
-        <v>567.46</v>
+        <v>576.04</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2876,10 +2876,10 @@
         <v>86</v>
       </c>
       <c r="B56">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C56">
-        <v>7.33</v>
+        <v>7.29</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
@@ -2888,7 +2888,7 @@
         <v>836.06</v>
       </c>
       <c r="F56">
-        <v>704.79</v>
+        <v>704.66</v>
       </c>
       <c r="G56">
         <v>686.38</v>
@@ -2914,22 +2914,22 @@
         <v>87</v>
       </c>
       <c r="B57">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C57">
-        <v>7.12</v>
+        <v>7.06</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>817.53</v>
+        <v>777.8</v>
       </c>
       <c r="F57">
-        <v>592.68</v>
+        <v>590.79</v>
       </c>
       <c r="G57">
-        <v>581.21</v>
+        <v>579.95</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2964,7 +2964,7 @@
         <v>879.19</v>
       </c>
       <c r="F58">
-        <v>601.51</v>
+        <v>598.99</v>
       </c>
       <c r="G58">
         <v>542.24</v>
@@ -2993,7 +2993,7 @@
         <v>83</v>
       </c>
       <c r="C59">
-        <v>6.99</v>
+        <v>6.83</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
@@ -3002,10 +3002,10 @@
         <v>777.8</v>
       </c>
       <c r="F59">
-        <v>504.41</v>
+        <v>499.37</v>
       </c>
       <c r="G59">
-        <v>586.38</v>
+        <v>585.12</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -3028,10 +3028,10 @@
         <v>90</v>
       </c>
       <c r="B60">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C60">
-        <v>6.49</v>
+        <v>6.5</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
@@ -3040,7 +3040,7 @@
         <v>754.1</v>
       </c>
       <c r="F60">
-        <v>504.41</v>
+        <v>501.89</v>
       </c>
       <c r="G60">
         <v>498.74</v>
@@ -3066,10 +3066,10 @@
         <v>91</v>
       </c>
       <c r="B61">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C61">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
@@ -3078,7 +3078,7 @@
         <v>752.46</v>
       </c>
       <c r="F61">
-        <v>592.68</v>
+        <v>605.29</v>
       </c>
       <c r="G61">
         <v>576.67</v>
@@ -3104,7 +3104,7 @@
         <v>92</v>
       </c>
       <c r="B62">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C62">
         <v>6.49</v>
@@ -3113,13 +3113,13 @@
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>839.47</v>
+        <v>875.03</v>
       </c>
       <c r="F62">
-        <v>530.89</v>
+        <v>533.29</v>
       </c>
       <c r="G62">
-        <v>501.89</v>
+        <v>511.98</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -3142,22 +3142,22 @@
         <v>93</v>
       </c>
       <c r="B63">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C63">
-        <v>6.07</v>
+        <v>6.06</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>780.33</v>
+        <v>775.28</v>
       </c>
       <c r="F63">
-        <v>500.63</v>
+        <v>498.11</v>
       </c>
       <c r="G63">
-        <v>490.54</v>
+        <v>479.19</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -3183,7 +3183,7 @@
         <v>133</v>
       </c>
       <c r="C64">
-        <v>4.92</v>
+        <v>4.82</v>
       </c>
       <c r="D64">
         <f>C64*$B$3</f>
@@ -3192,10 +3192,10 @@
         <v>547.79</v>
       </c>
       <c r="F64">
-        <v>376.04</v>
+        <v>373.52</v>
       </c>
       <c r="G64">
-        <v>385.5</v>
+        <v>385.37</v>
       </c>
       <c r="H64">
         <f>MIN(E64:G64)</f>
@@ -3218,7 +3218,7 @@
         <v>95</v>
       </c>
       <c r="B65">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C65">
         <v>6.68</v>
@@ -3227,7 +3227,7 @@
         <f>C65*$B$3</f>
       </c>
       <c r="E65">
-        <v>771.88</v>
+        <v>763.43</v>
       </c>
       <c r="F65">
         <v>517.02</v>
@@ -3256,22 +3256,22 @@
         <v>96</v>
       </c>
       <c r="B66">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="C66">
-        <v>5.86</v>
+        <v>5.87</v>
       </c>
       <c r="D66">
         <f>C66*$B$3</f>
       </c>
       <c r="E66">
-        <v>725.34</v>
+        <v>707.56</v>
       </c>
       <c r="F66">
-        <v>453.97</v>
+        <v>491.8</v>
       </c>
       <c r="G66">
-        <v>471.63</v>
+        <v>474.15</v>
       </c>
       <c r="H66">
         <f>MIN(E66:G66)</f>
@@ -3294,22 +3294,22 @@
         <v>97</v>
       </c>
       <c r="B67">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C67">
-        <v>6.22</v>
+        <v>5.9</v>
       </c>
       <c r="D67">
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>678.06</v>
+        <v>680.58</v>
       </c>
       <c r="F67">
-        <v>504.41</v>
+        <v>504.29</v>
       </c>
       <c r="G67">
-        <v>485.37</v>
+        <v>484.11</v>
       </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
@@ -3335,16 +3335,16 @@
         <v>513</v>
       </c>
       <c r="C68">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
       <c r="E68">
-        <v>750.69</v>
+        <v>651.83</v>
       </c>
       <c r="F68">
-        <v>513.24</v>
+        <v>504.29</v>
       </c>
       <c r="G68">
         <v>484.24</v>
@@ -3382,7 +3382,7 @@
         <v>760.02</v>
       </c>
       <c r="F69">
-        <v>479.19</v>
+        <v>487.89</v>
       </c>
       <c r="G69">
         <v>490.29</v>
@@ -3411,7 +3411,7 @@
         <v>123</v>
       </c>
       <c r="C70">
-        <v>5.89</v>
+        <v>5.87</v>
       </c>
       <c r="D70">
         <f>C70*$B$3</f>
@@ -3420,10 +3420,10 @@
         <v>732.15</v>
       </c>
       <c r="F70">
-        <v>469.36</v>
+        <v>469.1</v>
       </c>
       <c r="G70">
-        <v>434.93</v>
+        <v>434.05</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -3446,22 +3446,22 @@
         <v>101</v>
       </c>
       <c r="B71">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="C71">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
       </c>
       <c r="E71">
-        <v>768.47</v>
+        <v>687.26</v>
       </c>
       <c r="F71">
-        <v>509.08</v>
+        <v>509.46</v>
       </c>
       <c r="G71">
-        <v>505.42</v>
+        <v>506.93</v>
       </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
@@ -3522,22 +3522,22 @@
         <v>103</v>
       </c>
       <c r="B73">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C73">
-        <v>5.24</v>
+        <v>5.02</v>
       </c>
       <c r="D73">
         <f>C73*$B$3</f>
       </c>
       <c r="E73">
-        <v>652.71</v>
+        <v>641.61</v>
       </c>
       <c r="F73">
-        <v>403.53</v>
+        <v>413.62</v>
       </c>
       <c r="G73">
-        <v>413.24</v>
+        <v>414.25</v>
       </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
@@ -3572,7 +3572,7 @@
         <v>624.71</v>
       </c>
       <c r="F74">
-        <v>455.23</v>
+        <v>450.19</v>
       </c>
       <c r="G74">
         <v>440.1</v>
@@ -3598,22 +3598,22 @@
         <v>105</v>
       </c>
       <c r="B75">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C75">
-        <v>5.23</v>
+        <v>5.11</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
       </c>
       <c r="E75">
-        <v>586.76</v>
+        <v>623.07</v>
       </c>
       <c r="F75">
-        <v>424.71</v>
+        <v>421.18</v>
       </c>
       <c r="G75">
-        <v>411.85</v>
+        <v>412.1</v>
       </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
@@ -3636,10 +3636,10 @@
         <v>106</v>
       </c>
       <c r="B76">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C76">
-        <v>4.46</v>
+        <v>4.38</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
@@ -3648,10 +3648,10 @@
         <v>522.44</v>
       </c>
       <c r="F76">
-        <v>352.96</v>
+        <v>351.83</v>
       </c>
       <c r="G76">
-        <v>359.9</v>
+        <v>358.64</v>
       </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
@@ -3686,10 +3686,10 @@
         <v>470.87</v>
       </c>
       <c r="F77">
-        <v>291.68</v>
+        <v>291.55</v>
       </c>
       <c r="G77">
-        <v>301.26</v>
+        <v>300</v>
       </c>
       <c r="H77">
         <f>MIN(E77:G77)</f>
@@ -3712,10 +3712,10 @@
         <v>108</v>
       </c>
       <c r="B78">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C78">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="D78">
         <f>C78*$B$3</f>
@@ -3724,10 +3724,10 @@
         <v>528.37</v>
       </c>
       <c r="F78">
-        <v>416.9</v>
+        <v>403.53</v>
       </c>
       <c r="G78">
-        <v>339.09</v>
+        <v>336.57</v>
       </c>
       <c r="H78">
         <f>MIN(E78:G78)</f>
@@ -3750,10 +3750,10 @@
         <v>109</v>
       </c>
       <c r="B79">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C79">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
@@ -3762,7 +3762,7 @@
         <v>396.47</v>
       </c>
       <c r="F79">
-        <v>235.69</v>
+        <v>234.43</v>
       </c>
       <c r="G79">
         <v>232.03</v>
@@ -3788,7 +3788,7 @@
         <v>110</v>
       </c>
       <c r="B80">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>5.04</v>
@@ -3797,7 +3797,7 @@
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>526.73</v>
+        <v>525.85</v>
       </c>
       <c r="F80">
         <v>423.58</v>
@@ -3826,7 +3826,7 @@
         <v>111</v>
       </c>
       <c r="B81">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C81">
         <v>4.72</v>
@@ -3838,10 +3838,10 @@
         <v>540.23</v>
       </c>
       <c r="F81">
-        <v>389.66</v>
+        <v>384.61</v>
       </c>
       <c r="G81">
-        <v>388.4</v>
+        <v>387.14</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3864,22 +3864,22 @@
         <v>112</v>
       </c>
       <c r="B82">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C82">
-        <v>5.23</v>
+        <v>5.27</v>
       </c>
       <c r="D82">
         <f>C82*$B$3</f>
       </c>
       <c r="E82">
-        <v>631.52</v>
+        <v>625.6</v>
       </c>
       <c r="F82">
-        <v>446.78</v>
+        <v>445.4</v>
       </c>
       <c r="G82">
-        <v>445.14</v>
+        <v>441.36</v>
       </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
@@ -3902,10 +3902,10 @@
         <v>113</v>
       </c>
       <c r="B83">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C83">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="D83">
         <f>C83*$B$3</f>
@@ -3914,10 +3914,10 @@
         <v>411.73</v>
       </c>
       <c r="F83">
-        <v>263.81</v>
+        <v>263.68</v>
       </c>
       <c r="G83">
-        <v>211.85</v>
+        <v>201.64</v>
       </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
@@ -3940,7 +3940,7 @@
         <v>115</v>
       </c>
       <c r="B84">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C84">
         <v>3.55</v>
@@ -3949,13 +3949,13 @@
         <f>C84*$B$3</f>
       </c>
       <c r="E84">
-        <v>486.88</v>
+        <v>475.91</v>
       </c>
       <c r="F84">
-        <v>340.48</v>
+        <v>335.43</v>
       </c>
       <c r="G84">
-        <v>272.13</v>
+        <v>277.43</v>
       </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
@@ -3990,7 +3990,7 @@
         <v>400.76</v>
       </c>
       <c r="F85">
-        <v>327.74</v>
+        <v>326.48</v>
       </c>
       <c r="G85">
         <v>325.35</v>
@@ -4016,10 +4016,10 @@
         <v>117</v>
       </c>
       <c r="B86">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C86">
-        <v>4.93</v>
+        <v>4.92</v>
       </c>
       <c r="D86">
         <f>C86*$B$3</f>
@@ -4028,7 +4028,7 @@
         <v>560.53</v>
       </c>
       <c r="F86">
-        <v>366.58</v>
+        <v>365.32</v>
       </c>
       <c r="G86">
         <v>361.92</v>
@@ -4069,7 +4069,7 @@
         <v>298.74</v>
       </c>
       <c r="G87">
-        <v>308.95</v>
+        <v>298.86</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -4130,10 +4130,10 @@
         <v>120</v>
       </c>
       <c r="B89">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C89">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
@@ -4142,10 +4142,10 @@
         <v>462.42</v>
       </c>
       <c r="F89">
-        <v>386.38</v>
+        <v>416.14</v>
       </c>
       <c r="G89">
-        <v>279.95</v>
+        <v>277.43</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -4180,10 +4180,10 @@
         <v>350.82</v>
       </c>
       <c r="F90">
-        <v>233.16</v>
+        <v>231.78</v>
       </c>
       <c r="G90">
-        <v>233.16</v>
+        <v>232.91</v>
       </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
@@ -4206,10 +4206,10 @@
         <v>122</v>
       </c>
       <c r="B91">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C91">
-        <v>5.87</v>
+        <v>4.22</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
@@ -4218,7 +4218,7 @@
         <v>537.7</v>
       </c>
       <c r="F91">
-        <v>368.09</v>
+        <v>366.58</v>
       </c>
       <c r="G91">
         <v>353.09</v>
@@ -4244,19 +4244,19 @@
         <v>123</v>
       </c>
       <c r="B92">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="C92">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="D92">
         <f>C92*$B$3</f>
       </c>
       <c r="E92">
-        <v>499.62</v>
+        <v>493.69</v>
       </c>
       <c r="F92">
-        <v>333.29</v>
+        <v>332.91</v>
       </c>
       <c r="G92">
         <v>327.87</v>
@@ -4282,22 +4282,22 @@
         <v>124</v>
       </c>
       <c r="B93">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C93">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="D93">
         <f>C93*$B$3</f>
       </c>
       <c r="E93">
-        <v>483.61</v>
+        <v>468.35</v>
       </c>
       <c r="F93">
-        <v>351.83</v>
+        <v>351.7</v>
       </c>
       <c r="G93">
-        <v>339.22</v>
+        <v>337.96</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -4320,22 +4320,22 @@
         <v>125</v>
       </c>
       <c r="B94">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C94">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>344.89</v>
+        <v>345.77</v>
       </c>
       <c r="F94">
-        <v>226.99</v>
+        <v>224.46</v>
       </c>
       <c r="G94">
-        <v>220.68</v>
+        <v>219.42</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -4358,10 +4358,10 @@
         <v>126</v>
       </c>
       <c r="B95">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C95">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="D95">
         <f>C95*$B$3</f>
@@ -4370,7 +4370,7 @@
         <v>502.14</v>
       </c>
       <c r="F95">
-        <v>317.78</v>
+        <v>316.52</v>
       </c>
       <c r="G95">
         <v>304.79</v>
@@ -4396,22 +4396,22 @@
         <v>127</v>
       </c>
       <c r="B96">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C96">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="D96">
         <f>C96*$B$3</f>
       </c>
       <c r="E96">
-        <v>486.13</v>
+        <v>492.81</v>
       </c>
       <c r="F96">
         <v>325.98</v>
       </c>
       <c r="G96">
-        <v>350.44</v>
+        <v>349.18</v>
       </c>
       <c r="H96">
         <f>MIN(E96:G96)</f>
@@ -4446,7 +4446,7 @@
         <v>488.65</v>
       </c>
       <c r="F97">
-        <v>290.04</v>
+        <v>288.78</v>
       </c>
       <c r="G97">
         <v>289.91</v>
@@ -4513,13 +4513,13 @@
         <v>39</v>
       </c>
       <c r="C99">
-        <v>3.74</v>
+        <v>3.69</v>
       </c>
       <c r="D99">
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>545.27</v>
+        <v>544.39</v>
       </c>
       <c r="F99">
         <v>301.39</v>
@@ -4548,22 +4548,22 @@
         <v>131</v>
       </c>
       <c r="B100">
-        <v>1025</v>
+        <v>1013</v>
       </c>
       <c r="C100">
-        <v>3.76</v>
+        <v>3.69</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>421.81</v>
+        <v>429.38</v>
       </c>
       <c r="F100">
-        <v>326.23</v>
+        <v>322.82</v>
       </c>
       <c r="G100">
-        <v>327.87</v>
+        <v>324.08</v>
       </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
@@ -4601,7 +4601,7 @@
         <v>276.54</v>
       </c>
       <c r="G101">
-        <v>271.12</v>
+        <v>270.74</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -4636,7 +4636,7 @@
         <v>420.18</v>
       </c>
       <c r="F102">
-        <v>304.79</v>
+        <v>303.4</v>
       </c>
       <c r="G102">
         <v>244.51</v>
@@ -4665,7 +4665,7 @@
         <v>215</v>
       </c>
       <c r="C103">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
@@ -4677,7 +4677,7 @@
         <v>239.6</v>
       </c>
       <c r="G103">
-        <v>237.7</v>
+        <v>235.18</v>
       </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
@@ -4712,7 +4712,7 @@
         <v>380.45</v>
       </c>
       <c r="F104">
-        <v>250.94</v>
+        <v>249.68</v>
       </c>
       <c r="G104">
         <v>239.22</v>
@@ -4738,10 +4738,10 @@
         <v>136</v>
       </c>
       <c r="B105">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C105">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="D105">
         <f>C105*$B$3</f>
@@ -4779,7 +4779,7 @@
         <v>92</v>
       </c>
       <c r="C106">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="D106">
         <f>C106*$B$3</f>
@@ -4788,7 +4788,7 @@
         <v>400.76</v>
       </c>
       <c r="F106">
-        <v>252.21</v>
+        <v>250.94</v>
       </c>
       <c r="G106">
         <v>236.44</v>
@@ -4814,7 +4814,7 @@
         <v>138</v>
       </c>
       <c r="B107">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C107">
         <v>2.86</v>
@@ -4826,10 +4826,10 @@
         <v>330.52</v>
       </c>
       <c r="F107">
-        <v>252.21</v>
+        <v>252.08</v>
       </c>
       <c r="G107">
-        <v>243.25</v>
+        <v>243.88</v>
       </c>
       <c r="H107">
         <f>MIN(E107:G107)</f>
@@ -4893,7 +4893,7 @@
         <v>337</v>
       </c>
       <c r="C109">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
@@ -4905,7 +4905,7 @@
         <v>240.86</v>
       </c>
       <c r="G109">
-        <v>219.42</v>
+        <v>218.16</v>
       </c>
       <c r="H109">
         <f>MIN(E109:G109)</f>
@@ -4940,10 +4940,10 @@
         <v>331.4</v>
       </c>
       <c r="F110">
-        <v>236.06</v>
+        <v>235.81</v>
       </c>
       <c r="G110">
-        <v>219.29</v>
+        <v>214.38</v>
       </c>
       <c r="H110">
         <f>MIN(E110:G110)</f>
@@ -4978,7 +4978,7 @@
         <v>337.33</v>
       </c>
       <c r="F111">
-        <v>221.06</v>
+        <v>220.55</v>
       </c>
       <c r="G111">
         <v>221.82</v>
@@ -5007,7 +5007,7 @@
         <v>58</v>
       </c>
       <c r="C112">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="D112">
         <f>C112*$B$3</f>
@@ -5016,7 +5016,7 @@
         <v>278.06</v>
       </c>
       <c r="F112">
-        <v>182.72</v>
+        <v>182.85</v>
       </c>
       <c r="G112">
         <v>194.32</v>
@@ -5051,13 +5051,13 @@
         <f>C113*$B$3</f>
       </c>
       <c r="E113">
-        <v>324.59</v>
+        <v>323.71</v>
       </c>
       <c r="F113">
-        <v>235.81</v>
+        <v>233.29</v>
       </c>
       <c r="G113">
-        <v>229.13</v>
+        <v>228.88</v>
       </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
@@ -5089,13 +5089,13 @@
         <f>C114*$B$3</f>
       </c>
       <c r="E114">
-        <v>300.88</v>
+        <v>308.57</v>
       </c>
       <c r="F114">
         <v>211.35</v>
       </c>
       <c r="G114">
-        <v>218.79</v>
+        <v>217.53</v>
       </c>
       <c r="H114">
         <f>MIN(E114:G114)</f>
@@ -5118,10 +5118,10 @@
         <v>146</v>
       </c>
       <c r="B115">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C115">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="D115">
         <f>C115*$B$3</f>
@@ -5130,10 +5130,10 @@
         <v>357.63</v>
       </c>
       <c r="F115">
-        <v>170.24</v>
+        <v>162.67</v>
       </c>
       <c r="G115">
-        <v>181.59</v>
+        <v>180.33</v>
       </c>
       <c r="H115">
         <f>MIN(E115:G115)</f>
@@ -5168,7 +5168,7 @@
         <v>236.7</v>
       </c>
       <c r="F116">
-        <v>182.85</v>
+        <v>180.33</v>
       </c>
       <c r="G116">
         <v>192.94</v>
@@ -5194,10 +5194,10 @@
         <v>148</v>
       </c>
       <c r="B117">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C117">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="D117">
         <f>C117*$B$3</f>
@@ -5209,7 +5209,7 @@
         <v>179.44</v>
       </c>
       <c r="G117">
-        <v>167.72</v>
+        <v>168.98</v>
       </c>
       <c r="H117">
         <f>MIN(E117:G117)</f>
@@ -5244,10 +5244,10 @@
         <v>312.74</v>
       </c>
       <c r="F118">
-        <v>224.72</v>
+        <v>223.45</v>
       </c>
       <c r="G118">
-        <v>226.61</v>
+        <v>225.6</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -5282,10 +5282,10 @@
         <v>272.13</v>
       </c>
       <c r="F119">
-        <v>205.55</v>
+        <v>206.81</v>
       </c>
       <c r="G119">
-        <v>202.14</v>
+        <v>203.4</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -5323,7 +5323,7 @@
         <v>171.63</v>
       </c>
       <c r="G120">
-        <v>165.19</v>
+        <v>163.81</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -5358,10 +5358,10 @@
         <v>321.18</v>
       </c>
       <c r="F121">
-        <v>201.76</v>
+        <v>200.5</v>
       </c>
       <c r="G121">
-        <v>201.76</v>
+        <v>211.85</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -5387,7 +5387,7 @@
         <v>97</v>
       </c>
       <c r="C122">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="D122">
         <f>C122*$B$3</f>
@@ -5396,7 +5396,7 @@
         <v>242.62</v>
       </c>
       <c r="F122">
-        <v>153.47</v>
+        <v>153.34</v>
       </c>
       <c r="G122">
         <v>172.76</v>
@@ -5434,7 +5434,7 @@
         <v>142.87</v>
       </c>
       <c r="F123">
-        <v>131.02</v>
+        <v>130.89</v>
       </c>
       <c r="G123">
         <v>111.85</v>
@@ -5472,7 +5472,7 @@
         <v>245.14</v>
       </c>
       <c r="F124">
-        <v>166.46</v>
+        <v>167.46</v>
       </c>
       <c r="G124">
         <v>162.67</v>
@@ -5501,7 +5501,7 @@
         <v>75</v>
       </c>
       <c r="C125">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="D125">
         <f>C125*$B$3</f>
@@ -5510,10 +5510,10 @@
         <v>196.97</v>
       </c>
       <c r="F125">
-        <v>143.38</v>
+        <v>142.24</v>
       </c>
       <c r="G125">
-        <v>128.25</v>
+        <v>126.86</v>
       </c>
       <c r="H125">
         <f>MIN(E125:G125)</f>
@@ -5536,7 +5536,7 @@
         <v>157</v>
       </c>
       <c r="B126">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C126">
         <v>1.14</v>
@@ -5548,7 +5548,7 @@
         <v>140.23</v>
       </c>
       <c r="F126">
-        <v>106.05</v>
+        <v>105.93</v>
       </c>
       <c r="G126">
         <v>100.88</v>
@@ -5589,7 +5589,7 @@
         <v>111.73</v>
       </c>
       <c r="G127">
-        <v>106.68</v>
+        <v>103.28</v>
       </c>
       <c r="H127">
         <f>MIN(E127:G127)</f>
@@ -5621,13 +5621,13 @@
         <f>C128*$B$3</f>
       </c>
       <c r="E128">
-        <v>146.15</v>
+        <v>145.4</v>
       </c>
       <c r="F128">
-        <v>89.91</v>
+        <v>89.79</v>
       </c>
       <c r="G128">
-        <v>89.41</v>
+        <v>89.15</v>
       </c>
       <c r="H128">
         <f>MIN(E128:G128)</f>
@@ -5650,7 +5650,7 @@
         <v>160</v>
       </c>
       <c r="B129">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -5662,10 +5662,10 @@
         <v>109.84</v>
       </c>
       <c r="F129">
-        <v>81.46</v>
+        <v>80.83</v>
       </c>
       <c r="G129">
-        <v>88.15</v>
+        <v>88.02</v>
       </c>
       <c r="H129">
         <f>MIN(E129:G129)</f>
@@ -5697,10 +5697,10 @@
         <f>C130*$B$3</f>
       </c>
       <c r="E130">
-        <v>98.86</v>
+        <v>99.75</v>
       </c>
       <c r="F130">
-        <v>75.03</v>
+        <v>74.91</v>
       </c>
       <c r="G130">
         <v>74.02</v>
@@ -5726,7 +5726,7 @@
         <v>162</v>
       </c>
       <c r="B131">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C131">
         <v>0.73</v>
@@ -5738,10 +5738,10 @@
         <v>92.94</v>
       </c>
       <c r="F131">
-        <v>64.31</v>
+        <v>63.81</v>
       </c>
       <c r="G131">
-        <v>61.41</v>
+        <v>61.16</v>
       </c>
       <c r="H131">
         <f>MIN(E131:G131)</f>
@@ -5767,7 +5767,7 @@
         <v>1028</v>
       </c>
       <c r="C132">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="D132">
         <f>C132*$B$3</f>
@@ -5776,10 +5776,10 @@
         <v>114.12</v>
       </c>
       <c r="F132">
-        <v>75.54</v>
+        <v>75.41</v>
       </c>
       <c r="G132">
-        <v>81.71</v>
+        <v>81.59</v>
       </c>
       <c r="H132">
         <f>MIN(E132:G132)</f>
@@ -5814,10 +5814,10 @@
         <v>65.07</v>
       </c>
       <c r="F133">
-        <v>44.01</v>
+        <v>43.88</v>
       </c>
       <c r="G133">
-        <v>46.53</v>
+        <v>46.41</v>
       </c>
       <c r="H133">
         <f>MIN(E133:G133)</f>
@@ -5840,7 +5840,7 @@
         <v>165</v>
       </c>
       <c r="B134">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C134">
         <v>0.63</v>
@@ -5849,13 +5849,13 @@
         <f>C134*$B$3</f>
       </c>
       <c r="E134">
-        <v>83.61</v>
+        <v>87.01</v>
       </c>
       <c r="F134">
-        <v>52.08</v>
+        <v>52.21</v>
       </c>
       <c r="G134">
-        <v>50.06</v>
+        <v>49.94</v>
       </c>
       <c r="H134">
         <f>MIN(E134:G134)</f>
@@ -5878,7 +5878,7 @@
         <v>166</v>
       </c>
       <c r="B135">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C135">
         <v>0.41</v>
@@ -5890,10 +5890,10 @@
         <v>53.22</v>
       </c>
       <c r="F135">
-        <v>34.05</v>
+        <v>33.8</v>
       </c>
       <c r="G135">
-        <v>40.73</v>
+        <v>40.61</v>
       </c>
       <c r="H135">
         <f>MIN(E135:G135)</f>
@@ -5931,7 +5931,7 @@
         <v>30.52</v>
       </c>
       <c r="G136">
-        <v>30.52</v>
+        <v>30.39</v>
       </c>
       <c r="H136">
         <f>MIN(E136:G136)</f>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="168">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 21.09.2026 13:34</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 28.09.2026 16:49</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -921,7 +921,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>84.1975</v>
+        <v>84.3414</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -930,7 +930,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>12.6103</v>
+        <v>12.6263</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -976,22 +976,22 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6">
-        <v>70.75</v>
+        <v>66.95</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
       </c>
       <c r="E6">
-        <v>8758.23</v>
+        <v>8172.75</v>
       </c>
       <c r="F6">
-        <v>5767.7</v>
+        <v>5667.95</v>
       </c>
       <c r="G6">
-        <v>5548.53</v>
+        <v>5492.44</v>
       </c>
       <c r="H6">
         <f>MIN(E6:G6)</f>
@@ -1014,22 +1014,22 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>317</v>
+        <v>288</v>
       </c>
       <c r="C7">
-        <v>66.15</v>
+        <v>65.41</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
       </c>
       <c r="E7">
-        <v>7778.41</v>
+        <v>7670.48</v>
       </c>
       <c r="F7">
-        <v>5208.05</v>
+        <v>5075.77</v>
       </c>
       <c r="G7">
-        <v>5214.36</v>
+        <v>5227.29</v>
       </c>
       <c r="H7">
         <f>MIN(E7:G7)</f>
@@ -1052,22 +1052,22 @@
         <v>23</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C8">
-        <v>74.66</v>
+        <v>79.32</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
       </c>
       <c r="E8">
-        <v>8705.02</v>
+        <v>8656.47</v>
       </c>
       <c r="F8">
-        <v>6987.37</v>
+        <v>6626.28</v>
       </c>
       <c r="G8">
-        <v>5749.16</v>
+        <v>6294.21</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -1090,22 +1090,22 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="C9">
-        <v>53.08</v>
+        <v>51.57</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
       </c>
       <c r="E9">
-        <v>6154.2</v>
+        <v>5792.95</v>
       </c>
       <c r="F9">
-        <v>4287.5</v>
+        <v>4431.83</v>
       </c>
       <c r="G9">
-        <v>4192.92</v>
+        <v>4412.89</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -1128,22 +1128,22 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="C10">
-        <v>48.32</v>
+        <v>45.64</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
       </c>
       <c r="E10">
-        <v>5505.78</v>
+        <v>5012.39</v>
       </c>
       <c r="F10">
-        <v>3745.26</v>
+        <v>3825.77</v>
       </c>
       <c r="G10">
-        <v>3801.88</v>
+        <v>3712.13</v>
       </c>
       <c r="H10">
         <f>MIN(E10:G10)</f>
@@ -1166,22 +1166,22 @@
         <v>29</v>
       </c>
       <c r="B11">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="C11">
-        <v>43.57</v>
+        <v>42.37</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
       </c>
       <c r="E11">
-        <v>4861.52</v>
+        <v>4352.41</v>
       </c>
       <c r="F11">
-        <v>3503.77</v>
+        <v>3320.34</v>
       </c>
       <c r="G11">
-        <v>3417.39</v>
+        <v>3356.07</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -1204,22 +1204,22 @@
         <v>30</v>
       </c>
       <c r="B12">
-        <v>329</v>
+        <v>411</v>
       </c>
       <c r="C12">
-        <v>43.24</v>
+        <v>39.94</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
       </c>
       <c r="E12">
-        <v>5008.56</v>
+        <v>4197.99</v>
       </c>
       <c r="F12">
-        <v>3411.09</v>
+        <v>3301.4</v>
       </c>
       <c r="G12">
-        <v>3455.22</v>
+        <v>3290.16</v>
       </c>
       <c r="H12">
         <f>MIN(E12:G12)</f>
@@ -1242,22 +1242,22 @@
         <v>31</v>
       </c>
       <c r="B13">
-        <v>335</v>
+        <v>285</v>
       </c>
       <c r="C13">
-        <v>49.93</v>
+        <v>50.52</v>
       </c>
       <c r="D13">
         <f>C13*$B$3</f>
       </c>
       <c r="E13">
-        <v>5767.83</v>
+        <v>5938.91</v>
       </c>
       <c r="F13">
-        <v>3991.16</v>
+        <v>4071.98</v>
       </c>
       <c r="G13">
-        <v>3915.5</v>
+        <v>4071.98</v>
       </c>
       <c r="H13">
         <f>MIN(E13:G13)</f>
@@ -1280,22 +1280,22 @@
         <v>32</v>
       </c>
       <c r="B14">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C14">
-        <v>47.08</v>
+        <v>45.03</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
       </c>
       <c r="E14">
-        <v>5114.23</v>
+        <v>5429.06</v>
       </c>
       <c r="F14">
-        <v>3789.4</v>
+        <v>3876.27</v>
       </c>
       <c r="G14">
-        <v>3763.8</v>
+        <v>3821.98</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1318,22 +1318,22 @@
         <v>33</v>
       </c>
       <c r="B15">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C15">
-        <v>49.42</v>
+        <v>47.56</v>
       </c>
       <c r="D15">
         <f>C15*$B$3</f>
       </c>
       <c r="E15">
-        <v>5819.4</v>
+        <v>5303.42</v>
       </c>
       <c r="F15">
-        <v>3871.36</v>
+        <v>3825.77</v>
       </c>
       <c r="G15">
-        <v>4054.21</v>
+        <v>3995.59</v>
       </c>
       <c r="H15">
         <f>MIN(E15:G15)</f>
@@ -1356,22 +1356,22 @@
         <v>34</v>
       </c>
       <c r="B16">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C16">
-        <v>43.04</v>
+        <v>42.41</v>
       </c>
       <c r="D16">
         <f>C16*$B$3</f>
       </c>
       <c r="E16">
-        <v>5187.88</v>
+        <v>5457.84</v>
       </c>
       <c r="F16">
-        <v>3606.29</v>
+        <v>3591.8</v>
       </c>
       <c r="G16">
-        <v>3467.83</v>
+        <v>3415.41</v>
       </c>
       <c r="H16">
         <f>MIN(E16:G16)</f>
@@ -1394,22 +1394,22 @@
         <v>35</v>
       </c>
       <c r="B17">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C17">
-        <v>37.78</v>
+        <v>36.65</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
       </c>
       <c r="E17">
-        <v>4569.72</v>
+        <v>4326.02</v>
       </c>
       <c r="F17">
-        <v>3020.17</v>
+        <v>3028.67</v>
       </c>
       <c r="G17">
-        <v>3026.47</v>
+        <v>2929.3</v>
       </c>
       <c r="H17">
         <f>MIN(E17:G17)</f>
@@ -1432,22 +1432,22 @@
         <v>36</v>
       </c>
       <c r="B18">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C18">
-        <v>45.47</v>
+        <v>43.47</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
       </c>
       <c r="E18">
-        <v>4921.55</v>
+        <v>6341.94</v>
       </c>
       <c r="F18">
-        <v>3770.48</v>
+        <v>3613.65</v>
       </c>
       <c r="G18">
-        <v>3735.17</v>
+        <v>3489.91</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1470,22 +1470,22 @@
         <v>37</v>
       </c>
       <c r="B19">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C19">
-        <v>42.84</v>
+        <v>41.31</v>
       </c>
       <c r="D19">
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>5727.22</v>
+        <v>4360.87</v>
       </c>
       <c r="F19">
-        <v>3526.6</v>
+        <v>3368.82</v>
       </c>
       <c r="G19">
-        <v>3360.27</v>
+        <v>3363.02</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1508,22 +1508,22 @@
         <v>38</v>
       </c>
       <c r="B20">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20">
-        <v>29.75</v>
+        <v>28.83</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
       </c>
       <c r="E20">
-        <v>3753.83</v>
+        <v>3584.48</v>
       </c>
       <c r="F20">
-        <v>2336.18</v>
+        <v>2882.58</v>
       </c>
       <c r="G20">
-        <v>2332.91</v>
+        <v>2605.82</v>
       </c>
       <c r="H20">
         <f>MIN(E20:G20)</f>
@@ -1546,22 +1546,22 @@
         <v>39</v>
       </c>
       <c r="B21">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C21">
-        <v>27.84</v>
+        <v>26.4</v>
       </c>
       <c r="D21">
         <f>C21*$B$3</f>
       </c>
       <c r="E21">
-        <v>3297.34</v>
+        <v>2871.85</v>
       </c>
       <c r="F21">
-        <v>2455.23</v>
+        <v>2152.15</v>
       </c>
       <c r="G21">
-        <v>2248.42</v>
+        <v>2167.94</v>
       </c>
       <c r="H21">
         <f>MIN(E21:G21)</f>
@@ -1584,22 +1584,22 @@
         <v>40</v>
       </c>
       <c r="B22">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="C22">
-        <v>33.29</v>
+        <v>30.55</v>
       </c>
       <c r="D22">
         <f>C22*$B$3</f>
       </c>
       <c r="E22">
-        <v>3840.97</v>
+        <v>3596.35</v>
       </c>
       <c r="F22">
-        <v>2698.6</v>
+        <v>2487.25</v>
       </c>
       <c r="G22">
-        <v>2815.63</v>
+        <v>2671.73</v>
       </c>
       <c r="H22">
         <f>MIN(E22:G22)</f>
@@ -1622,22 +1622,22 @@
         <v>41</v>
       </c>
       <c r="B23">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="C23">
-        <v>23.95</v>
+        <v>22.37</v>
       </c>
       <c r="D23">
         <f>C23*$B$3</f>
       </c>
       <c r="E23">
-        <v>2956.61</v>
+        <v>2375.51</v>
       </c>
       <c r="F23">
-        <v>1910.46</v>
+        <v>1742.43</v>
       </c>
       <c r="G23">
-        <v>1840.98</v>
+        <v>1723.49</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1660,22 +1660,22 @@
         <v>43</v>
       </c>
       <c r="B24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24">
-        <v>5.07</v>
+        <v>5.04</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
       </c>
       <c r="E24">
-        <v>771.88</v>
+        <v>684.6</v>
       </c>
       <c r="F24">
-        <v>414.88</v>
+        <v>458.21</v>
       </c>
       <c r="G24">
-        <v>535.94</v>
+        <v>517.68</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1698,22 +1698,22 @@
         <v>46</v>
       </c>
       <c r="B25">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C25">
-        <v>25.6</v>
+        <v>24.89</v>
       </c>
       <c r="D25">
         <f>C25*$B$3</f>
       </c>
       <c r="E25">
-        <v>2849.17</v>
+        <v>2899.88</v>
       </c>
       <c r="F25">
-        <v>2116.89</v>
+        <v>2058.09</v>
       </c>
       <c r="G25">
-        <v>2112.23</v>
+        <v>2056.82</v>
       </c>
       <c r="H25">
         <f>MIN(E25:G25)</f>
@@ -1736,22 +1736,22 @@
         <v>47</v>
       </c>
       <c r="B26">
-        <v>523</v>
+        <v>442</v>
       </c>
       <c r="C26">
-        <v>17.5</v>
+        <v>18.48</v>
       </c>
       <c r="D26">
         <f>C26*$B$3</f>
       </c>
       <c r="E26">
-        <v>1960.65</v>
+        <v>1951.27</v>
       </c>
       <c r="F26">
-        <v>1380.83</v>
+        <v>1452.02</v>
       </c>
       <c r="G26">
-        <v>1372</v>
+        <v>1452.02</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1774,22 +1774,22 @@
         <v>48</v>
       </c>
       <c r="B27">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C27">
-        <v>17.41</v>
+        <v>16.78</v>
       </c>
       <c r="D27">
         <f>C27*$B$3</f>
       </c>
       <c r="E27">
-        <v>1944.51</v>
+        <v>1800.26</v>
       </c>
       <c r="F27">
-        <v>1360.65</v>
+        <v>1309.22</v>
       </c>
       <c r="G27">
-        <v>1412.35</v>
+        <v>1325.76</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1812,22 +1812,22 @@
         <v>49</v>
       </c>
       <c r="B28">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="C28">
-        <v>18.88</v>
+        <v>18.98</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
       </c>
       <c r="E28">
-        <v>2155.1</v>
+        <v>2299.12</v>
       </c>
       <c r="F28">
-        <v>1563.68</v>
+        <v>1533.97</v>
       </c>
       <c r="G28">
-        <v>1519.54</v>
+        <v>1526.52</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1850,22 +1850,22 @@
         <v>52</v>
       </c>
       <c r="B29">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="C29">
-        <v>19.75</v>
+        <v>17.43</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
       </c>
       <c r="E29">
-        <v>2169.48</v>
+        <v>2108.21</v>
       </c>
       <c r="F29">
-        <v>1500.63</v>
+        <v>1450.51</v>
       </c>
       <c r="G29">
-        <v>1469.1</v>
+        <v>1414.15</v>
       </c>
       <c r="H29">
         <f>MIN(E29:G29)</f>
@@ -1888,22 +1888,22 @@
         <v>53</v>
       </c>
       <c r="B30">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C30">
-        <v>16.54</v>
+        <v>16.41</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
       </c>
       <c r="E30">
-        <v>1925.09</v>
+        <v>1875.01</v>
       </c>
       <c r="F30">
-        <v>1336.69</v>
+        <v>1351.01</v>
       </c>
       <c r="G30">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1926,22 +1926,22 @@
         <v>54</v>
       </c>
       <c r="B31">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C31">
-        <v>17.52</v>
+        <v>17.11</v>
       </c>
       <c r="D31">
         <f>C31*$B$3</f>
       </c>
       <c r="E31">
-        <v>1989.4</v>
+        <v>1723.11</v>
       </c>
       <c r="F31">
-        <v>1366.96</v>
+        <v>1325.76</v>
       </c>
       <c r="G31">
-        <v>1374.52</v>
+        <v>1375</v>
       </c>
       <c r="H31">
         <f>MIN(E31:G31)</f>
@@ -1964,22 +1964,22 @@
         <v>55</v>
       </c>
       <c r="B32">
-        <v>641</v>
+        <v>610</v>
       </c>
       <c r="C32">
-        <v>15.3</v>
+        <v>16.02</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>1874.39</v>
+        <v>1769.7</v>
       </c>
       <c r="F32">
-        <v>1288.77</v>
+        <v>1275.26</v>
       </c>
       <c r="G32">
-        <v>1255.99</v>
+        <v>1267.68</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -2002,22 +2002,22 @@
         <v>56</v>
       </c>
       <c r="B33">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="C33">
-        <v>13.75</v>
+        <v>12.86</v>
       </c>
       <c r="D33">
         <f>C33*$B$3</f>
       </c>
       <c r="E33">
-        <v>1645.27</v>
+        <v>1611.12</v>
       </c>
       <c r="F33">
-        <v>1109.71</v>
+        <v>1007.33</v>
       </c>
       <c r="G33">
-        <v>1102.14</v>
+        <v>994.83</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -2040,22 +2040,22 @@
         <v>57</v>
       </c>
       <c r="B34">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="C34">
-        <v>15.82</v>
+        <v>15.12</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
       </c>
       <c r="E34">
-        <v>1804.16</v>
+        <v>1924.12</v>
       </c>
       <c r="F34">
-        <v>1197.85</v>
+        <v>1239.78</v>
       </c>
       <c r="G34">
-        <v>1223.2</v>
+        <v>1196.97</v>
       </c>
       <c r="H34">
         <f>MIN(E34:G34)</f>
@@ -2078,22 +2078,22 @@
         <v>58</v>
       </c>
       <c r="B35">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C35">
-        <v>15.05</v>
+        <v>13.64</v>
       </c>
       <c r="D35">
         <f>C35*$B$3</f>
       </c>
       <c r="E35">
-        <v>1730.64</v>
+        <v>1632.33</v>
       </c>
       <c r="F35">
-        <v>1197.85</v>
+        <v>1090.91</v>
       </c>
       <c r="G35">
-        <v>1181.84</v>
+        <v>1108.59</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -2116,22 +2116,22 @@
         <v>60</v>
       </c>
       <c r="B36">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C36">
-        <v>7.29</v>
+        <v>6.74</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
       </c>
       <c r="E36">
-        <v>809.96</v>
+        <v>751.64</v>
       </c>
       <c r="F36">
-        <v>620.43</v>
+        <v>534.09</v>
       </c>
       <c r="G36">
-        <v>643.13</v>
+        <v>549.24</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -2154,22 +2154,22 @@
         <v>61</v>
       </c>
       <c r="B37">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C37">
-        <v>10.51</v>
+        <v>10.75</v>
       </c>
       <c r="D37">
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>1066.96</v>
+        <v>1087.63</v>
       </c>
       <c r="F37">
-        <v>944.26</v>
+        <v>938.39</v>
       </c>
       <c r="G37">
-        <v>859.52</v>
+        <v>860.61</v>
       </c>
       <c r="H37">
         <f>MIN(E37:G37)</f>
@@ -2192,22 +2192,22 @@
         <v>62</v>
       </c>
       <c r="B38">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C38">
-        <v>11.79</v>
+        <v>12.1</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>1404.28</v>
+        <v>1293.82</v>
       </c>
       <c r="F38">
-        <v>856.24</v>
+        <v>947.48</v>
       </c>
       <c r="G38">
-        <v>983.6</v>
+        <v>953.29</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -2230,22 +2230,22 @@
         <v>63</v>
       </c>
       <c r="B39">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39">
-        <v>10.4</v>
+        <v>9.04</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
       </c>
       <c r="E39">
-        <v>1132.91</v>
+        <v>1096.97</v>
       </c>
       <c r="F39">
-        <v>876.29</v>
+        <v>714.27</v>
       </c>
       <c r="G39">
-        <v>879.95</v>
+        <v>782.07</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -2268,22 +2268,22 @@
         <v>64</v>
       </c>
       <c r="B40">
-        <v>916</v>
+        <v>681</v>
       </c>
       <c r="C40">
-        <v>9.96</v>
+        <v>10.53</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>1150.69</v>
+        <v>1242.93</v>
       </c>
       <c r="F40">
-        <v>795.84</v>
+        <v>824.62</v>
       </c>
       <c r="G40">
-        <v>781.84</v>
+        <v>794.07</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -2306,22 +2306,22 @@
         <v>66</v>
       </c>
       <c r="B41">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C41">
-        <v>12.76</v>
+        <v>12.69</v>
       </c>
       <c r="D41">
         <f>C41*$B$3</f>
       </c>
       <c r="E41">
-        <v>1701.89</v>
+        <v>1504.17</v>
       </c>
       <c r="F41">
-        <v>1007.56</v>
+        <v>1254.8</v>
       </c>
       <c r="G41">
-        <v>1046.65</v>
+        <v>1071.97</v>
       </c>
       <c r="H41">
         <f>MIN(E41:G41)</f>
@@ -2344,22 +2344,22 @@
         <v>68</v>
       </c>
       <c r="B42">
-        <v>835</v>
+        <v>744</v>
       </c>
       <c r="C42">
-        <v>10.16</v>
+        <v>9.76</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
       </c>
       <c r="E42">
-        <v>1188.65</v>
+        <v>1268.31</v>
       </c>
       <c r="F42">
-        <v>824.71</v>
+        <v>813.13</v>
       </c>
       <c r="G42">
-        <v>812.1</v>
+        <v>801.77</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2382,22 +2382,22 @@
         <v>69</v>
       </c>
       <c r="B43">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C43">
-        <v>8.82</v>
+        <v>8.38</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>930.01</v>
+        <v>919.57</v>
       </c>
       <c r="F43">
-        <v>718.79</v>
+        <v>694.32</v>
       </c>
       <c r="G43">
-        <v>716.9</v>
+        <v>683.08</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2420,22 +2420,22 @@
         <v>70</v>
       </c>
       <c r="B44">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C44">
-        <v>11.87</v>
+        <v>11.06</v>
       </c>
       <c r="D44">
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>1421.18</v>
+        <v>1390.53</v>
       </c>
       <c r="F44">
-        <v>957.75</v>
+        <v>954.3</v>
       </c>
       <c r="G44">
-        <v>873.89</v>
+        <v>852.15</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2458,22 +2458,22 @@
         <v>72</v>
       </c>
       <c r="B45">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C45">
-        <v>7.25</v>
+        <v>6.73</v>
       </c>
       <c r="D45">
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>940.98</v>
+        <v>824.62</v>
       </c>
       <c r="F45">
-        <v>605.04</v>
+        <v>525.89</v>
       </c>
       <c r="G45">
-        <v>574.9</v>
+        <v>530.3</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2496,22 +2496,22 @@
         <v>74</v>
       </c>
       <c r="B46">
-        <v>1093</v>
+        <v>1042</v>
       </c>
       <c r="C46">
-        <v>9.52</v>
+        <v>9.5</v>
       </c>
       <c r="D46">
         <f>C46*$B$3</f>
       </c>
       <c r="E46">
-        <v>1066.96</v>
+        <v>1098.61</v>
       </c>
       <c r="F46">
-        <v>736.44</v>
+        <v>744.95</v>
       </c>
       <c r="G46">
-        <v>725.09</v>
+        <v>729.55</v>
       </c>
       <c r="H46">
         <f>MIN(E46:G46)</f>
@@ -2534,22 +2534,22 @@
         <v>75</v>
       </c>
       <c r="B47">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C47">
-        <v>10.55</v>
+        <v>11.64</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>1161.66</v>
+        <v>1211.49</v>
       </c>
       <c r="F47">
-        <v>907.82</v>
+        <v>972.23</v>
       </c>
       <c r="G47">
-        <v>925.34</v>
+        <v>982.33</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2572,22 +2572,22 @@
         <v>76</v>
       </c>
       <c r="B48">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="C48">
-        <v>8.55</v>
+        <v>8.72</v>
       </c>
       <c r="D48">
         <f>C48*$B$3</f>
       </c>
       <c r="E48">
-        <v>1002.64</v>
+        <v>990.03</v>
       </c>
       <c r="F48">
-        <v>715</v>
+        <v>691.92</v>
       </c>
       <c r="G48">
-        <v>677.17</v>
+        <v>679.29</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2610,22 +2610,22 @@
         <v>77</v>
       </c>
       <c r="B49">
-        <v>769</v>
+        <v>627</v>
       </c>
       <c r="C49">
-        <v>7.83</v>
+        <v>7.96</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>945.14</v>
+        <v>952.65</v>
       </c>
       <c r="F49">
-        <v>640.48</v>
+        <v>643.44</v>
       </c>
       <c r="G49">
-        <v>623.71</v>
+        <v>625</v>
       </c>
       <c r="H49">
         <f>MIN(E49:G49)</f>
@@ -2648,22 +2648,22 @@
         <v>79</v>
       </c>
       <c r="B50">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C50">
-        <v>8</v>
+        <v>8.21</v>
       </c>
       <c r="D50">
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>832.78</v>
+        <v>928.16</v>
       </c>
       <c r="F50">
-        <v>630.39</v>
+        <v>618.56</v>
       </c>
       <c r="G50">
-        <v>630.52</v>
+        <v>631.32</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2686,22 +2686,22 @@
         <v>80</v>
       </c>
       <c r="B51">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C51">
-        <v>9.84</v>
+        <v>8.89</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>1075.41</v>
+        <v>967.17</v>
       </c>
       <c r="F51">
-        <v>817.02</v>
+        <v>767.81</v>
       </c>
       <c r="G51">
-        <v>805.55</v>
+        <v>732.2</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2724,22 +2724,22 @@
         <v>81</v>
       </c>
       <c r="B52">
-        <v>275</v>
+        <v>212</v>
       </c>
       <c r="C52">
-        <v>7.79</v>
+        <v>8.76</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>888.52</v>
+        <v>905.18</v>
       </c>
       <c r="F52">
-        <v>627.99</v>
+        <v>628.79</v>
       </c>
       <c r="G52">
-        <v>622.32</v>
+        <v>649.12</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2762,22 +2762,22 @@
         <v>82</v>
       </c>
       <c r="B53">
-        <v>910</v>
+        <v>730</v>
       </c>
       <c r="C53">
-        <v>8.17</v>
+        <v>7.89</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>930.77</v>
+        <v>1017.17</v>
       </c>
       <c r="F53">
-        <v>640.6</v>
+        <v>656.57</v>
       </c>
       <c r="G53">
-        <v>629.25</v>
+        <v>640.15</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2800,22 +2800,22 @@
         <v>84</v>
       </c>
       <c r="B54">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C54">
-        <v>5.34</v>
+        <v>5.26</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
       </c>
       <c r="E54">
-        <v>608.7</v>
+        <v>542.93</v>
       </c>
       <c r="F54">
-        <v>431.15</v>
+        <v>431.19</v>
       </c>
       <c r="G54">
-        <v>435.06</v>
+        <v>425.51</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2838,22 +2838,22 @@
         <v>85</v>
       </c>
       <c r="B55">
-        <v>636</v>
+        <v>580</v>
       </c>
       <c r="C55">
-        <v>7.38</v>
+        <v>8.02</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>920.68</v>
+        <v>900.13</v>
       </c>
       <c r="F55">
-        <v>587.14</v>
+        <v>622.48</v>
       </c>
       <c r="G55">
-        <v>576.04</v>
+        <v>612.38</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2876,22 +2876,22 @@
         <v>86</v>
       </c>
       <c r="B56">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="C56">
-        <v>7.29</v>
+        <v>7.38</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>836.06</v>
+        <v>894.19</v>
       </c>
       <c r="F56">
-        <v>704.66</v>
+        <v>630.05</v>
       </c>
       <c r="G56">
-        <v>686.38</v>
+        <v>651.39</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2914,22 +2914,22 @@
         <v>87</v>
       </c>
       <c r="B57">
-        <v>360</v>
+        <v>264</v>
       </c>
       <c r="C57">
-        <v>7.06</v>
+        <v>7.03</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>777.8</v>
+        <v>765.15</v>
       </c>
       <c r="F57">
-        <v>590.79</v>
+        <v>568.18</v>
       </c>
       <c r="G57">
-        <v>579.95</v>
+        <v>584.47</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2952,22 +2952,22 @@
         <v>88</v>
       </c>
       <c r="B58">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C58">
-        <v>6.32</v>
+        <v>6.13</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>879.19</v>
+        <v>772.86</v>
       </c>
       <c r="F58">
-        <v>598.99</v>
+        <v>516.54</v>
       </c>
       <c r="G58">
-        <v>542.24</v>
+        <v>530.3</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2990,22 +2990,22 @@
         <v>89</v>
       </c>
       <c r="B59">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C59">
-        <v>6.83</v>
+        <v>7.12</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
       </c>
       <c r="E59">
-        <v>777.8</v>
+        <v>764.4</v>
       </c>
       <c r="F59">
-        <v>499.37</v>
+        <v>538.01</v>
       </c>
       <c r="G59">
-        <v>585.12</v>
+        <v>542.93</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -3028,22 +3028,22 @@
         <v>90</v>
       </c>
       <c r="B60">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C60">
-        <v>6.5</v>
+        <v>6.14</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>754.1</v>
+        <v>712.63</v>
       </c>
       <c r="F60">
-        <v>501.89</v>
+        <v>521.84</v>
       </c>
       <c r="G60">
-        <v>498.74</v>
+        <v>491.16</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -3066,22 +3066,22 @@
         <v>91</v>
       </c>
       <c r="B61">
-        <v>377</v>
+        <v>412</v>
       </c>
       <c r="C61">
-        <v>6.98</v>
+        <v>7.06</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>752.46</v>
+        <v>738.01</v>
       </c>
       <c r="F61">
-        <v>605.29</v>
+        <v>587.12</v>
       </c>
       <c r="G61">
-        <v>576.67</v>
+        <v>582.96</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
@@ -3104,22 +3104,22 @@
         <v>92</v>
       </c>
       <c r="B62">
-        <v>782</v>
+        <v>709</v>
       </c>
       <c r="C62">
-        <v>6.49</v>
+        <v>6.63</v>
       </c>
       <c r="D62">
         <f>C62*$B$3</f>
       </c>
       <c r="E62">
-        <v>875.03</v>
+        <v>771.97</v>
       </c>
       <c r="F62">
-        <v>533.29</v>
+        <v>552.91</v>
       </c>
       <c r="G62">
-        <v>511.98</v>
+        <v>529.04</v>
       </c>
       <c r="H62">
         <f>MIN(E62:G62)</f>
@@ -3142,22 +3142,22 @@
         <v>93</v>
       </c>
       <c r="B63">
-        <v>504</v>
+        <v>449</v>
       </c>
       <c r="C63">
-        <v>6.06</v>
+        <v>6.29</v>
       </c>
       <c r="D63">
         <f>C63*$B$3</f>
       </c>
       <c r="E63">
-        <v>775.28</v>
+        <v>758.46</v>
       </c>
       <c r="F63">
-        <v>498.11</v>
+        <v>498.74</v>
       </c>
       <c r="G63">
-        <v>479.19</v>
+        <v>490.53</v>
       </c>
       <c r="H63">
         <f>MIN(E63:G63)</f>
@@ -3180,22 +3180,22 @@
         <v>94</v>
       </c>
       <c r="B64">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="C64">
-        <v>4.82</v>
+        <v>4.69</v>
       </c>
       <c r="D64">
         <f>C64*$B$3</f>
       </c>
       <c r="E64">
-        <v>547.79</v>
+        <v>475.89</v>
       </c>
       <c r="F64">
-        <v>373.52</v>
+        <v>364.14</v>
       </c>
       <c r="G64">
-        <v>385.37</v>
+        <v>390.78</v>
       </c>
       <c r="H64">
         <f>MIN(E64:G64)</f>
@@ -3218,22 +3218,22 @@
         <v>95</v>
       </c>
       <c r="B65">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="C65">
-        <v>6.68</v>
+        <v>6.27</v>
       </c>
       <c r="D65">
         <f>C65*$B$3</f>
       </c>
       <c r="E65">
-        <v>763.43</v>
+        <v>868.69</v>
       </c>
       <c r="F65">
-        <v>517.02</v>
+        <v>503.79</v>
       </c>
       <c r="G65">
-        <v>522.07</v>
+        <v>511.24</v>
       </c>
       <c r="H65">
         <f>MIN(E65:G65)</f>
@@ -3256,22 +3256,22 @@
         <v>96</v>
       </c>
       <c r="B66">
-        <v>739</v>
+        <v>687</v>
       </c>
       <c r="C66">
-        <v>5.87</v>
+        <v>6.16</v>
       </c>
       <c r="D66">
         <f>C66*$B$3</f>
       </c>
       <c r="E66">
-        <v>707.56</v>
+        <v>727.91</v>
       </c>
       <c r="F66">
-        <v>491.8</v>
+        <v>488.13</v>
       </c>
       <c r="G66">
-        <v>474.15</v>
+        <v>477.27</v>
       </c>
       <c r="H66">
         <f>MIN(E66:G66)</f>
@@ -3294,22 +3294,22 @@
         <v>97</v>
       </c>
       <c r="B67">
-        <v>559</v>
+        <v>486</v>
       </c>
       <c r="C67">
-        <v>5.9</v>
+        <v>6.34</v>
       </c>
       <c r="D67">
         <f>C67*$B$3</f>
       </c>
       <c r="E67">
-        <v>680.58</v>
+        <v>780.43</v>
       </c>
       <c r="F67">
-        <v>504.29</v>
+        <v>499.75</v>
       </c>
       <c r="G67">
-        <v>484.11</v>
+        <v>502.53</v>
       </c>
       <c r="H67">
         <f>MIN(E67:G67)</f>
@@ -3332,22 +3332,22 @@
         <v>98</v>
       </c>
       <c r="B68">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="C68">
-        <v>6.14</v>
+        <v>5.89</v>
       </c>
       <c r="D68">
         <f>C68*$B$3</f>
       </c>
       <c r="E68">
-        <v>651.83</v>
+        <v>706.69</v>
       </c>
       <c r="F68">
-        <v>504.29</v>
+        <v>502.53</v>
       </c>
       <c r="G68">
-        <v>484.24</v>
+        <v>485.86</v>
       </c>
       <c r="H68">
         <f>MIN(E68:G68)</f>
@@ -3370,22 +3370,22 @@
         <v>99</v>
       </c>
       <c r="B69">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="C69">
-        <v>6.68</v>
+        <v>6.37</v>
       </c>
       <c r="D69">
         <f>C69*$B$3</f>
       </c>
       <c r="E69">
-        <v>760.02</v>
+        <v>629.42</v>
       </c>
       <c r="F69">
-        <v>487.89</v>
+        <v>459.98</v>
       </c>
       <c r="G69">
-        <v>490.29</v>
+        <v>465.78</v>
       </c>
       <c r="H69">
         <f>MIN(E69:G69)</f>
@@ -3408,22 +3408,22 @@
         <v>100</v>
       </c>
       <c r="B70">
-        <v>123</v>
+        <v>247</v>
       </c>
       <c r="C70">
-        <v>5.87</v>
+        <v>5.49</v>
       </c>
       <c r="D70">
         <f>C70*$B$3</f>
       </c>
       <c r="E70">
-        <v>732.15</v>
+        <v>659.22</v>
       </c>
       <c r="F70">
-        <v>469.1</v>
+        <v>415.53</v>
       </c>
       <c r="G70">
-        <v>434.05</v>
+        <v>404.04</v>
       </c>
       <c r="H70">
         <f>MIN(E70:G70)</f>
@@ -3446,22 +3446,22 @@
         <v>101</v>
       </c>
       <c r="B71">
-        <v>857</v>
+        <v>820</v>
       </c>
       <c r="C71">
-        <v>5.92</v>
+        <v>6.12</v>
       </c>
       <c r="D71">
         <f>C71*$B$3</f>
       </c>
       <c r="E71">
-        <v>687.26</v>
+        <v>719.45</v>
       </c>
       <c r="F71">
-        <v>509.46</v>
+        <v>512.25</v>
       </c>
       <c r="G71">
-        <v>506.93</v>
+        <v>500.89</v>
       </c>
       <c r="H71">
         <f>MIN(E71:G71)</f>
@@ -3484,22 +3484,22 @@
         <v>102</v>
       </c>
       <c r="B72">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C72">
-        <v>6.37</v>
+        <v>6.3</v>
       </c>
       <c r="D72">
         <f>C72*$B$3</f>
       </c>
       <c r="E72">
-        <v>774.4</v>
+        <v>665.91</v>
       </c>
       <c r="F72">
-        <v>499.37</v>
+        <v>517.68</v>
       </c>
       <c r="G72">
-        <v>468.98</v>
+        <v>464.65</v>
       </c>
       <c r="H72">
         <f>MIN(E72:G72)</f>
@@ -3522,22 +3522,22 @@
         <v>103</v>
       </c>
       <c r="B73">
-        <v>875</v>
+        <v>791</v>
       </c>
       <c r="C73">
-        <v>5.02</v>
+        <v>5.29</v>
       </c>
       <c r="D73">
         <f>C73*$B$3</f>
       </c>
       <c r="E73">
-        <v>641.61</v>
+        <v>624.37</v>
       </c>
       <c r="F73">
-        <v>413.62</v>
+        <v>405.94</v>
       </c>
       <c r="G73">
-        <v>414.25</v>
+        <v>403.28</v>
       </c>
       <c r="H73">
         <f>MIN(E73:G73)</f>
@@ -3560,22 +3560,22 @@
         <v>104</v>
       </c>
       <c r="B74">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="C74">
-        <v>5.98</v>
+        <v>5.57</v>
       </c>
       <c r="D74">
         <f>C74*$B$3</f>
       </c>
       <c r="E74">
-        <v>624.71</v>
+        <v>620.08</v>
       </c>
       <c r="F74">
-        <v>450.19</v>
+        <v>433.59</v>
       </c>
       <c r="G74">
-        <v>440.1</v>
+        <v>415.41</v>
       </c>
       <c r="H74">
         <f>MIN(E74:G74)</f>
@@ -3598,22 +3598,22 @@
         <v>105</v>
       </c>
       <c r="B75">
-        <v>379</v>
+        <v>326</v>
       </c>
       <c r="C75">
-        <v>5.11</v>
+        <v>5.27</v>
       </c>
       <c r="D75">
         <f>C75*$B$3</f>
       </c>
       <c r="E75">
-        <v>623.07</v>
+        <v>615.03</v>
       </c>
       <c r="F75">
-        <v>421.18</v>
+        <v>404.93</v>
       </c>
       <c r="G75">
-        <v>412.1</v>
+        <v>408.84</v>
       </c>
       <c r="H75">
         <f>MIN(E75:G75)</f>
@@ -3636,22 +3636,22 @@
         <v>106</v>
       </c>
       <c r="B76">
-        <v>776</v>
+        <v>703</v>
       </c>
       <c r="C76">
-        <v>4.38</v>
+        <v>4.16</v>
       </c>
       <c r="D76">
         <f>C76*$B$3</f>
       </c>
       <c r="E76">
-        <v>522.44</v>
+        <v>495.46</v>
       </c>
       <c r="F76">
-        <v>351.83</v>
+        <v>343.44</v>
       </c>
       <c r="G76">
-        <v>358.64</v>
+        <v>333.33</v>
       </c>
       <c r="H76">
         <f>MIN(E76:G76)</f>
@@ -3674,22 +3674,22 @@
         <v>107</v>
       </c>
       <c r="B77">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="C77">
-        <v>3.99</v>
+        <v>3.83</v>
       </c>
       <c r="D77">
         <f>C77*$B$3</f>
       </c>
       <c r="E77">
-        <v>470.87</v>
+        <v>395.33</v>
       </c>
       <c r="F77">
-        <v>291.55</v>
+        <v>282.2</v>
       </c>
       <c r="G77">
-        <v>300</v>
+        <v>287.88</v>
       </c>
       <c r="H77">
         <f>MIN(E77:G77)</f>
@@ -3712,22 +3712,22 @@
         <v>108</v>
       </c>
       <c r="B78">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C78">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="D78">
         <f>C78*$B$3</f>
       </c>
       <c r="E78">
-        <v>528.37</v>
+        <v>443.69</v>
       </c>
       <c r="F78">
-        <v>403.53</v>
+        <v>422.98</v>
       </c>
       <c r="G78">
-        <v>336.57</v>
+        <v>361.87</v>
       </c>
       <c r="H78">
         <f>MIN(E78:G78)</f>
@@ -3750,22 +3750,22 @@
         <v>109</v>
       </c>
       <c r="B79">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="C79">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="D79">
         <f>C79*$B$3</f>
       </c>
       <c r="E79">
-        <v>396.47</v>
+        <v>352.02</v>
       </c>
       <c r="F79">
-        <v>234.43</v>
+        <v>219.95</v>
       </c>
       <c r="G79">
-        <v>232.03</v>
+        <v>223.49</v>
       </c>
       <c r="H79">
         <f>MIN(E79:G79)</f>
@@ -3788,22 +3788,22 @@
         <v>110</v>
       </c>
       <c r="B80">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C80">
-        <v>5.04</v>
+        <v>4.68</v>
       </c>
       <c r="D80">
         <f>C80*$B$3</f>
       </c>
       <c r="E80">
-        <v>525.85</v>
+        <v>542.05</v>
       </c>
       <c r="F80">
-        <v>423.58</v>
+        <v>416.42</v>
       </c>
       <c r="G80">
-        <v>388.02</v>
+        <v>372.98</v>
       </c>
       <c r="H80">
         <f>MIN(E80:G80)</f>
@@ -3826,22 +3826,22 @@
         <v>111</v>
       </c>
       <c r="B81">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C81">
-        <v>4.72</v>
+        <v>4.57</v>
       </c>
       <c r="D81">
         <f>C81*$B$3</f>
       </c>
       <c r="E81">
-        <v>540.23</v>
+        <v>563.26</v>
       </c>
       <c r="F81">
-        <v>384.61</v>
+        <v>366.16</v>
       </c>
       <c r="G81">
-        <v>387.14</v>
+        <v>392.55</v>
       </c>
       <c r="H81">
         <f>MIN(E81:G81)</f>
@@ -3864,22 +3864,22 @@
         <v>112</v>
       </c>
       <c r="B82">
-        <v>497</v>
+        <v>404</v>
       </c>
       <c r="C82">
-        <v>5.27</v>
+        <v>5.81</v>
       </c>
       <c r="D82">
         <f>C82*$B$3</f>
       </c>
       <c r="E82">
-        <v>625.6</v>
+        <v>600.63</v>
       </c>
       <c r="F82">
-        <v>445.4</v>
+        <v>465.91</v>
       </c>
       <c r="G82">
-        <v>441.36</v>
+        <v>467.3</v>
       </c>
       <c r="H82">
         <f>MIN(E82:G82)</f>
@@ -3902,22 +3902,22 @@
         <v>113</v>
       </c>
       <c r="B83">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="C83">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="D83">
         <f>C83*$B$3</f>
       </c>
       <c r="E83">
-        <v>411.73</v>
+        <v>302.02</v>
       </c>
       <c r="F83">
-        <v>263.68</v>
+        <v>208.21</v>
       </c>
       <c r="G83">
-        <v>201.64</v>
+        <v>198.23</v>
       </c>
       <c r="H83">
         <f>MIN(E83:G83)</f>
@@ -3940,22 +3940,22 @@
         <v>115</v>
       </c>
       <c r="B84">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C84">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="D84">
         <f>C84*$B$3</f>
       </c>
       <c r="E84">
-        <v>475.91</v>
+        <v>435.23</v>
       </c>
       <c r="F84">
-        <v>335.43</v>
+        <v>321.97</v>
       </c>
       <c r="G84">
-        <v>277.43</v>
+        <v>322.6</v>
       </c>
       <c r="H84">
         <f>MIN(E84:G84)</f>
@@ -3978,22 +3978,22 @@
         <v>116</v>
       </c>
       <c r="B85">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C85">
-        <v>3.95</v>
+        <v>3.53</v>
       </c>
       <c r="D85">
         <f>C85*$B$3</f>
       </c>
       <c r="E85">
-        <v>400.76</v>
+        <v>381.69</v>
       </c>
       <c r="F85">
-        <v>326.48</v>
+        <v>294.7</v>
       </c>
       <c r="G85">
-        <v>325.35</v>
+        <v>295.46</v>
       </c>
       <c r="H85">
         <f>MIN(E85:G85)</f>
@@ -4016,22 +4016,22 @@
         <v>117</v>
       </c>
       <c r="B86">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C86">
-        <v>4.92</v>
+        <v>5.04</v>
       </c>
       <c r="D86">
         <f>C86*$B$3</f>
       </c>
       <c r="E86">
-        <v>560.53</v>
+        <v>508.08</v>
       </c>
       <c r="F86">
-        <v>365.32</v>
+        <v>438.13</v>
       </c>
       <c r="G86">
-        <v>361.92</v>
+        <v>412.88</v>
       </c>
       <c r="H86">
         <f>MIN(E86:G86)</f>
@@ -4054,22 +4054,22 @@
         <v>118</v>
       </c>
       <c r="B87">
-        <v>568</v>
+        <v>480</v>
       </c>
       <c r="C87">
-        <v>4.14</v>
+        <v>3.91</v>
       </c>
       <c r="D87">
         <f>C87*$B$3</f>
       </c>
       <c r="E87">
-        <v>502.14</v>
+        <v>459.72</v>
       </c>
       <c r="F87">
-        <v>298.74</v>
+        <v>347.22</v>
       </c>
       <c r="G87">
-        <v>298.86</v>
+        <v>315.66</v>
       </c>
       <c r="H87">
         <f>MIN(E87:G87)</f>
@@ -4092,22 +4092,22 @@
         <v>119</v>
       </c>
       <c r="B88">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C88">
-        <v>4.39</v>
+        <v>4.18</v>
       </c>
       <c r="D88">
         <f>C88*$B$3</f>
       </c>
       <c r="E88">
-        <v>442.12</v>
+        <v>412.25</v>
       </c>
       <c r="F88">
-        <v>347.92</v>
+        <v>335.86</v>
       </c>
       <c r="G88">
-        <v>301.01</v>
+        <v>317.93</v>
       </c>
       <c r="H88">
         <f>MIN(E88:G88)</f>
@@ -4130,22 +4130,22 @@
         <v>120</v>
       </c>
       <c r="B89">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="C89">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="D89">
         <f>C89*$B$3</f>
       </c>
       <c r="E89">
-        <v>462.42</v>
+        <v>441.92</v>
       </c>
       <c r="F89">
-        <v>416.14</v>
+        <v>415.53</v>
       </c>
       <c r="G89">
-        <v>277.43</v>
+        <v>325.63</v>
       </c>
       <c r="H89">
         <f>MIN(E89:G89)</f>
@@ -4168,22 +4168,22 @@
         <v>121</v>
       </c>
       <c r="B90">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C90">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="D90">
         <f>C90*$B$3</f>
       </c>
       <c r="E90">
-        <v>350.82</v>
+        <v>329.17</v>
       </c>
       <c r="F90">
-        <v>231.78</v>
+        <v>219.7</v>
       </c>
       <c r="G90">
-        <v>232.91</v>
+        <v>222.1</v>
       </c>
       <c r="H90">
         <f>MIN(E90:G90)</f>
@@ -4206,22 +4206,22 @@
         <v>122</v>
       </c>
       <c r="B91">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C91">
-        <v>4.22</v>
+        <v>4.08</v>
       </c>
       <c r="D91">
         <f>C91*$B$3</f>
       </c>
       <c r="E91">
-        <v>537.7</v>
+        <v>534.47</v>
       </c>
       <c r="F91">
-        <v>366.58</v>
+        <v>331.06</v>
       </c>
       <c r="G91">
-        <v>353.09</v>
+        <v>353.54</v>
       </c>
       <c r="H91">
         <f>MIN(E91:G91)</f>
@@ -4244,22 +4244,22 @@
         <v>123</v>
       </c>
       <c r="B92">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="C92">
-        <v>4.19</v>
+        <v>3.98</v>
       </c>
       <c r="D92">
         <f>C92*$B$3</f>
       </c>
       <c r="E92">
-        <v>493.69</v>
+        <v>565.78</v>
       </c>
       <c r="F92">
-        <v>332.91</v>
+        <v>338.26</v>
       </c>
       <c r="G92">
-        <v>327.87</v>
+        <v>327.02</v>
       </c>
       <c r="H92">
         <f>MIN(E92:G92)</f>
@@ -4282,7 +4282,7 @@
         <v>124</v>
       </c>
       <c r="B93">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="C93">
         <v>3.84</v>
@@ -4291,13 +4291,13 @@
         <f>C93*$B$3</f>
       </c>
       <c r="E93">
-        <v>468.35</v>
+        <v>483.59</v>
       </c>
       <c r="F93">
-        <v>351.7</v>
+        <v>334.47</v>
       </c>
       <c r="G93">
-        <v>337.96</v>
+        <v>325.51</v>
       </c>
       <c r="H93">
         <f>MIN(E93:G93)</f>
@@ -4320,22 +4320,22 @@
         <v>125</v>
       </c>
       <c r="B94">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="C94">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="D94">
         <f>C94*$B$3</f>
       </c>
       <c r="E94">
-        <v>345.77</v>
+        <v>345.2</v>
       </c>
       <c r="F94">
-        <v>224.46</v>
+        <v>226.01</v>
       </c>
       <c r="G94">
-        <v>219.42</v>
+        <v>208.84</v>
       </c>
       <c r="H94">
         <f>MIN(E94:G94)</f>
@@ -4358,22 +4358,22 @@
         <v>126</v>
       </c>
       <c r="B95">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C95">
-        <v>3.79</v>
+        <v>3.68</v>
       </c>
       <c r="D95">
         <f>C95*$B$3</f>
       </c>
       <c r="E95">
-        <v>502.14</v>
+        <v>439.4</v>
       </c>
       <c r="F95">
-        <v>316.52</v>
+        <v>314.39</v>
       </c>
       <c r="G95">
-        <v>304.79</v>
+        <v>297.98</v>
       </c>
       <c r="H95">
         <f>MIN(E95:G95)</f>
@@ -4396,22 +4396,22 @@
         <v>127</v>
       </c>
       <c r="B96">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C96">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="D96">
         <f>C96*$B$3</f>
       </c>
       <c r="E96">
-        <v>492.81</v>
+        <v>487.75</v>
       </c>
       <c r="F96">
-        <v>325.98</v>
+        <v>348.86</v>
       </c>
       <c r="G96">
-        <v>349.18</v>
+        <v>351.39</v>
       </c>
       <c r="H96">
         <f>MIN(E96:G96)</f>
@@ -4434,22 +4434,22 @@
         <v>128</v>
       </c>
       <c r="B97">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="C97">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="D97">
         <f>C97*$B$3</f>
       </c>
       <c r="E97">
-        <v>488.65</v>
+        <v>512.38</v>
       </c>
       <c r="F97">
-        <v>288.78</v>
+        <v>293.18</v>
       </c>
       <c r="G97">
-        <v>289.91</v>
+        <v>281.44</v>
       </c>
       <c r="H97">
         <f>MIN(E97:G97)</f>
@@ -4472,22 +4472,22 @@
         <v>129</v>
       </c>
       <c r="B98">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C98">
-        <v>3.78</v>
+        <v>3.02</v>
       </c>
       <c r="D98">
         <f>C98*$B$3</f>
       </c>
       <c r="E98">
-        <v>399.87</v>
+        <v>324.87</v>
       </c>
       <c r="F98">
-        <v>258.89</v>
+        <v>238.76</v>
       </c>
       <c r="G98">
-        <v>250.82</v>
+        <v>236.11</v>
       </c>
       <c r="H98">
         <f>MIN(E98:G98)</f>
@@ -4510,22 +4510,22 @@
         <v>130</v>
       </c>
       <c r="B99">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C99">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="D99">
         <f>C99*$B$3</f>
       </c>
       <c r="E99">
-        <v>544.39</v>
+        <v>432.58</v>
       </c>
       <c r="F99">
-        <v>301.39</v>
+        <v>273.74</v>
       </c>
       <c r="G99">
-        <v>271</v>
+        <v>267.68</v>
       </c>
       <c r="H99">
         <f>MIN(E99:G99)</f>
@@ -4548,22 +4548,22 @@
         <v>131</v>
       </c>
       <c r="B100">
-        <v>1013</v>
+        <v>851</v>
       </c>
       <c r="C100">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="D100">
         <f>C100*$B$3</f>
       </c>
       <c r="E100">
-        <v>429.38</v>
+        <v>443.69</v>
       </c>
       <c r="F100">
-        <v>322.82</v>
+        <v>324.5</v>
       </c>
       <c r="G100">
-        <v>324.08</v>
+        <v>331.44</v>
       </c>
       <c r="H100">
         <f>MIN(E100:G100)</f>
@@ -4586,22 +4586,22 @@
         <v>132</v>
       </c>
       <c r="B101">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="C101">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="D101">
         <f>C101*$B$3</f>
       </c>
       <c r="E101">
-        <v>459.9</v>
+        <v>357.07</v>
       </c>
       <c r="F101">
-        <v>276.54</v>
+        <v>313.26</v>
       </c>
       <c r="G101">
-        <v>270.74</v>
+        <v>294.19</v>
       </c>
       <c r="H101">
         <f>MIN(E101:G101)</f>
@@ -4624,22 +4624,22 @@
         <v>133</v>
       </c>
       <c r="B102">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C102">
-        <v>10.61</v>
+        <v>3.6</v>
       </c>
       <c r="D102">
         <f>C102*$B$3</f>
       </c>
       <c r="E102">
-        <v>420.18</v>
+        <v>416.54</v>
       </c>
       <c r="F102">
-        <v>303.4</v>
+        <v>250.88</v>
       </c>
       <c r="G102">
-        <v>244.51</v>
+        <v>237.12</v>
       </c>
       <c r="H102">
         <f>MIN(E102:G102)</f>
@@ -4662,22 +4662,22 @@
         <v>134</v>
       </c>
       <c r="B103">
-        <v>215</v>
+        <v>364</v>
       </c>
       <c r="C103">
-        <v>3.02</v>
+        <v>2.86</v>
       </c>
       <c r="D103">
         <f>C103*$B$3</f>
       </c>
       <c r="E103">
-        <v>354.98</v>
+        <v>287.5</v>
       </c>
       <c r="F103">
-        <v>239.6</v>
+        <v>239.9</v>
       </c>
       <c r="G103">
-        <v>235.18</v>
+        <v>236.49</v>
       </c>
       <c r="H103">
         <f>MIN(E103:G103)</f>
@@ -4700,22 +4700,22 @@
         <v>135</v>
       </c>
       <c r="B104">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C104">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="D104">
         <f>C104*$B$3</f>
       </c>
       <c r="E104">
-        <v>380.45</v>
+        <v>477.65</v>
       </c>
       <c r="F104">
-        <v>249.68</v>
+        <v>266.29</v>
       </c>
       <c r="G104">
-        <v>239.22</v>
+        <v>216.67</v>
       </c>
       <c r="H104">
         <f>MIN(E104:G104)</f>
@@ -4738,22 +4738,22 @@
         <v>136</v>
       </c>
       <c r="B105">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C105">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="D105">
         <f>C105*$B$3</f>
       </c>
       <c r="E105">
-        <v>422.7</v>
+        <v>482.7</v>
       </c>
       <c r="F105">
-        <v>258.51</v>
+        <v>262.37</v>
       </c>
       <c r="G105">
-        <v>250.82</v>
+        <v>294.19</v>
       </c>
       <c r="H105">
         <f>MIN(E105:G105)</f>
@@ -4776,22 +4776,22 @@
         <v>137</v>
       </c>
       <c r="B106">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C106">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="D106">
         <f>C106*$B$3</f>
       </c>
       <c r="E106">
-        <v>400.76</v>
+        <v>344.45</v>
       </c>
       <c r="F106">
-        <v>250.94</v>
+        <v>241.79</v>
       </c>
       <c r="G106">
-        <v>236.44</v>
+        <v>238.01</v>
       </c>
       <c r="H106">
         <f>MIN(E106:G106)</f>
@@ -4814,22 +4814,22 @@
         <v>138</v>
       </c>
       <c r="B107">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="C107">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="D107">
         <f>C107*$B$3</f>
       </c>
       <c r="E107">
-        <v>330.52</v>
+        <v>323.99</v>
       </c>
       <c r="F107">
-        <v>252.08</v>
+        <v>257.32</v>
       </c>
       <c r="G107">
-        <v>243.88</v>
+        <v>241.29</v>
       </c>
       <c r="H107">
         <f>MIN(E107:G107)</f>
@@ -4852,22 +4852,22 @@
         <v>139</v>
       </c>
       <c r="B108">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C108">
-        <v>2.77</v>
+        <v>4.49</v>
       </c>
       <c r="D108">
         <f>C108*$B$3</f>
       </c>
       <c r="E108">
-        <v>277.3</v>
+        <v>322.35</v>
       </c>
       <c r="F108">
-        <v>234.43</v>
+        <v>225.63</v>
       </c>
       <c r="G108">
-        <v>223.2</v>
+        <v>213.26</v>
       </c>
       <c r="H108">
         <f>MIN(E108:G108)</f>
@@ -4890,22 +4890,22 @@
         <v>140</v>
       </c>
       <c r="B109">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="C109">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="D109">
         <f>C109*$B$3</f>
       </c>
       <c r="E109">
-        <v>338.08</v>
+        <v>341.79</v>
       </c>
       <c r="F109">
-        <v>240.86</v>
+        <v>225.88</v>
       </c>
       <c r="G109">
-        <v>218.16</v>
+        <v>223.49</v>
       </c>
       <c r="H109">
         <f>MIN(E109:G109)</f>
@@ -4928,22 +4928,22 @@
         <v>141</v>
       </c>
       <c r="B110">
-        <v>399</v>
+        <v>348</v>
       </c>
       <c r="C110">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="D110">
         <f>C110*$B$3</f>
       </c>
       <c r="E110">
-        <v>331.4</v>
+        <v>324.87</v>
       </c>
       <c r="F110">
-        <v>235.81</v>
+        <v>228.54</v>
       </c>
       <c r="G110">
-        <v>214.38</v>
+        <v>228.54</v>
       </c>
       <c r="H110">
         <f>MIN(E110:G110)</f>
@@ -4966,22 +4966,22 @@
         <v>142</v>
       </c>
       <c r="B111">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C111">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="D111">
         <f>C111*$B$3</f>
       </c>
       <c r="E111">
-        <v>337.33</v>
+        <v>341.79</v>
       </c>
       <c r="F111">
-        <v>220.55</v>
+        <v>231.82</v>
       </c>
       <c r="G111">
-        <v>221.82</v>
+        <v>229.8</v>
       </c>
       <c r="H111">
         <f>MIN(E111:G111)</f>
@@ -5004,22 +5004,22 @@
         <v>143</v>
       </c>
       <c r="B112">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C112">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="D112">
         <f>C112*$B$3</f>
       </c>
       <c r="E112">
-        <v>278.06</v>
+        <v>270.58</v>
       </c>
       <c r="F112">
-        <v>182.85</v>
+        <v>185.99</v>
       </c>
       <c r="G112">
-        <v>194.32</v>
+        <v>187.75</v>
       </c>
       <c r="H112">
         <f>MIN(E112:G112)</f>
@@ -5042,22 +5042,22 @@
         <v>144</v>
       </c>
       <c r="B113">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C113">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="D113">
         <f>C113*$B$3</f>
       </c>
       <c r="E113">
-        <v>323.71</v>
+        <v>302.02</v>
       </c>
       <c r="F113">
-        <v>233.29</v>
+        <v>239.77</v>
       </c>
       <c r="G113">
-        <v>228.88</v>
+        <v>233.59</v>
       </c>
       <c r="H113">
         <f>MIN(E113:G113)</f>
@@ -5080,22 +5080,22 @@
         <v>145</v>
       </c>
       <c r="B114">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C114">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="D114">
         <f>C114*$B$3</f>
       </c>
       <c r="E114">
-        <v>308.57</v>
+        <v>297.73</v>
       </c>
       <c r="F114">
-        <v>211.35</v>
+        <v>214.65</v>
       </c>
       <c r="G114">
-        <v>217.53</v>
+        <v>212.75</v>
       </c>
       <c r="H114">
         <f>MIN(E114:G114)</f>
@@ -5118,22 +5118,22 @@
         <v>146</v>
       </c>
       <c r="B115">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C115">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="D115">
         <f>C115*$B$3</f>
       </c>
       <c r="E115">
-        <v>357.63</v>
+        <v>285.86</v>
       </c>
       <c r="F115">
-        <v>162.67</v>
+        <v>190.03</v>
       </c>
       <c r="G115">
-        <v>180.33</v>
+        <v>189.39</v>
       </c>
       <c r="H115">
         <f>MIN(E115:G115)</f>
@@ -5156,22 +5156,22 @@
         <v>147</v>
       </c>
       <c r="B116">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C116">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="D116">
         <f>C116*$B$3</f>
       </c>
       <c r="E116">
-        <v>236.7</v>
+        <v>202.65</v>
       </c>
       <c r="F116">
-        <v>180.33</v>
+        <v>163.01</v>
       </c>
       <c r="G116">
-        <v>192.94</v>
+        <v>175.38</v>
       </c>
       <c r="H116">
         <f>MIN(E116:G116)</f>
@@ -5194,22 +5194,22 @@
         <v>148</v>
       </c>
       <c r="B117">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C117">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="D117">
         <f>C117*$B$3</f>
       </c>
       <c r="E117">
-        <v>253.59</v>
+        <v>250.25</v>
       </c>
       <c r="F117">
-        <v>179.44</v>
+        <v>181.82</v>
       </c>
       <c r="G117">
-        <v>168.98</v>
+        <v>175.13</v>
       </c>
       <c r="H117">
         <f>MIN(E117:G117)</f>
@@ -5232,22 +5232,22 @@
         <v>149</v>
       </c>
       <c r="B118">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C118">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="D118">
         <f>C118*$B$3</f>
       </c>
       <c r="E118">
-        <v>312.74</v>
+        <v>296.09</v>
       </c>
       <c r="F118">
-        <v>223.45</v>
+        <v>222.22</v>
       </c>
       <c r="G118">
-        <v>225.6</v>
+        <v>219.7</v>
       </c>
       <c r="H118">
         <f>MIN(E118:G118)</f>
@@ -5270,22 +5270,22 @@
         <v>150</v>
       </c>
       <c r="B119">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="C119">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="D119">
         <f>C119*$B$3</f>
       </c>
       <c r="E119">
-        <v>272.13</v>
+        <v>287.5</v>
       </c>
       <c r="F119">
-        <v>206.81</v>
+        <v>202.9</v>
       </c>
       <c r="G119">
-        <v>203.4</v>
+        <v>190.53</v>
       </c>
       <c r="H119">
         <f>MIN(E119:G119)</f>
@@ -5308,22 +5308,22 @@
         <v>151</v>
       </c>
       <c r="B120">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="C120">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="D120">
         <f>C120*$B$3</f>
       </c>
       <c r="E120">
-        <v>305.17</v>
+        <v>255.3</v>
       </c>
       <c r="F120">
-        <v>171.63</v>
+        <v>166.67</v>
       </c>
       <c r="G120">
-        <v>163.81</v>
+        <v>162.88</v>
       </c>
       <c r="H120">
         <f>MIN(E120:G120)</f>
@@ -5346,22 +5346,22 @@
         <v>152</v>
       </c>
       <c r="B121">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C121">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="D121">
         <f>C121*$B$3</f>
       </c>
       <c r="E121">
-        <v>321.18</v>
+        <v>296.84</v>
       </c>
       <c r="F121">
-        <v>200.5</v>
+        <v>198.11</v>
       </c>
       <c r="G121">
-        <v>211.85</v>
+        <v>220.96</v>
       </c>
       <c r="H121">
         <f>MIN(E121:G121)</f>
@@ -5384,22 +5384,22 @@
         <v>153</v>
       </c>
       <c r="B122">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C122">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="D122">
         <f>C122*$B$3</f>
       </c>
       <c r="E122">
-        <v>242.62</v>
+        <v>247.73</v>
       </c>
       <c r="F122">
-        <v>153.34</v>
+        <v>145.2</v>
       </c>
       <c r="G122">
-        <v>172.76</v>
+        <v>168.81</v>
       </c>
       <c r="H122">
         <f>MIN(E122:G122)</f>
@@ -5422,22 +5422,22 @@
         <v>154</v>
       </c>
       <c r="B123">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C123">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="D123">
         <f>C123*$B$3</f>
       </c>
       <c r="E123">
-        <v>142.87</v>
+        <v>169.57</v>
       </c>
       <c r="F123">
-        <v>130.89</v>
+        <v>113.51</v>
       </c>
       <c r="G123">
-        <v>111.85</v>
+        <v>113.76</v>
       </c>
       <c r="H123">
         <f>MIN(E123:G123)</f>
@@ -5460,22 +5460,22 @@
         <v>155</v>
       </c>
       <c r="B124">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C124">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="D124">
         <f>C124*$B$3</f>
       </c>
       <c r="E124">
-        <v>245.14</v>
+        <v>251.01</v>
       </c>
       <c r="F124">
-        <v>167.46</v>
+        <v>179.17</v>
       </c>
       <c r="G124">
-        <v>162.67</v>
+        <v>166.54</v>
       </c>
       <c r="H124">
         <f>MIN(E124:G124)</f>
@@ -5498,22 +5498,22 @@
         <v>156</v>
       </c>
       <c r="B125">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C125">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="D125">
         <f>C125*$B$3</f>
       </c>
       <c r="E125">
-        <v>196.97</v>
+        <v>190.03</v>
       </c>
       <c r="F125">
-        <v>142.24</v>
+        <v>138.51</v>
       </c>
       <c r="G125">
-        <v>126.86</v>
+        <v>125.25</v>
       </c>
       <c r="H125">
         <f>MIN(E125:G125)</f>
@@ -5536,22 +5536,22 @@
         <v>157</v>
       </c>
       <c r="B126">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C126">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="D126">
         <f>C126*$B$3</f>
       </c>
       <c r="E126">
-        <v>140.23</v>
+        <v>110.23</v>
       </c>
       <c r="F126">
-        <v>105.93</v>
+        <v>94.44</v>
       </c>
       <c r="G126">
-        <v>100.88</v>
+        <v>90.15</v>
       </c>
       <c r="H126">
         <f>MIN(E126:G126)</f>
@@ -5574,22 +5574,22 @@
         <v>158</v>
       </c>
       <c r="B127">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="C127">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="D127">
         <f>C127*$B$3</f>
       </c>
       <c r="E127">
-        <v>145.4</v>
+        <v>207.83</v>
       </c>
       <c r="F127">
-        <v>111.73</v>
+        <v>104.04</v>
       </c>
       <c r="G127">
-        <v>103.28</v>
+        <v>104.67</v>
       </c>
       <c r="H127">
         <f>MIN(E127:G127)</f>
@@ -5612,22 +5612,22 @@
         <v>159</v>
       </c>
       <c r="B128">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="C128">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="D128">
         <f>C128*$B$3</f>
       </c>
       <c r="E128">
-        <v>145.4</v>
+        <v>130.56</v>
       </c>
       <c r="F128">
-        <v>89.79</v>
+        <v>92.68</v>
       </c>
       <c r="G128">
-        <v>89.15</v>
+        <v>88.26</v>
       </c>
       <c r="H128">
         <f>MIN(E128:G128)</f>
@@ -5650,22 +5650,22 @@
         <v>160</v>
       </c>
       <c r="B129">
-        <v>269</v>
+        <v>222</v>
       </c>
       <c r="C129">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="D129">
         <f>C129*$B$3</f>
       </c>
       <c r="E129">
-        <v>109.84</v>
+        <v>112.75</v>
       </c>
       <c r="F129">
-        <v>80.83</v>
+        <v>86.62</v>
       </c>
       <c r="G129">
-        <v>88.02</v>
+        <v>87.12</v>
       </c>
       <c r="H129">
         <f>MIN(E129:G129)</f>
@@ -5688,22 +5688,22 @@
         <v>161</v>
       </c>
       <c r="B130">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C130">
-        <v>1.03</v>
+        <v>0.91</v>
       </c>
       <c r="D130">
         <f>C130*$B$3</f>
       </c>
       <c r="E130">
-        <v>99.75</v>
+        <v>107.7</v>
       </c>
       <c r="F130">
-        <v>74.91</v>
+        <v>73.61</v>
       </c>
       <c r="G130">
-        <v>74.02</v>
+        <v>73.99</v>
       </c>
       <c r="H130">
         <f>MIN(E130:G130)</f>
@@ -5726,22 +5726,22 @@
         <v>162</v>
       </c>
       <c r="B131">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="C131">
-        <v>0.73</v>
+        <v>0.81</v>
       </c>
       <c r="D131">
         <f>C131*$B$3</f>
       </c>
       <c r="E131">
-        <v>92.94</v>
+        <v>92.42</v>
       </c>
       <c r="F131">
-        <v>63.81</v>
+        <v>63.01</v>
       </c>
       <c r="G131">
-        <v>61.16</v>
+        <v>62.88</v>
       </c>
       <c r="H131">
         <f>MIN(E131:G131)</f>
@@ -5764,22 +5764,22 @@
         <v>163</v>
       </c>
       <c r="B132">
-        <v>1028</v>
+        <v>991</v>
       </c>
       <c r="C132">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="D132">
         <f>C132*$B$3</f>
       </c>
       <c r="E132">
-        <v>114.12</v>
+        <v>119.57</v>
       </c>
       <c r="F132">
-        <v>75.41</v>
+        <v>74.24</v>
       </c>
       <c r="G132">
-        <v>81.59</v>
+        <v>75.51</v>
       </c>
       <c r="H132">
         <f>MIN(E132:G132)</f>
@@ -5802,22 +5802,22 @@
         <v>164</v>
       </c>
       <c r="B133">
-        <v>682</v>
+        <v>748</v>
       </c>
       <c r="C133">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="D133">
         <f>C133*$B$3</f>
       </c>
       <c r="E133">
-        <v>65.07</v>
+        <v>68.69</v>
       </c>
       <c r="F133">
-        <v>43.88</v>
+        <v>41.16</v>
       </c>
       <c r="G133">
-        <v>46.41</v>
+        <v>41.67</v>
       </c>
       <c r="H133">
         <f>MIN(E133:G133)</f>
@@ -5840,7 +5840,7 @@
         <v>165</v>
       </c>
       <c r="B134">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="C134">
         <v>0.63</v>
@@ -5849,13 +5849,13 @@
         <f>C134*$B$3</f>
       </c>
       <c r="E134">
-        <v>87.01</v>
+        <v>70.33</v>
       </c>
       <c r="F134">
-        <v>52.21</v>
+        <v>52.78</v>
       </c>
       <c r="G134">
-        <v>49.94</v>
+        <v>50.38</v>
       </c>
       <c r="H134">
         <f>MIN(E134:G134)</f>
@@ -5878,22 +5878,22 @@
         <v>166</v>
       </c>
       <c r="B135">
-        <v>287</v>
+        <v>329</v>
       </c>
       <c r="C135">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="D135">
         <f>C135*$B$3</f>
       </c>
       <c r="E135">
-        <v>53.22</v>
+        <v>43.18</v>
       </c>
       <c r="F135">
-        <v>33.8</v>
+        <v>35.1</v>
       </c>
       <c r="G135">
-        <v>40.61</v>
+        <v>32.32</v>
       </c>
       <c r="H135">
         <f>MIN(E135:G135)</f>
@@ -5916,22 +5916,22 @@
         <v>167</v>
       </c>
       <c r="B136">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C136">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="D136">
         <f>C136*$B$3</f>
       </c>
       <c r="E136">
-        <v>51.45</v>
+        <v>51.64</v>
       </c>
       <c r="F136">
-        <v>30.52</v>
+        <v>30.56</v>
       </c>
       <c r="G136">
-        <v>30.39</v>
+        <v>31.06</v>
       </c>
       <c r="H136">
         <f>MIN(E136:G136)</f>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="83">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 28.09.2026 17:06</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 28.09.2026 17:17</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -730,7 +730,7 @@
         <f>C6*$B$3</f>
       </c>
       <c r="E6">
-        <v>2871.85</v>
+        <v>3298.62</v>
       </c>
       <c r="F6">
         <v>2152.15</v>
@@ -809,7 +809,7 @@
         <v>2375.51</v>
       </c>
       <c r="F8">
-        <v>1736.12</v>
+        <v>1729.8</v>
       </c>
       <c r="G8">
         <v>1723.49</v>
@@ -835,7 +835,7 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C9">
         <v>12.86</v>
@@ -911,7 +911,7 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11">
         <v>24.89</v>
@@ -987,7 +987,7 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13">
         <v>8.89</v>
@@ -1025,7 +1025,7 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C14">
         <v>6.27</v>
@@ -1072,10 +1072,10 @@
         <f>C15*$B$3</f>
       </c>
       <c r="E15">
-        <v>4197.99</v>
+        <v>4225.9</v>
       </c>
       <c r="F15">
-        <v>3301.4</v>
+        <v>3307.71</v>
       </c>
       <c r="G15">
         <v>3290.16</v>
@@ -1101,7 +1101,7 @@
         <v>33</v>
       </c>
       <c r="B16">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C16">
         <v>2.72</v>
@@ -1113,7 +1113,7 @@
         <v>345.2</v>
       </c>
       <c r="F16">
-        <v>226.01</v>
+        <v>224.75</v>
       </c>
       <c r="G16">
         <v>208.84</v>
@@ -1151,7 +1151,7 @@
         <v>990.03</v>
       </c>
       <c r="F17">
-        <v>691.92</v>
+        <v>693.18</v>
       </c>
       <c r="G17">
         <v>679.29</v>
@@ -1265,7 +1265,7 @@
         <v>381.69</v>
       </c>
       <c r="F20">
-        <v>294.7</v>
+        <v>294.45</v>
       </c>
       <c r="G20">
         <v>295.46</v>
@@ -1341,7 +1341,7 @@
         <v>477.65</v>
       </c>
       <c r="F22">
-        <v>266.29</v>
+        <v>265.91</v>
       </c>
       <c r="G22">
         <v>216.67</v>
@@ -1443,7 +1443,7 @@
         <v>45</v>
       </c>
       <c r="B25">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C25">
         <v>5.49</v>
@@ -1572,7 +1572,7 @@
         <v>335.86</v>
       </c>
       <c r="G28">
-        <v>317.93</v>
+        <v>317.8</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1645,7 +1645,7 @@
         <v>508.08</v>
       </c>
       <c r="F30">
-        <v>438.13</v>
+        <v>440.53</v>
       </c>
       <c r="G30">
         <v>412.88</v>
@@ -1785,10 +1785,10 @@
         <v>54</v>
       </c>
       <c r="B34">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C34">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
@@ -1861,7 +1861,7 @@
         <v>56</v>
       </c>
       <c r="B36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C36">
         <v>3.16</v>
@@ -1911,7 +1911,7 @@
         <v>341.79</v>
       </c>
       <c r="F37">
-        <v>231.82</v>
+        <v>232.07</v>
       </c>
       <c r="G37">
         <v>229.8</v>
@@ -1978,16 +1978,16 @@
         <v>701</v>
       </c>
       <c r="C39">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
       </c>
       <c r="E39">
-        <v>495.46</v>
+        <v>497.1</v>
       </c>
       <c r="F39">
-        <v>343.44</v>
+        <v>342.17</v>
       </c>
       <c r="G39">
         <v>333.33</v>
@@ -2013,7 +2013,7 @@
         <v>60</v>
       </c>
       <c r="B40">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C40">
         <v>2.65</v>
@@ -2022,7 +2022,7 @@
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>302.02</v>
+        <v>305.43</v>
       </c>
       <c r="F40">
         <v>239.77</v>
@@ -2051,7 +2051,7 @@
         <v>61</v>
       </c>
       <c r="B41">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C41">
         <v>7.38</v>
@@ -2060,13 +2060,13 @@
         <f>C41*$B$3</f>
       </c>
       <c r="E41">
-        <v>894.19</v>
+        <v>805.94</v>
       </c>
       <c r="F41">
         <v>630.05</v>
       </c>
       <c r="G41">
-        <v>651.39</v>
+        <v>650.13</v>
       </c>
       <c r="H41">
         <f>MIN(E41:G41)</f>
@@ -2092,7 +2092,7 @@
         <v>94</v>
       </c>
       <c r="C42">
-        <v>11.64</v>
+        <v>11.66</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
@@ -2104,7 +2104,7 @@
         <v>972.23</v>
       </c>
       <c r="G42">
-        <v>982.33</v>
+        <v>978.54</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2127,19 +2127,19 @@
         <v>64</v>
       </c>
       <c r="B43">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C43">
-        <v>5.91</v>
+        <v>6.05</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>719.45</v>
+        <v>734.72</v>
       </c>
       <c r="F43">
-        <v>512.25</v>
+        <v>513.51</v>
       </c>
       <c r="G43">
         <v>500.89</v>
@@ -2165,7 +2165,7 @@
         <v>65</v>
       </c>
       <c r="B44">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="C44">
         <v>3.79</v>
@@ -2174,13 +2174,13 @@
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>443.69</v>
+        <v>451.26</v>
       </c>
       <c r="F44">
-        <v>324.5</v>
+        <v>315.66</v>
       </c>
       <c r="G44">
-        <v>331.44</v>
+        <v>331.31</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2393,7 +2393,7 @@
         <v>71</v>
       </c>
       <c r="B50">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C50">
         <v>2.15</v>
@@ -2431,7 +2431,7 @@
         <v>72</v>
       </c>
       <c r="B51">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C51">
         <v>3.84</v>
@@ -2440,7 +2440,7 @@
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>483.59</v>
+        <v>485.23</v>
       </c>
       <c r="F51">
         <v>334.47</v>
@@ -2469,7 +2469,7 @@
         <v>73</v>
       </c>
       <c r="B52">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C52">
         <v>1.94</v>
@@ -2507,7 +2507,7 @@
         <v>74</v>
       </c>
       <c r="B53">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C53">
         <v>2.68</v>
@@ -2557,7 +2557,7 @@
         <v>905.18</v>
       </c>
       <c r="F54">
-        <v>628.79</v>
+        <v>627.53</v>
       </c>
       <c r="G54">
         <v>649.12</v>
@@ -2782,10 +2782,10 @@
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>563.26</v>
+        <v>521.72</v>
       </c>
       <c r="F60">
-        <v>366.16</v>
+        <v>377.53</v>
       </c>
       <c r="G60">
         <v>392.55</v>
@@ -2811,16 +2811,16 @@
         <v>82</v>
       </c>
       <c r="B61">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C61">
-        <v>7.04</v>
+        <v>7.05</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>765.15</v>
+        <v>753.29</v>
       </c>
       <c r="F61">
         <v>586.49</v>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="83">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 28.09.2026 17:17</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 02.10.2026 15:08</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -666,7 +666,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>84.3414</v>
+        <v>83.2454</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -675,7 +675,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>12.6263</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -721,22 +721,22 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C6">
-        <v>26.4</v>
+        <v>26.41</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
       </c>
       <c r="E6">
-        <v>3298.62</v>
+        <v>2843.63</v>
       </c>
       <c r="F6">
-        <v>2152.15</v>
+        <v>2110</v>
       </c>
       <c r="G6">
-        <v>2167.94</v>
+        <v>2096.25</v>
       </c>
       <c r="H6">
         <f>MIN(E6:G6)</f>
@@ -759,22 +759,22 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="C7">
-        <v>16.78</v>
+        <v>17.31</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
       </c>
       <c r="E7">
-        <v>1800.26</v>
+        <v>1930.38</v>
       </c>
       <c r="F7">
-        <v>1309.22</v>
+        <v>1369.13</v>
       </c>
       <c r="G7">
-        <v>1357.33</v>
+        <v>1425</v>
       </c>
       <c r="H7">
         <f>MIN(E7:G7)</f>
@@ -797,22 +797,22 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C8">
-        <v>22.37</v>
+        <v>20.76</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
       </c>
       <c r="E8">
-        <v>2375.51</v>
+        <v>2306.38</v>
       </c>
       <c r="F8">
-        <v>1729.8</v>
+        <v>1699.63</v>
       </c>
       <c r="G8">
-        <v>1723.49</v>
+        <v>1518.75</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -835,22 +835,22 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C9">
-        <v>12.86</v>
+        <v>12.64</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
       </c>
       <c r="E9">
-        <v>1611.12</v>
+        <v>1539.25</v>
       </c>
       <c r="F9">
-        <v>1007.33</v>
+        <v>983.75</v>
       </c>
       <c r="G9">
-        <v>991.04</v>
+        <v>932.63</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -873,22 +873,22 @@
         <v>26</v>
       </c>
       <c r="B10">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="C10">
-        <v>36.65</v>
+        <v>33.41</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
       </c>
       <c r="E10">
-        <v>4326.02</v>
+        <v>3971.63</v>
       </c>
       <c r="F10">
-        <v>3027.79</v>
+        <v>2699.88</v>
       </c>
       <c r="G10">
-        <v>2929.3</v>
+        <v>2711.75</v>
       </c>
       <c r="H10">
         <f>MIN(E10:G10)</f>
@@ -911,22 +911,22 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C11">
-        <v>24.89</v>
+        <v>24.16</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
       </c>
       <c r="E11">
-        <v>2899.88</v>
+        <v>2728.63</v>
       </c>
       <c r="F11">
-        <v>2058.09</v>
+        <v>1967.37</v>
       </c>
       <c r="G11">
-        <v>2056.82</v>
+        <v>1967.25</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -949,22 +949,22 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C12">
-        <v>17.11</v>
+        <v>16.4</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
       </c>
       <c r="E12">
-        <v>1723.11</v>
+        <v>1685.25</v>
       </c>
       <c r="F12">
-        <v>1325.76</v>
+        <v>1312.5</v>
       </c>
       <c r="G12">
-        <v>1375</v>
+        <v>1406.25</v>
       </c>
       <c r="H12">
         <f>MIN(E12:G12)</f>
@@ -987,22 +987,22 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C13">
-        <v>8.89</v>
+        <v>8.75</v>
       </c>
       <c r="D13">
         <f>C13*$B$3</f>
       </c>
       <c r="E13">
-        <v>967.17</v>
+        <v>953.38</v>
       </c>
       <c r="F13">
-        <v>767.81</v>
+        <v>746.38</v>
       </c>
       <c r="G13">
-        <v>732.2</v>
+        <v>707</v>
       </c>
       <c r="H13">
         <f>MIN(E13:G13)</f>
@@ -1025,22 +1025,22 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="C14">
-        <v>6.27</v>
+        <v>6.19</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
       </c>
       <c r="E14">
-        <v>868.69</v>
+        <v>859.38</v>
       </c>
       <c r="F14">
-        <v>503.79</v>
+        <v>500</v>
       </c>
       <c r="G14">
-        <v>511.24</v>
+        <v>510.5</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1063,22 +1063,22 @@
         <v>32</v>
       </c>
       <c r="B15">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="C15">
-        <v>39.94</v>
+        <v>39.07</v>
       </c>
       <c r="D15">
         <f>C15*$B$3</f>
       </c>
       <c r="E15">
-        <v>4225.9</v>
+        <v>4196.63</v>
       </c>
       <c r="F15">
-        <v>3307.71</v>
+        <v>3137.5</v>
       </c>
       <c r="G15">
-        <v>3290.16</v>
+        <v>3159.25</v>
       </c>
       <c r="H15">
         <f>MIN(E15:G15)</f>
@@ -1101,7 +1101,7 @@
         <v>33</v>
       </c>
       <c r="B16">
-        <v>694</v>
+        <v>624</v>
       </c>
       <c r="C16">
         <v>2.72</v>
@@ -1110,13 +1110,13 @@
         <f>C16*$B$3</f>
       </c>
       <c r="E16">
-        <v>345.2</v>
+        <v>323.13</v>
       </c>
       <c r="F16">
-        <v>224.75</v>
+        <v>211.25</v>
       </c>
       <c r="G16">
-        <v>208.84</v>
+        <v>217.5</v>
       </c>
       <c r="H16">
         <f>MIN(E16:G16)</f>
@@ -1139,22 +1139,22 @@
         <v>34</v>
       </c>
       <c r="B17">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C17">
-        <v>8.72</v>
+        <v>8.21</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
       </c>
       <c r="E17">
-        <v>990.03</v>
+        <v>820.75</v>
       </c>
       <c r="F17">
-        <v>693.18</v>
+        <v>670</v>
       </c>
       <c r="G17">
-        <v>679.29</v>
+        <v>643.75</v>
       </c>
       <c r="H17">
         <f>MIN(E17:G17)</f>
@@ -1177,22 +1177,22 @@
         <v>37</v>
       </c>
       <c r="B18">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C18">
-        <v>6.13</v>
+        <v>6.15</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
       </c>
       <c r="E18">
-        <v>772.86</v>
+        <v>766.25</v>
       </c>
       <c r="F18">
-        <v>516.54</v>
+        <v>572.5</v>
       </c>
       <c r="G18">
-        <v>530.3</v>
+        <v>492.5</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1215,22 +1215,22 @@
         <v>38</v>
       </c>
       <c r="B19">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="C19">
-        <v>5.57</v>
+        <v>5.36</v>
       </c>
       <c r="D19">
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>620.08</v>
+        <v>610.13</v>
       </c>
       <c r="F19">
-        <v>433.59</v>
+        <v>417</v>
       </c>
       <c r="G19">
-        <v>415.41</v>
+        <v>391</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1253,22 +1253,22 @@
         <v>39</v>
       </c>
       <c r="B20">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="C20">
-        <v>3.53</v>
+        <v>3.41</v>
       </c>
       <c r="D20">
         <f>C20*$B$3</f>
       </c>
       <c r="E20">
-        <v>381.69</v>
+        <v>372.63</v>
       </c>
       <c r="F20">
-        <v>294.45</v>
+        <v>261</v>
       </c>
       <c r="G20">
-        <v>295.46</v>
+        <v>269</v>
       </c>
       <c r="H20">
         <f>MIN(E20:G20)</f>
@@ -1291,22 +1291,22 @@
         <v>40</v>
       </c>
       <c r="B21">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C21">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="D21">
         <f>C21*$B$3</f>
       </c>
       <c r="E21">
-        <v>534.47</v>
+        <v>492.62</v>
       </c>
       <c r="F21">
-        <v>331.06</v>
+        <v>319</v>
       </c>
       <c r="G21">
-        <v>353.54</v>
+        <v>325</v>
       </c>
       <c r="H21">
         <f>MIN(E21:G21)</f>
@@ -1329,22 +1329,22 @@
         <v>41</v>
       </c>
       <c r="B22">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C22">
-        <v>2.93</v>
+        <v>8.91</v>
       </c>
       <c r="D22">
         <f>C22*$B$3</f>
       </c>
       <c r="E22">
-        <v>477.65</v>
+        <v>450.62</v>
       </c>
       <c r="F22">
-        <v>265.91</v>
+        <v>224.13</v>
       </c>
       <c r="G22">
-        <v>216.67</v>
+        <v>217.5</v>
       </c>
       <c r="H22">
         <f>MIN(E22:G22)</f>
@@ -1367,22 +1367,22 @@
         <v>42</v>
       </c>
       <c r="B23">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C23">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="D23">
         <f>C23*$B$3</f>
       </c>
       <c r="E23">
-        <v>482.7</v>
+        <v>397.75</v>
       </c>
       <c r="F23">
-        <v>262.37</v>
+        <v>255.63</v>
       </c>
       <c r="G23">
-        <v>294.19</v>
+        <v>259.88</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1405,22 +1405,22 @@
         <v>43</v>
       </c>
       <c r="B24">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="C24">
-        <v>6.37</v>
+        <v>5.96</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
       </c>
       <c r="E24">
-        <v>629.42</v>
+        <v>593.38</v>
       </c>
       <c r="F24">
-        <v>459.98</v>
+        <v>451.13</v>
       </c>
       <c r="G24">
-        <v>465.78</v>
+        <v>438.12</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1443,22 +1443,22 @@
         <v>45</v>
       </c>
       <c r="B25">
-        <v>245</v>
+        <v>292</v>
       </c>
       <c r="C25">
-        <v>5.49</v>
+        <v>5.61</v>
       </c>
       <c r="D25">
         <f>C25*$B$3</f>
       </c>
       <c r="E25">
-        <v>659.22</v>
+        <v>595</v>
       </c>
       <c r="F25">
-        <v>415.53</v>
+        <v>440.63</v>
       </c>
       <c r="G25">
-        <v>404.04</v>
+        <v>429.88</v>
       </c>
       <c r="H25">
         <f>MIN(E25:G25)</f>
@@ -1481,22 +1481,22 @@
         <v>46</v>
       </c>
       <c r="B26">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26">
-        <v>6.3</v>
+        <v>6.35</v>
       </c>
       <c r="D26">
         <f>C26*$B$3</f>
       </c>
       <c r="E26">
-        <v>665.91</v>
+        <v>658</v>
       </c>
       <c r="F26">
-        <v>517.68</v>
+        <v>498.75</v>
       </c>
       <c r="G26">
-        <v>464.65</v>
+        <v>462.5</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1519,22 +1519,22 @@
         <v>47</v>
       </c>
       <c r="B27">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="C27">
-        <v>4.68</v>
+        <v>4.71</v>
       </c>
       <c r="D27">
         <f>C27*$B$3</f>
       </c>
       <c r="E27">
-        <v>542.05</v>
+        <v>466.63</v>
       </c>
       <c r="F27">
-        <v>416.42</v>
+        <v>352.5</v>
       </c>
       <c r="G27">
-        <v>372.98</v>
+        <v>342.38</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1557,22 +1557,22 @@
         <v>48</v>
       </c>
       <c r="B28">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C28">
-        <v>4.18</v>
+        <v>3.76</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
       </c>
       <c r="E28">
-        <v>412.25</v>
+        <v>502.75</v>
       </c>
       <c r="F28">
-        <v>335.86</v>
+        <v>275.63</v>
       </c>
       <c r="G28">
-        <v>317.8</v>
+        <v>273.38</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1595,22 +1595,22 @@
         <v>49</v>
       </c>
       <c r="B29">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C29">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
       </c>
       <c r="E29">
-        <v>443.69</v>
+        <v>499.38</v>
       </c>
       <c r="F29">
-        <v>422.98</v>
+        <v>396.25</v>
       </c>
       <c r="G29">
-        <v>361.87</v>
+        <v>348</v>
       </c>
       <c r="H29">
         <f>MIN(E29:G29)</f>
@@ -1633,22 +1633,22 @@
         <v>50</v>
       </c>
       <c r="B30">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C30">
-        <v>5.04</v>
+        <v>4.76</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
       </c>
       <c r="E30">
-        <v>508.08</v>
+        <v>419.63</v>
       </c>
       <c r="F30">
-        <v>440.53</v>
+        <v>385</v>
       </c>
       <c r="G30">
-        <v>412.88</v>
+        <v>368.75</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1671,22 +1671,22 @@
         <v>51</v>
       </c>
       <c r="B31">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="C31">
-        <v>3.83</v>
+        <v>4.01</v>
       </c>
       <c r="D31">
         <f>C31*$B$3</f>
       </c>
       <c r="E31">
-        <v>395.33</v>
+        <v>410.38</v>
       </c>
       <c r="F31">
-        <v>282.2</v>
+        <v>273.13</v>
       </c>
       <c r="G31">
-        <v>287.88</v>
+        <v>261.25</v>
       </c>
       <c r="H31">
         <f>MIN(E31:G31)</f>
@@ -1709,22 +1709,22 @@
         <v>52</v>
       </c>
       <c r="B32">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C32">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>432.58</v>
+        <v>401.13</v>
       </c>
       <c r="F32">
-        <v>273.74</v>
+        <v>268.63</v>
       </c>
       <c r="G32">
-        <v>267.68</v>
+        <v>273.75</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -1747,22 +1747,22 @@
         <v>53</v>
       </c>
       <c r="B33">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C33">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="D33">
         <f>C33*$B$3</f>
       </c>
       <c r="E33">
-        <v>324.87</v>
+        <v>351.63</v>
       </c>
       <c r="F33">
-        <v>238.76</v>
+        <v>222.13</v>
       </c>
       <c r="G33">
-        <v>236.11</v>
+        <v>227.5</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -1785,22 +1785,22 @@
         <v>54</v>
       </c>
       <c r="B34">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C34">
-        <v>3.71</v>
+        <v>3.28</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
       </c>
       <c r="E34">
-        <v>416.54</v>
+        <v>410.38</v>
       </c>
       <c r="F34">
-        <v>250.88</v>
+        <v>244.5</v>
       </c>
       <c r="G34">
-        <v>237.12</v>
+        <v>239.37</v>
       </c>
       <c r="H34">
         <f>MIN(E34:G34)</f>
@@ -1823,22 +1823,22 @@
         <v>55</v>
       </c>
       <c r="B35">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C35">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="D35">
         <f>C35*$B$3</f>
       </c>
       <c r="E35">
-        <v>287.5</v>
+        <v>289.5</v>
       </c>
       <c r="F35">
-        <v>239.9</v>
+        <v>222.5</v>
       </c>
       <c r="G35">
-        <v>236.49</v>
+        <v>201.13</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -1861,22 +1861,22 @@
         <v>56</v>
       </c>
       <c r="B36">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C36">
-        <v>3.16</v>
+        <v>2.82</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
       </c>
       <c r="E36">
-        <v>344.45</v>
+        <v>349.13</v>
       </c>
       <c r="F36">
-        <v>241.79</v>
+        <v>225</v>
       </c>
       <c r="G36">
-        <v>238.01</v>
+        <v>218.75</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -1899,22 +1899,22 @@
         <v>57</v>
       </c>
       <c r="B37">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="C37">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="D37">
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>341.79</v>
+        <v>308.75</v>
       </c>
       <c r="F37">
-        <v>232.07</v>
+        <v>223.75</v>
       </c>
       <c r="G37">
-        <v>229.8</v>
+        <v>217.5</v>
       </c>
       <c r="H37">
         <f>MIN(E37:G37)</f>
@@ -1937,22 +1937,22 @@
         <v>58</v>
       </c>
       <c r="B38">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="C38">
-        <v>3.98</v>
+        <v>4.66</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>565.78</v>
+        <v>531.25</v>
       </c>
       <c r="F38">
-        <v>338.26</v>
+        <v>361.25</v>
       </c>
       <c r="G38">
-        <v>327.02</v>
+        <v>372.5</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -1975,7 +1975,7 @@
         <v>59</v>
       </c>
       <c r="B39">
-        <v>701</v>
+        <v>659</v>
       </c>
       <c r="C39">
         <v>4.13</v>
@@ -1984,13 +1984,13 @@
         <f>C39*$B$3</f>
       </c>
       <c r="E39">
-        <v>497.1</v>
+        <v>449.88</v>
       </c>
       <c r="F39">
-        <v>342.17</v>
+        <v>337.5</v>
       </c>
       <c r="G39">
-        <v>333.33</v>
+        <v>315</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -2013,22 +2013,22 @@
         <v>60</v>
       </c>
       <c r="B40">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="C40">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>305.43</v>
+        <v>306.25</v>
       </c>
       <c r="F40">
-        <v>239.77</v>
+        <v>225</v>
       </c>
       <c r="G40">
-        <v>233.59</v>
+        <v>221.88</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -2051,22 +2051,22 @@
         <v>61</v>
       </c>
       <c r="B41">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C41">
-        <v>7.38</v>
+        <v>7.29</v>
       </c>
       <c r="D41">
         <f>C41*$B$3</f>
       </c>
       <c r="E41">
-        <v>805.94</v>
+        <v>923.25</v>
       </c>
       <c r="F41">
-        <v>630.05</v>
+        <v>648.63</v>
       </c>
       <c r="G41">
-        <v>650.13</v>
+        <v>640.88</v>
       </c>
       <c r="H41">
         <f>MIN(E41:G41)</f>
@@ -2089,22 +2089,22 @@
         <v>62</v>
       </c>
       <c r="B42">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C42">
-        <v>11.66</v>
+        <v>11.36</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
       </c>
       <c r="E42">
-        <v>1211.49</v>
+        <v>1154</v>
       </c>
       <c r="F42">
-        <v>972.23</v>
+        <v>883.75</v>
       </c>
       <c r="G42">
-        <v>978.54</v>
+        <v>923.75</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2127,22 +2127,22 @@
         <v>64</v>
       </c>
       <c r="B43">
-        <v>828</v>
+        <v>682</v>
       </c>
       <c r="C43">
-        <v>6.05</v>
+        <v>5.89</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>734.72</v>
+        <v>652.13</v>
       </c>
       <c r="F43">
-        <v>513.51</v>
+        <v>497.5</v>
       </c>
       <c r="G43">
-        <v>500.89</v>
+        <v>487.5</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2165,22 +2165,22 @@
         <v>65</v>
       </c>
       <c r="B44">
-        <v>871</v>
+        <v>757</v>
       </c>
       <c r="C44">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="D44">
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>451.26</v>
+        <v>428</v>
       </c>
       <c r="F44">
-        <v>315.66</v>
+        <v>316.25</v>
       </c>
       <c r="G44">
-        <v>331.31</v>
+        <v>321</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2203,22 +2203,22 @@
         <v>66</v>
       </c>
       <c r="B45">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="C45">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="D45">
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>341.79</v>
+        <v>370.88</v>
       </c>
       <c r="F45">
-        <v>225.88</v>
+        <v>227.25</v>
       </c>
       <c r="G45">
-        <v>223.49</v>
+        <v>198.75</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2241,22 +2241,22 @@
         <v>67</v>
       </c>
       <c r="B46">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C46">
-        <v>10.76</v>
+        <v>10.5</v>
       </c>
       <c r="D46">
         <f>C46*$B$3</f>
       </c>
       <c r="E46">
-        <v>1087.63</v>
+        <v>1062.5</v>
       </c>
       <c r="F46">
-        <v>938.26</v>
+        <v>925.63</v>
       </c>
       <c r="G46">
-        <v>860.61</v>
+        <v>839.5</v>
       </c>
       <c r="H46">
         <f>MIN(E46:G46)</f>
@@ -2279,22 +2279,22 @@
         <v>68</v>
       </c>
       <c r="B47">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C47">
-        <v>3.62</v>
+        <v>3.73</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>441.92</v>
+        <v>407</v>
       </c>
       <c r="F47">
-        <v>348.36</v>
+        <v>333.88</v>
       </c>
       <c r="G47">
-        <v>325.63</v>
+        <v>321.13</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2317,22 +2317,22 @@
         <v>69</v>
       </c>
       <c r="B48">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C48">
-        <v>9.04</v>
+        <v>9.9</v>
       </c>
       <c r="D48">
         <f>C48*$B$3</f>
       </c>
       <c r="E48">
-        <v>1096.97</v>
+        <v>1061.63</v>
       </c>
       <c r="F48">
-        <v>714.27</v>
+        <v>849.87</v>
       </c>
       <c r="G48">
-        <v>782.07</v>
+        <v>811</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2355,22 +2355,22 @@
         <v>70</v>
       </c>
       <c r="B49">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C49">
-        <v>30.55</v>
+        <v>31.46</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>3596.35</v>
+        <v>3402.5</v>
       </c>
       <c r="F49">
-        <v>2487.25</v>
+        <v>2412.25</v>
       </c>
       <c r="G49">
-        <v>2671.73</v>
+        <v>2511.25</v>
       </c>
       <c r="H49">
         <f>MIN(E49:G49)</f>
@@ -2393,22 +2393,22 @@
         <v>71</v>
       </c>
       <c r="B50">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="C50">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="D50">
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>250.25</v>
+        <v>222.38</v>
       </c>
       <c r="F50">
-        <v>179.29</v>
+        <v>156.25</v>
       </c>
       <c r="G50">
-        <v>175.13</v>
+        <v>147.25</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2431,22 +2431,22 @@
         <v>72</v>
       </c>
       <c r="B51">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="C51">
-        <v>3.84</v>
+        <v>3.79</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>485.23</v>
+        <v>421.25</v>
       </c>
       <c r="F51">
-        <v>334.47</v>
+        <v>312.63</v>
       </c>
       <c r="G51">
-        <v>325.51</v>
+        <v>313.38</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2469,22 +2469,22 @@
         <v>73</v>
       </c>
       <c r="B52">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C52">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>247.73</v>
+        <v>227.38</v>
       </c>
       <c r="F52">
-        <v>145.2</v>
+        <v>136.25</v>
       </c>
       <c r="G52">
-        <v>168.81</v>
+        <v>148.63</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2507,22 +2507,22 @@
         <v>74</v>
       </c>
       <c r="B53">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C53">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>324.87</v>
+        <v>328.13</v>
       </c>
       <c r="F53">
-        <v>237.37</v>
+        <v>241.25</v>
       </c>
       <c r="G53">
-        <v>228.54</v>
+        <v>226.25</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2545,22 +2545,22 @@
         <v>75</v>
       </c>
       <c r="B54">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C54">
-        <v>8.76</v>
+        <v>8.24</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
       </c>
       <c r="E54">
-        <v>905.18</v>
+        <v>885.38</v>
       </c>
       <c r="F54">
-        <v>627.53</v>
+        <v>625</v>
       </c>
       <c r="G54">
-        <v>649.12</v>
+        <v>716.25</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2583,22 +2583,22 @@
         <v>76</v>
       </c>
       <c r="B55">
-        <v>264</v>
+        <v>230</v>
       </c>
       <c r="C55">
-        <v>15.12</v>
+        <v>15.39</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>1924.12</v>
+        <v>1867.37</v>
       </c>
       <c r="F55">
-        <v>1239.78</v>
+        <v>1237.13</v>
       </c>
       <c r="G55">
-        <v>1196.97</v>
+        <v>1196.13</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2621,22 +2621,22 @@
         <v>77</v>
       </c>
       <c r="B56">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C56">
-        <v>6.14</v>
+        <v>6.02</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>712.63</v>
+        <v>650.38</v>
       </c>
       <c r="F56">
-        <v>521.84</v>
+        <v>498.5</v>
       </c>
       <c r="G56">
-        <v>491.16</v>
+        <v>484.75</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2659,22 +2659,22 @@
         <v>78</v>
       </c>
       <c r="B57">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C57">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>285.86</v>
+        <v>261</v>
       </c>
       <c r="F57">
-        <v>190.03</v>
+        <v>187.5</v>
       </c>
       <c r="G57">
-        <v>189.39</v>
+        <v>178.75</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2697,22 +2697,22 @@
         <v>79</v>
       </c>
       <c r="B58">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C58">
-        <v>4.1</v>
+        <v>3.89</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>435.23</v>
+        <v>419.63</v>
       </c>
       <c r="F58">
-        <v>321.97</v>
+        <v>311.88</v>
       </c>
       <c r="G58">
-        <v>322.6</v>
+        <v>298.75</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2735,22 +2735,22 @@
         <v>80</v>
       </c>
       <c r="B59">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="C59">
-        <v>42.37</v>
+        <v>40.07</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
       </c>
       <c r="E59">
-        <v>4352.41</v>
+        <v>4261.25</v>
       </c>
       <c r="F59">
-        <v>3320.34</v>
+        <v>3110</v>
       </c>
       <c r="G59">
-        <v>3356.07</v>
+        <v>3118.5</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -2773,22 +2773,22 @@
         <v>81</v>
       </c>
       <c r="B60">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C60">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>521.72</v>
+        <v>534.63</v>
       </c>
       <c r="F60">
-        <v>377.53</v>
+        <v>387.5</v>
       </c>
       <c r="G60">
-        <v>392.55</v>
+        <v>384.88</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -2811,22 +2811,22 @@
         <v>82</v>
       </c>
       <c r="B61">
-        <v>262</v>
+        <v>135</v>
       </c>
       <c r="C61">
-        <v>7.05</v>
+        <v>7.16</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>753.29</v>
+        <v>835.13</v>
       </c>
       <c r="F61">
-        <v>586.49</v>
+        <v>587.5</v>
       </c>
       <c r="G61">
-        <v>584.47</v>
+        <v>587.5</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>

--- a/lisskins-steamdt-compare/comparison.xlsx
+++ b/lisskins-steamdt-compare/comparison.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="83">
   <si>
-    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 02.10.2026 15:08</t>
+    <t>Сравнение цен LIS-SKINS vs SteamDT (Steam/BUFF/YouPin), обновлено 05.10.2026 20:09</t>
   </si>
   <si>
     <t>Список: https://lis-skins.com/ru/market/cs2/?user_list_id=01kvbgbzhn0acjzykwfagmc96y</t>
@@ -666,7 +666,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>83.2454</v>
+        <v>84.9309</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -724,19 +724,19 @@
         <v>131</v>
       </c>
       <c r="C6">
-        <v>26.41</v>
+        <v>25.69</v>
       </c>
       <c r="D6">
         <f>C6*$B$3</f>
       </c>
       <c r="E6">
-        <v>2843.63</v>
+        <v>2994.5</v>
       </c>
       <c r="F6">
-        <v>2110</v>
+        <v>2107.25</v>
       </c>
       <c r="G6">
-        <v>2096.25</v>
+        <v>2000</v>
       </c>
       <c r="H6">
         <f>MIN(E6:G6)</f>
@@ -759,22 +759,22 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="C7">
-        <v>17.31</v>
+        <v>16.78</v>
       </c>
       <c r="D7">
         <f>C7*$B$3</f>
       </c>
       <c r="E7">
-        <v>1930.38</v>
+        <v>1961.87</v>
       </c>
       <c r="F7">
-        <v>1369.13</v>
+        <v>1350</v>
       </c>
       <c r="G7">
-        <v>1425</v>
+        <v>1375</v>
       </c>
       <c r="H7">
         <f>MIN(E7:G7)</f>
@@ -797,22 +797,22 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="C8">
-        <v>20.76</v>
+        <v>19.25</v>
       </c>
       <c r="D8">
         <f>C8*$B$3</f>
       </c>
       <c r="E8">
-        <v>2306.38</v>
+        <v>2235.38</v>
       </c>
       <c r="F8">
-        <v>1699.63</v>
+        <v>1645</v>
       </c>
       <c r="G8">
-        <v>1518.75</v>
+        <v>1600</v>
       </c>
       <c r="H8">
         <f>MIN(E8:G8)</f>
@@ -835,22 +835,22 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C9">
-        <v>12.64</v>
+        <v>11.79</v>
       </c>
       <c r="D9">
         <f>C9*$B$3</f>
       </c>
       <c r="E9">
-        <v>1539.25</v>
+        <v>1494.63</v>
       </c>
       <c r="F9">
-        <v>983.75</v>
+        <v>1088.25</v>
       </c>
       <c r="G9">
-        <v>932.63</v>
+        <v>916.87</v>
       </c>
       <c r="H9">
         <f>MIN(E9:G9)</f>
@@ -873,22 +873,22 @@
         <v>26</v>
       </c>
       <c r="B10">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="C10">
-        <v>33.41</v>
+        <v>33.48</v>
       </c>
       <c r="D10">
         <f>C10*$B$3</f>
       </c>
       <c r="E10">
-        <v>3971.63</v>
+        <v>3942.25</v>
       </c>
       <c r="F10">
-        <v>2699.88</v>
+        <v>2837.38</v>
       </c>
       <c r="G10">
-        <v>2711.75</v>
+        <v>2606.25</v>
       </c>
       <c r="H10">
         <f>MIN(E10:G10)</f>
@@ -911,22 +911,22 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C11">
-        <v>24.16</v>
+        <v>24.61</v>
       </c>
       <c r="D11">
         <f>C11*$B$3</f>
       </c>
       <c r="E11">
-        <v>2728.63</v>
+        <v>2825.88</v>
       </c>
       <c r="F11">
-        <v>1967.37</v>
+        <v>1962.5</v>
       </c>
       <c r="G11">
-        <v>1967.25</v>
+        <v>2050</v>
       </c>
       <c r="H11">
         <f>MIN(E11:G11)</f>
@@ -949,22 +949,22 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C12">
-        <v>16.4</v>
+        <v>17.03</v>
       </c>
       <c r="D12">
         <f>C12*$B$3</f>
       </c>
       <c r="E12">
-        <v>1685.25</v>
+        <v>2002.12</v>
       </c>
       <c r="F12">
-        <v>1312.5</v>
+        <v>1348.5</v>
       </c>
       <c r="G12">
-        <v>1406.25</v>
+        <v>1325</v>
       </c>
       <c r="H12">
         <f>MIN(E12:G12)</f>
@@ -987,22 +987,22 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="C13">
-        <v>8.75</v>
+        <v>8.57</v>
       </c>
       <c r="D13">
         <f>C13*$B$3</f>
       </c>
       <c r="E13">
-        <v>953.38</v>
+        <v>928.5</v>
       </c>
       <c r="F13">
-        <v>746.38</v>
+        <v>717.38</v>
       </c>
       <c r="G13">
-        <v>707</v>
+        <v>676.25</v>
       </c>
       <c r="H13">
         <f>MIN(E13:G13)</f>
@@ -1025,22 +1025,22 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="C14">
-        <v>6.19</v>
+        <v>6.31</v>
       </c>
       <c r="D14">
         <f>C14*$B$3</f>
       </c>
       <c r="E14">
-        <v>859.38</v>
+        <v>684.38</v>
       </c>
       <c r="F14">
-        <v>500</v>
+        <v>507.5</v>
       </c>
       <c r="G14">
-        <v>510.5</v>
+        <v>511.88</v>
       </c>
       <c r="H14">
         <f>MIN(E14:G14)</f>
@@ -1063,22 +1063,22 @@
         <v>32</v>
       </c>
       <c r="B15">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C15">
-        <v>39.07</v>
+        <v>38.34</v>
       </c>
       <c r="D15">
         <f>C15*$B$3</f>
       </c>
       <c r="E15">
-        <v>4196.63</v>
+        <v>5035.25</v>
       </c>
       <c r="F15">
-        <v>3137.5</v>
+        <v>2975</v>
       </c>
       <c r="G15">
-        <v>3159.25</v>
+        <v>2975.25</v>
       </c>
       <c r="H15">
         <f>MIN(E15:G15)</f>
@@ -1101,22 +1101,22 @@
         <v>33</v>
       </c>
       <c r="B16">
-        <v>624</v>
+        <v>648</v>
       </c>
       <c r="C16">
-        <v>2.72</v>
+        <v>2.57</v>
       </c>
       <c r="D16">
         <f>C16*$B$3</f>
       </c>
       <c r="E16">
-        <v>323.13</v>
+        <v>320.38</v>
       </c>
       <c r="F16">
-        <v>211.25</v>
+        <v>212.37</v>
       </c>
       <c r="G16">
-        <v>217.5</v>
+        <v>200</v>
       </c>
       <c r="H16">
         <f>MIN(E16:G16)</f>
@@ -1139,22 +1139,22 @@
         <v>34</v>
       </c>
       <c r="B17">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="C17">
-        <v>8.21</v>
+        <v>8.03</v>
       </c>
       <c r="D17">
         <f>C17*$B$3</f>
       </c>
       <c r="E17">
-        <v>820.75</v>
+        <v>1048.5</v>
       </c>
       <c r="F17">
-        <v>670</v>
+        <v>682.13</v>
       </c>
       <c r="G17">
-        <v>643.75</v>
+        <v>625</v>
       </c>
       <c r="H17">
         <f>MIN(E17:G17)</f>
@@ -1177,22 +1177,22 @@
         <v>37</v>
       </c>
       <c r="B18">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C18">
-        <v>6.15</v>
+        <v>6.06</v>
       </c>
       <c r="D18">
         <f>C18*$B$3</f>
       </c>
       <c r="E18">
-        <v>766.25</v>
+        <v>706.25</v>
       </c>
       <c r="F18">
-        <v>572.5</v>
+        <v>525</v>
       </c>
       <c r="G18">
-        <v>492.5</v>
+        <v>477.5</v>
       </c>
       <c r="H18">
         <f>MIN(E18:G18)</f>
@@ -1215,22 +1215,22 @@
         <v>38</v>
       </c>
       <c r="B19">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C19">
-        <v>5.36</v>
+        <v>5.14</v>
       </c>
       <c r="D19">
         <f>C19*$B$3</f>
       </c>
       <c r="E19">
-        <v>610.13</v>
+        <v>620.63</v>
       </c>
       <c r="F19">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="G19">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="H19">
         <f>MIN(E19:G19)</f>
@@ -1253,7 +1253,7 @@
         <v>39</v>
       </c>
       <c r="B20">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C20">
         <v>3.41</v>
@@ -1262,13 +1262,13 @@
         <f>C20*$B$3</f>
       </c>
       <c r="E20">
-        <v>372.63</v>
+        <v>369.88</v>
       </c>
       <c r="F20">
-        <v>261</v>
+        <v>256.25</v>
       </c>
       <c r="G20">
-        <v>269</v>
+        <v>273.63</v>
       </c>
       <c r="H20">
         <f>MIN(E20:G20)</f>
@@ -1291,22 +1291,22 @@
         <v>40</v>
       </c>
       <c r="B21">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C21">
-        <v>4.09</v>
+        <v>3.85</v>
       </c>
       <c r="D21">
         <f>C21*$B$3</f>
       </c>
       <c r="E21">
-        <v>492.62</v>
+        <v>502.38</v>
       </c>
       <c r="F21">
-        <v>319</v>
+        <v>306.25</v>
       </c>
       <c r="G21">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="H21">
         <f>MIN(E21:G21)</f>
@@ -1329,22 +1329,22 @@
         <v>41</v>
       </c>
       <c r="B22">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C22">
-        <v>8.91</v>
+        <v>2.78</v>
       </c>
       <c r="D22">
         <f>C22*$B$3</f>
       </c>
       <c r="E22">
-        <v>450.62</v>
+        <v>465.5</v>
       </c>
       <c r="F22">
-        <v>224.13</v>
+        <v>293.75</v>
       </c>
       <c r="G22">
-        <v>217.5</v>
+        <v>216.13</v>
       </c>
       <c r="H22">
         <f>MIN(E22:G22)</f>
@@ -1367,22 +1367,22 @@
         <v>42</v>
       </c>
       <c r="B23">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="C23">
-        <v>3.27</v>
+        <v>3.14</v>
       </c>
       <c r="D23">
         <f>C23*$B$3</f>
       </c>
       <c r="E23">
-        <v>397.75</v>
+        <v>343.88</v>
       </c>
       <c r="F23">
-        <v>255.63</v>
+        <v>240.25</v>
       </c>
       <c r="G23">
-        <v>259.88</v>
+        <v>244.25</v>
       </c>
       <c r="H23">
         <f>MIN(E23:G23)</f>
@@ -1405,22 +1405,22 @@
         <v>43</v>
       </c>
       <c r="B24">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="C24">
-        <v>5.96</v>
+        <v>5.75</v>
       </c>
       <c r="D24">
         <f>C24*$B$3</f>
       </c>
       <c r="E24">
-        <v>593.38</v>
+        <v>624</v>
       </c>
       <c r="F24">
-        <v>451.13</v>
+        <v>448.75</v>
       </c>
       <c r="G24">
-        <v>438.12</v>
+        <v>448.75</v>
       </c>
       <c r="H24">
         <f>MIN(E24:G24)</f>
@@ -1443,22 +1443,22 @@
         <v>45</v>
       </c>
       <c r="B25">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="C25">
-        <v>5.61</v>
+        <v>5.48</v>
       </c>
       <c r="D25">
         <f>C25*$B$3</f>
       </c>
       <c r="E25">
-        <v>595</v>
+        <v>578.75</v>
       </c>
       <c r="F25">
-        <v>440.63</v>
+        <v>437.5</v>
       </c>
       <c r="G25">
-        <v>429.88</v>
+        <v>425.88</v>
       </c>
       <c r="H25">
         <f>MIN(E25:G25)</f>
@@ -1481,22 +1481,22 @@
         <v>46</v>
       </c>
       <c r="B26">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C26">
-        <v>6.35</v>
+        <v>6.09</v>
       </c>
       <c r="D26">
         <f>C26*$B$3</f>
       </c>
       <c r="E26">
-        <v>658</v>
+        <v>626.5</v>
       </c>
       <c r="F26">
-        <v>498.75</v>
+        <v>509.88</v>
       </c>
       <c r="G26">
-        <v>462.5</v>
+        <v>473.5</v>
       </c>
       <c r="H26">
         <f>MIN(E26:G26)</f>
@@ -1519,22 +1519,22 @@
         <v>47</v>
       </c>
       <c r="B27">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C27">
-        <v>4.71</v>
+        <v>4.46</v>
       </c>
       <c r="D27">
         <f>C27*$B$3</f>
       </c>
       <c r="E27">
-        <v>466.63</v>
+        <v>503.25</v>
       </c>
       <c r="F27">
-        <v>352.5</v>
+        <v>358.63</v>
       </c>
       <c r="G27">
-        <v>342.38</v>
+        <v>346</v>
       </c>
       <c r="H27">
         <f>MIN(E27:G27)</f>
@@ -1557,22 +1557,22 @@
         <v>48</v>
       </c>
       <c r="B28">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="C28">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="D28">
         <f>C28*$B$3</f>
       </c>
       <c r="E28">
-        <v>502.75</v>
+        <v>588.75</v>
       </c>
       <c r="F28">
-        <v>275.63</v>
+        <v>310.25</v>
       </c>
       <c r="G28">
-        <v>273.38</v>
+        <v>293.63</v>
       </c>
       <c r="H28">
         <f>MIN(E28:G28)</f>
@@ -1595,22 +1595,22 @@
         <v>49</v>
       </c>
       <c r="B29">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="C29">
-        <v>4.57</v>
+        <v>4.37</v>
       </c>
       <c r="D29">
         <f>C29*$B$3</f>
       </c>
       <c r="E29">
-        <v>499.38</v>
+        <v>503.25</v>
       </c>
       <c r="F29">
-        <v>396.25</v>
+        <v>373.75</v>
       </c>
       <c r="G29">
-        <v>348</v>
+        <v>339.63</v>
       </c>
       <c r="H29">
         <f>MIN(E29:G29)</f>
@@ -1633,22 +1633,22 @@
         <v>50</v>
       </c>
       <c r="B30">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="C30">
-        <v>4.76</v>
+        <v>4.53</v>
       </c>
       <c r="D30">
         <f>C30*$B$3</f>
       </c>
       <c r="E30">
-        <v>419.63</v>
+        <v>515</v>
       </c>
       <c r="F30">
-        <v>385</v>
+        <v>366.63</v>
       </c>
       <c r="G30">
-        <v>368.75</v>
+        <v>362.5</v>
       </c>
       <c r="H30">
         <f>MIN(E30:G30)</f>
@@ -1671,22 +1671,22 @@
         <v>51</v>
       </c>
       <c r="B31">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C31">
-        <v>4.01</v>
+        <v>3.12</v>
       </c>
       <c r="D31">
         <f>C31*$B$3</f>
       </c>
       <c r="E31">
-        <v>410.38</v>
+        <v>454.62</v>
       </c>
       <c r="F31">
-        <v>273.13</v>
+        <v>267.88</v>
       </c>
       <c r="G31">
-        <v>261.25</v>
+        <v>242.5</v>
       </c>
       <c r="H31">
         <f>MIN(E31:G31)</f>
@@ -1709,22 +1709,22 @@
         <v>52</v>
       </c>
       <c r="B32">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C32">
-        <v>3.67</v>
+        <v>3.44</v>
       </c>
       <c r="D32">
         <f>C32*$B$3</f>
       </c>
       <c r="E32">
-        <v>401.13</v>
+        <v>368.13</v>
       </c>
       <c r="F32">
-        <v>268.63</v>
+        <v>266</v>
       </c>
       <c r="G32">
-        <v>273.75</v>
+        <v>267.38</v>
       </c>
       <c r="H32">
         <f>MIN(E32:G32)</f>
@@ -1747,22 +1747,22 @@
         <v>53</v>
       </c>
       <c r="B33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C33">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="D33">
         <f>C33*$B$3</f>
       </c>
       <c r="E33">
-        <v>351.63</v>
+        <v>377.38</v>
       </c>
       <c r="F33">
-        <v>222.13</v>
+        <v>211.25</v>
       </c>
       <c r="G33">
-        <v>227.5</v>
+        <v>218.75</v>
       </c>
       <c r="H33">
         <f>MIN(E33:G33)</f>
@@ -1785,22 +1785,22 @@
         <v>54</v>
       </c>
       <c r="B34">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C34">
-        <v>3.28</v>
+        <v>3.13</v>
       </c>
       <c r="D34">
         <f>C34*$B$3</f>
       </c>
       <c r="E34">
-        <v>410.38</v>
+        <v>380.75</v>
       </c>
       <c r="F34">
-        <v>244.5</v>
+        <v>234.75</v>
       </c>
       <c r="G34">
-        <v>239.37</v>
+        <v>243.13</v>
       </c>
       <c r="H34">
         <f>MIN(E34:G34)</f>
@@ -1823,22 +1823,22 @@
         <v>55</v>
       </c>
       <c r="B35">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="C35">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="D35">
         <f>C35*$B$3</f>
       </c>
       <c r="E35">
-        <v>289.5</v>
+        <v>292.63</v>
       </c>
       <c r="F35">
-        <v>222.5</v>
+        <v>194.88</v>
       </c>
       <c r="G35">
-        <v>201.13</v>
+        <v>196.25</v>
       </c>
       <c r="H35">
         <f>MIN(E35:G35)</f>
@@ -1861,22 +1861,22 @@
         <v>56</v>
       </c>
       <c r="B36">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="C36">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="D36">
         <f>C36*$B$3</f>
       </c>
       <c r="E36">
-        <v>349.13</v>
+        <v>344.63</v>
       </c>
       <c r="F36">
-        <v>225</v>
+        <v>216.5</v>
       </c>
       <c r="G36">
-        <v>218.75</v>
+        <v>218.38</v>
       </c>
       <c r="H36">
         <f>MIN(E36:G36)</f>
@@ -1899,22 +1899,22 @@
         <v>57</v>
       </c>
       <c r="B37">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="C37">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="D37">
         <f>C37*$B$3</f>
       </c>
       <c r="E37">
-        <v>308.75</v>
+        <v>306.13</v>
       </c>
       <c r="F37">
-        <v>223.75</v>
+        <v>218.75</v>
       </c>
       <c r="G37">
-        <v>217.5</v>
+        <v>203.5</v>
       </c>
       <c r="H37">
         <f>MIN(E37:G37)</f>
@@ -1937,22 +1937,22 @@
         <v>58</v>
       </c>
       <c r="B38">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="C38">
-        <v>4.66</v>
+        <v>3.94</v>
       </c>
       <c r="D38">
         <f>C38*$B$3</f>
       </c>
       <c r="E38">
-        <v>531.25</v>
+        <v>439.5</v>
       </c>
       <c r="F38">
-        <v>361.25</v>
+        <v>334.88</v>
       </c>
       <c r="G38">
-        <v>372.5</v>
+        <v>306.13</v>
       </c>
       <c r="H38">
         <f>MIN(E38:G38)</f>
@@ -1975,22 +1975,22 @@
         <v>59</v>
       </c>
       <c r="B39">
-        <v>659</v>
+        <v>687</v>
       </c>
       <c r="C39">
-        <v>4.13</v>
+        <v>3.88</v>
       </c>
       <c r="D39">
         <f>C39*$B$3</f>
       </c>
       <c r="E39">
-        <v>449.88</v>
+        <v>443.63</v>
       </c>
       <c r="F39">
-        <v>337.5</v>
+        <v>287.5</v>
       </c>
       <c r="G39">
-        <v>315</v>
+        <v>315.88</v>
       </c>
       <c r="H39">
         <f>MIN(E39:G39)</f>
@@ -2013,22 +2013,22 @@
         <v>60</v>
       </c>
       <c r="B40">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C40">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="D40">
         <f>C40*$B$3</f>
       </c>
       <c r="E40">
-        <v>306.25</v>
+        <v>301.88</v>
       </c>
       <c r="F40">
-        <v>225</v>
+        <v>236.25</v>
       </c>
       <c r="G40">
-        <v>221.88</v>
+        <v>215</v>
       </c>
       <c r="H40">
         <f>MIN(E40:G40)</f>
@@ -2051,22 +2051,22 @@
         <v>61</v>
       </c>
       <c r="B41">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C41">
-        <v>7.29</v>
+        <v>7.76</v>
       </c>
       <c r="D41">
         <f>C41*$B$3</f>
       </c>
       <c r="E41">
-        <v>923.25</v>
+        <v>804.37</v>
       </c>
       <c r="F41">
-        <v>648.63</v>
+        <v>637.5</v>
       </c>
       <c r="G41">
-        <v>640.88</v>
+        <v>675</v>
       </c>
       <c r="H41">
         <f>MIN(E41:G41)</f>
@@ -2089,22 +2089,22 @@
         <v>62</v>
       </c>
       <c r="B42">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C42">
-        <v>11.36</v>
+        <v>10.97</v>
       </c>
       <c r="D42">
         <f>C42*$B$3</f>
       </c>
       <c r="E42">
-        <v>1154</v>
+        <v>1149.13</v>
       </c>
       <c r="F42">
-        <v>883.75</v>
+        <v>919.5</v>
       </c>
       <c r="G42">
-        <v>923.75</v>
+        <v>875</v>
       </c>
       <c r="H42">
         <f>MIN(E42:G42)</f>
@@ -2127,22 +2127,22 @@
         <v>64</v>
       </c>
       <c r="B43">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="C43">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="D43">
         <f>C43*$B$3</f>
       </c>
       <c r="E43">
-        <v>652.13</v>
+        <v>645.88</v>
       </c>
       <c r="F43">
-        <v>497.5</v>
+        <v>493.75</v>
       </c>
       <c r="G43">
-        <v>487.5</v>
+        <v>499.88</v>
       </c>
       <c r="H43">
         <f>MIN(E43:G43)</f>
@@ -2165,22 +2165,22 @@
         <v>65</v>
       </c>
       <c r="B44">
-        <v>757</v>
+        <v>821</v>
       </c>
       <c r="C44">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="D44">
         <f>C44*$B$3</f>
       </c>
       <c r="E44">
-        <v>428</v>
+        <v>406.75</v>
       </c>
       <c r="F44">
-        <v>316.25</v>
+        <v>323.75</v>
       </c>
       <c r="G44">
-        <v>321</v>
+        <v>322.25</v>
       </c>
       <c r="H44">
         <f>MIN(E44:G44)</f>
@@ -2203,22 +2203,22 @@
         <v>66</v>
       </c>
       <c r="B45">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="C45">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="D45">
         <f>C45*$B$3</f>
       </c>
       <c r="E45">
-        <v>370.88</v>
+        <v>367.38</v>
       </c>
       <c r="F45">
-        <v>227.25</v>
+        <v>247.5</v>
       </c>
       <c r="G45">
-        <v>198.75</v>
+        <v>218.75</v>
       </c>
       <c r="H45">
         <f>MIN(E45:G45)</f>
@@ -2241,22 +2241,22 @@
         <v>67</v>
       </c>
       <c r="B46">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C46">
-        <v>10.5</v>
+        <v>10.65</v>
       </c>
       <c r="D46">
         <f>C46*$B$3</f>
       </c>
       <c r="E46">
-        <v>1062.5</v>
+        <v>1012.37</v>
       </c>
       <c r="F46">
-        <v>925.63</v>
+        <v>922.38</v>
       </c>
       <c r="G46">
-        <v>839.5</v>
+        <v>838.63</v>
       </c>
       <c r="H46">
         <f>MIN(E46:G46)</f>
@@ -2279,22 +2279,22 @@
         <v>68</v>
       </c>
       <c r="B47">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C47">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="D47">
         <f>C47*$B$3</f>
       </c>
       <c r="E47">
-        <v>407</v>
+        <v>385.75</v>
       </c>
       <c r="F47">
-        <v>333.88</v>
+        <v>330.13</v>
       </c>
       <c r="G47">
-        <v>321.13</v>
+        <v>287.38</v>
       </c>
       <c r="H47">
         <f>MIN(E47:G47)</f>
@@ -2317,22 +2317,22 @@
         <v>69</v>
       </c>
       <c r="B48">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C48">
-        <v>9.9</v>
+        <v>9.77</v>
       </c>
       <c r="D48">
         <f>C48*$B$3</f>
       </c>
       <c r="E48">
-        <v>1061.63</v>
+        <v>1075.25</v>
       </c>
       <c r="F48">
-        <v>849.87</v>
+        <v>937.5</v>
       </c>
       <c r="G48">
-        <v>811</v>
+        <v>808.75</v>
       </c>
       <c r="H48">
         <f>MIN(E48:G48)</f>
@@ -2358,19 +2358,19 @@
         <v>121</v>
       </c>
       <c r="C49">
-        <v>31.46</v>
+        <v>30.88</v>
       </c>
       <c r="D49">
         <f>C49*$B$3</f>
       </c>
       <c r="E49">
-        <v>3402.5</v>
+        <v>3231.88</v>
       </c>
       <c r="F49">
-        <v>2412.25</v>
+        <v>2562.5</v>
       </c>
       <c r="G49">
-        <v>2511.25</v>
+        <v>2487.5</v>
       </c>
       <c r="H49">
         <f>MIN(E49:G49)</f>
@@ -2393,22 +2393,22 @@
         <v>71</v>
       </c>
       <c r="B50">
-        <v>368</v>
+        <v>448</v>
       </c>
       <c r="C50">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="D50">
         <f>C50*$B$3</f>
       </c>
       <c r="E50">
-        <v>222.38</v>
+        <v>215.5</v>
       </c>
       <c r="F50">
-        <v>156.25</v>
+        <v>153.75</v>
       </c>
       <c r="G50">
-        <v>147.25</v>
+        <v>144.75</v>
       </c>
       <c r="H50">
         <f>MIN(E50:G50)</f>
@@ -2431,22 +2431,22 @@
         <v>72</v>
       </c>
       <c r="B51">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="C51">
-        <v>3.79</v>
+        <v>3.54</v>
       </c>
       <c r="D51">
         <f>C51*$B$3</f>
       </c>
       <c r="E51">
-        <v>421.25</v>
+        <v>395</v>
       </c>
       <c r="F51">
-        <v>312.63</v>
+        <v>326.13</v>
       </c>
       <c r="G51">
-        <v>313.38</v>
+        <v>298.5</v>
       </c>
       <c r="H51">
         <f>MIN(E51:G51)</f>
@@ -2469,22 +2469,22 @@
         <v>73</v>
       </c>
       <c r="B52">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C52">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="D52">
         <f>C52*$B$3</f>
       </c>
       <c r="E52">
-        <v>227.38</v>
+        <v>198.75</v>
       </c>
       <c r="F52">
-        <v>136.25</v>
+        <v>135</v>
       </c>
       <c r="G52">
-        <v>148.63</v>
+        <v>147.38</v>
       </c>
       <c r="H52">
         <f>MIN(E52:G52)</f>
@@ -2507,22 +2507,22 @@
         <v>74</v>
       </c>
       <c r="B53">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="C53">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="D53">
         <f>C53*$B$3</f>
       </c>
       <c r="E53">
-        <v>328.13</v>
+        <v>298.5</v>
       </c>
       <c r="F53">
-        <v>241.25</v>
+        <v>233.75</v>
       </c>
       <c r="G53">
-        <v>226.25</v>
+        <v>225</v>
       </c>
       <c r="H53">
         <f>MIN(E53:G53)</f>
@@ -2545,22 +2545,22 @@
         <v>75</v>
       </c>
       <c r="B54">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="C54">
-        <v>8.24</v>
+        <v>8.94</v>
       </c>
       <c r="D54">
         <f>C54*$B$3</f>
       </c>
       <c r="E54">
-        <v>885.38</v>
+        <v>921</v>
       </c>
       <c r="F54">
-        <v>625</v>
+        <v>687.5</v>
       </c>
       <c r="G54">
-        <v>716.25</v>
+        <v>707.5</v>
       </c>
       <c r="H54">
         <f>MIN(E54:G54)</f>
@@ -2583,22 +2583,22 @@
         <v>76</v>
       </c>
       <c r="B55">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C55">
-        <v>15.39</v>
+        <v>15.09</v>
       </c>
       <c r="D55">
         <f>C55*$B$3</f>
       </c>
       <c r="E55">
-        <v>1867.37</v>
+        <v>1748.88</v>
       </c>
       <c r="F55">
-        <v>1237.13</v>
+        <v>1223.75</v>
       </c>
       <c r="G55">
-        <v>1196.13</v>
+        <v>1173.75</v>
       </c>
       <c r="H55">
         <f>MIN(E55:G55)</f>
@@ -2621,22 +2621,22 @@
         <v>77</v>
       </c>
       <c r="B56">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="C56">
-        <v>6.02</v>
+        <v>5.95</v>
       </c>
       <c r="D56">
         <f>C56*$B$3</f>
       </c>
       <c r="E56">
-        <v>650.38</v>
+        <v>659.25</v>
       </c>
       <c r="F56">
-        <v>498.5</v>
+        <v>496.75</v>
       </c>
       <c r="G56">
-        <v>484.75</v>
+        <v>477.87</v>
       </c>
       <c r="H56">
         <f>MIN(E56:G56)</f>
@@ -2659,22 +2659,22 @@
         <v>78</v>
       </c>
       <c r="B57">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="C57">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="D57">
         <f>C57*$B$3</f>
       </c>
       <c r="E57">
-        <v>261</v>
+        <v>296.88</v>
       </c>
       <c r="F57">
-        <v>187.5</v>
+        <v>181.13</v>
       </c>
       <c r="G57">
-        <v>178.75</v>
+        <v>162.5</v>
       </c>
       <c r="H57">
         <f>MIN(E57:G57)</f>
@@ -2697,22 +2697,22 @@
         <v>79</v>
       </c>
       <c r="B58">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="C58">
-        <v>3.89</v>
+        <v>3.54</v>
       </c>
       <c r="D58">
         <f>C58*$B$3</f>
       </c>
       <c r="E58">
-        <v>419.63</v>
+        <v>383.25</v>
       </c>
       <c r="F58">
-        <v>311.88</v>
+        <v>304.75</v>
       </c>
       <c r="G58">
-        <v>298.75</v>
+        <v>274.88</v>
       </c>
       <c r="H58">
         <f>MIN(E58:G58)</f>
@@ -2735,22 +2735,22 @@
         <v>80</v>
       </c>
       <c r="B59">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C59">
-        <v>40.07</v>
+        <v>37.26</v>
       </c>
       <c r="D59">
         <f>C59*$B$3</f>
       </c>
       <c r="E59">
-        <v>4261.25</v>
+        <v>4194</v>
       </c>
       <c r="F59">
-        <v>3110</v>
+        <v>3140.88</v>
       </c>
       <c r="G59">
-        <v>3118.5</v>
+        <v>2900</v>
       </c>
       <c r="H59">
         <f>MIN(E59:G59)</f>
@@ -2773,22 +2773,22 @@
         <v>81</v>
       </c>
       <c r="B60">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C60">
-        <v>4.47</v>
+        <v>4.65</v>
       </c>
       <c r="D60">
         <f>C60*$B$3</f>
       </c>
       <c r="E60">
-        <v>534.63</v>
+        <v>482.25</v>
       </c>
       <c r="F60">
-        <v>387.5</v>
+        <v>371.25</v>
       </c>
       <c r="G60">
-        <v>384.88</v>
+        <v>378.5</v>
       </c>
       <c r="H60">
         <f>MIN(E60:G60)</f>
@@ -2811,22 +2811,22 @@
         <v>82</v>
       </c>
       <c r="B61">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="C61">
-        <v>7.16</v>
+        <v>7</v>
       </c>
       <c r="D61">
         <f>C61*$B$3</f>
       </c>
       <c r="E61">
-        <v>835.13</v>
+        <v>773.25</v>
       </c>
       <c r="F61">
-        <v>587.5</v>
+        <v>572.5</v>
       </c>
       <c r="G61">
-        <v>587.5</v>
+        <v>573.5</v>
       </c>
       <c r="H61">
         <f>MIN(E61:G61)</f>
